--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -6018,12 +6018,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>sourced in inputs.csv</t>
+          <t>assumption: no tax depreciation life is established; the team economic project life is used as a proxy, not a sourced tax basis</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Straight-line tax depreciation over the tourism asset life, from opening.</t>
+          <t>Straight-line tax depreciation over the project life from opening. Chow review point 4.</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Zero tax in every case, because cumulative taxable income stays negative (Appraisal rows 29 and 30). The rule has no effect on the results.</t>
+          <t>Exact only where annual taxable income has one sign over the operating years, which holds for the base and every sensitivity case (constant annual taxable income). The Thai rule is five years (Revenue Code section 65 ter (12)). The workbook does not model loss vintages.</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B24" s="4">
-        <f>B9*(B15*(1-B5)*B27)/B28</f>
+        <f>B15*(1-B5)*B27/(B16*B27+B28/B9)</f>
         <v/>
       </c>
       <c r="C24" s="4">
@@ -8371,7 +8371,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Sensitivity cases (formula-based, pre-tax; tax is zero in every case because cumulative taxable income stays negative). Replacement capex is applied in the cases that carry it.</t>
+          <t>Sensitivity cases (formula-based). Pre-tax NPV in columns G and H; after-tax NPV in columns K and M, exact because annual taxable income is constant across operating years in each case (columns J and L).</t>
         </is>
       </c>
     </row>
@@ -8416,6 +8416,31 @@
           <t>Legacy NPV, pre-tax (THB bn)</t>
         </is>
       </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Replacement share per operating year</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Primary taxable income (THB bn a year)</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>Primary NPV, after tax (THB bn)</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>Legacy taxable income (THB bn a year)</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>Legacy NPV, after tax (THB bn)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8440,11 +8465,31 @@
         <v/>
       </c>
       <c r="G68" s="4">
-        <f>(D68-C68*$B$5)*$B$15*F68-B68*$B$28-$B$16*$B$9*F68</f>
+        <f>(D68-C68*$B$5)*$B$15*F68-B68*$B$28-I68*B68*$B$9*F68</f>
         <v/>
       </c>
       <c r="H68" s="4">
-        <f>(D68-C68*$B$5)*$C$15*F68-B68*($C$9/$B$9)*$B$28-$B$16*$C$9*F68</f>
+        <f>(D68-C68*$B$5)*$C$15*F68-B68*($C$9/$B$9)*$B$28-I68*B68*$C$9*F68</f>
+        <v/>
+      </c>
+      <c r="I68">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J68" s="4">
+        <f>D68*$B$15-C68*$B$5*$B$15-B68*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K68" s="4">
+        <f>G68-$B$17*MAX(0,J68)*F68</f>
+        <v/>
+      </c>
+      <c r="L68" s="4">
+        <f>D68*$C$15-C68*$B$5*$C$15-B68*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M68" s="4">
+        <f>H68-$B$17*MAX(0,L68)*F68</f>
         <v/>
       </c>
     </row>
@@ -8471,11 +8516,31 @@
         <v/>
       </c>
       <c r="G69" s="4">
-        <f>(D69-C69*$B$5)*$B$15*F69-B69*$B$28-$B$16*$B$9*F69</f>
+        <f>(D69-C69*$B$5)*$B$15*F69-B69*$B$28-I69*B69*$B$9*F69</f>
         <v/>
       </c>
       <c r="H69" s="4">
-        <f>(D69-C69*$B$5)*$C$15*F69-B69*($C$9/$B$9)*$B$28-$B$16*$C$9*F69</f>
+        <f>(D69-C69*$B$5)*$C$15*F69-B69*($C$9/$B$9)*$B$28-I69*B69*$C$9*F69</f>
+        <v/>
+      </c>
+      <c r="I69">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J69" s="4">
+        <f>D69*$B$15-C69*$B$5*$B$15-B69*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K69" s="4">
+        <f>G69-$B$17*MAX(0,J69)*F69</f>
+        <v/>
+      </c>
+      <c r="L69" s="4">
+        <f>D69*$C$15-C69*$B$5*$C$15-B69*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M69" s="4">
+        <f>H69-$B$17*MAX(0,L69)*F69</f>
         <v/>
       </c>
     </row>
@@ -8502,11 +8567,31 @@
         <v/>
       </c>
       <c r="G70" s="4">
-        <f>(D70-C70*$B$5)*$B$15*F70-B70*$B$28-$B$16*$B$9*F70</f>
+        <f>(D70-C70*$B$5)*$B$15*F70-B70*$B$28-I70*B70*$B$9*F70</f>
         <v/>
       </c>
       <c r="H70" s="4">
-        <f>(D70-C70*$B$5)*$C$15*F70-B70*($C$9/$B$9)*$B$28-$B$16*$C$9*F70</f>
+        <f>(D70-C70*$B$5)*$C$15*F70-B70*($C$9/$B$9)*$B$28-I70*B70*$C$9*F70</f>
+        <v/>
+      </c>
+      <c r="I70">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J70" s="4">
+        <f>D70*$B$15-C70*$B$5*$B$15-B70*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K70" s="4">
+        <f>G70-$B$17*MAX(0,J70)*F70</f>
+        <v/>
+      </c>
+      <c r="L70" s="4">
+        <f>D70*$C$15-C70*$B$5*$C$15-B70*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M70" s="4">
+        <f>H70-$B$17*MAX(0,L70)*F70</f>
         <v/>
       </c>
     </row>
@@ -8533,11 +8618,31 @@
         <v/>
       </c>
       <c r="G71" s="4">
-        <f>(D71-C71*$B$5)*$B$15*F71-B71*$B$28-$B$16*$B$9*F71</f>
+        <f>(D71-C71*$B$5)*$B$15*F71-B71*$B$28-I71*B71*$B$9*F71</f>
         <v/>
       </c>
       <c r="H71" s="4">
-        <f>(D71-C71*$B$5)*$C$15*F71-B71*($C$9/$B$9)*$B$28-$B$16*$C$9*F71</f>
+        <f>(D71-C71*$B$5)*$C$15*F71-B71*($C$9/$B$9)*$B$28-I71*B71*$C$9*F71</f>
+        <v/>
+      </c>
+      <c r="I71">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J71" s="4">
+        <f>D71*$B$15-C71*$B$5*$B$15-B71*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K71" s="4">
+        <f>G71-$B$17*MAX(0,J71)*F71</f>
+        <v/>
+      </c>
+      <c r="L71" s="4">
+        <f>D71*$C$15-C71*$B$5*$C$15-B71*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M71" s="4">
+        <f>H71-$B$17*MAX(0,L71)*F71</f>
         <v/>
       </c>
     </row>
@@ -8564,11 +8669,31 @@
         <v/>
       </c>
       <c r="G72" s="4">
-        <f>(D72-C72*$B$5)*$B$15*F72-B72*$B$28-$B$16*$B$9*F72</f>
+        <f>(D72-C72*$B$5)*$B$15*F72-B72*$B$28-I72*B72*$B$9*F72</f>
         <v/>
       </c>
       <c r="H72" s="4">
-        <f>(D72-C72*$B$5)*$C$15*F72-B72*($C$9/$B$9)*$B$28-$B$16*$C$9*F72</f>
+        <f>(D72-C72*$B$5)*$C$15*F72-B72*($C$9/$B$9)*$B$28-I72*B72*$C$9*F72</f>
+        <v/>
+      </c>
+      <c r="I72">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J72" s="4">
+        <f>D72*$B$15-C72*$B$5*$B$15-B72*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K72" s="4">
+        <f>G72-$B$17*MAX(0,J72)*F72</f>
+        <v/>
+      </c>
+      <c r="L72" s="4">
+        <f>D72*$C$15-C72*$B$5*$C$15-B72*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M72" s="4">
+        <f>H72-$B$17*MAX(0,L72)*F72</f>
         <v/>
       </c>
     </row>
@@ -8595,11 +8720,31 @@
         <v/>
       </c>
       <c r="G73" s="4">
-        <f>(D73-C73*$B$5)*$B$15*F73-B73*$B$28-$B$16*$B$9*F73</f>
+        <f>(D73-C73*$B$5)*$B$15*F73-B73*$B$28-I73*B73*$B$9*F73</f>
         <v/>
       </c>
       <c r="H73" s="4">
-        <f>(D73-C73*$B$5)*$C$15*F73-B73*($C$9/$B$9)*$B$28-$B$16*$C$9*F73</f>
+        <f>(D73-C73*$B$5)*$C$15*F73-B73*($C$9/$B$9)*$B$28-I73*B73*$C$9*F73</f>
+        <v/>
+      </c>
+      <c r="I73">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J73" s="4">
+        <f>D73*$B$15-C73*$B$5*$B$15-B73*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K73" s="4">
+        <f>G73-$B$17*MAX(0,J73)*F73</f>
+        <v/>
+      </c>
+      <c r="L73" s="4">
+        <f>D73*$C$15-C73*$B$5*$C$15-B73*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M73" s="4">
+        <f>H73-$B$17*MAX(0,L73)*F73</f>
         <v/>
       </c>
     </row>
@@ -8626,11 +8771,31 @@
         <v/>
       </c>
       <c r="G74" s="4">
-        <f>(D74-C74*$B$5)*$B$15*F74-B74*$B$28-$B$16*$B$9*F74</f>
+        <f>(D74-C74*$B$5)*$B$15*F74-B74*$B$28-I74*B74*$B$9*F74</f>
         <v/>
       </c>
       <c r="H74" s="4">
-        <f>(D74-C74*$B$5)*$C$15*F74-B74*($C$9/$B$9)*$B$28-$B$16*$C$9*F74</f>
+        <f>(D74-C74*$B$5)*$C$15*F74-B74*($C$9/$B$9)*$B$28-I74*B74*$C$9*F74</f>
+        <v/>
+      </c>
+      <c r="I74">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J74" s="4">
+        <f>D74*$B$15-C74*$B$5*$B$15-B74*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K74" s="4">
+        <f>G74-$B$17*MAX(0,J74)*F74</f>
+        <v/>
+      </c>
+      <c r="L74" s="4">
+        <f>D74*$C$15-C74*$B$5*$C$15-B74*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M74" s="4">
+        <f>H74-$B$17*MAX(0,L74)*F74</f>
         <v/>
       </c>
     </row>
@@ -8657,11 +8822,31 @@
         <v/>
       </c>
       <c r="G75" s="4">
-        <f>(D75-C75*$B$5)*$B$15*F75-B75*$B$28-$B$16*$B$9*F75</f>
+        <f>(D75-C75*$B$5)*$B$15*F75-B75*$B$28-I75*B75*$B$9*F75</f>
         <v/>
       </c>
       <c r="H75" s="4">
-        <f>(D75-C75*$B$5)*$C$15*F75-B75*($C$9/$B$9)*$B$28-$B$16*$C$9*F75</f>
+        <f>(D75-C75*$B$5)*$C$15*F75-B75*($C$9/$B$9)*$B$28-I75*B75*$C$9*F75</f>
+        <v/>
+      </c>
+      <c r="I75">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J75" s="4">
+        <f>D75*$B$15-C75*$B$5*$B$15-B75*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K75" s="4">
+        <f>G75-$B$17*MAX(0,J75)*F75</f>
+        <v/>
+      </c>
+      <c r="L75" s="4">
+        <f>D75*$C$15-C75*$B$5*$C$15-B75*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M75" s="4">
+        <f>H75-$B$17*MAX(0,L75)*F75</f>
         <v/>
       </c>
     </row>
@@ -8688,11 +8873,31 @@
         <v/>
       </c>
       <c r="G76" s="4">
-        <f>(D76-C76*$B$5)*$B$15*F76-B76*$B$28-$B$16*$B$9*F76</f>
+        <f>(D76-C76*$B$5)*$B$15*F76-B76*$B$28-I76*B76*$B$9*F76</f>
         <v/>
       </c>
       <c r="H76" s="4">
-        <f>(D76-C76*$B$5)*$C$15*F76-B76*($C$9/$B$9)*$B$28-$B$16*$C$9*F76</f>
+        <f>(D76-C76*$B$5)*$C$15*F76-B76*($C$9/$B$9)*$B$28-I76*B76*$C$9*F76</f>
+        <v/>
+      </c>
+      <c r="I76">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J76" s="4">
+        <f>D76*$B$15-C76*$B$5*$B$15-B76*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K76" s="4">
+        <f>G76-$B$17*MAX(0,J76)*F76</f>
+        <v/>
+      </c>
+      <c r="L76" s="4">
+        <f>D76*$C$15-C76*$B$5*$C$15-B76*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M76" s="4">
+        <f>H76-$B$17*MAX(0,L76)*F76</f>
         <v/>
       </c>
     </row>
@@ -8719,11 +8924,31 @@
         <v/>
       </c>
       <c r="G77" s="4">
-        <f>(D77-C77*$B$5)*$B$15*F77-B77*$B$28-$B$16*$B$9*F77</f>
+        <f>(D77-C77*$B$5)*$B$15*F77-B77*$B$28-I77*B77*$B$9*F77</f>
         <v/>
       </c>
       <c r="H77" s="4">
-        <f>(D77-C77*$B$5)*$C$15*F77-B77*($C$9/$B$9)*$B$28-$B$16*$C$9*F77</f>
+        <f>(D77-C77*$B$5)*$C$15*F77-B77*($C$9/$B$9)*$B$28-I77*B77*$C$9*F77</f>
+        <v/>
+      </c>
+      <c r="I77">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J77" s="4">
+        <f>D77*$B$15-C77*$B$5*$B$15-B77*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K77" s="4">
+        <f>G77-$B$17*MAX(0,J77)*F77</f>
+        <v/>
+      </c>
+      <c r="L77" s="4">
+        <f>D77*$C$15-C77*$B$5*$C$15-B77*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M77" s="4">
+        <f>H77-$B$17*MAX(0,L77)*F77</f>
         <v/>
       </c>
     </row>
@@ -8750,11 +8975,31 @@
         <v/>
       </c>
       <c r="G78" s="4">
-        <f>(D78-C78*$B$5)*$B$15*F78-B78*$B$28-$B$16*$B$9*F78</f>
+        <f>(D78-C78*$B$5)*$B$15*F78-B78*$B$28-I78*B78*$B$9*F78</f>
         <v/>
       </c>
       <c r="H78" s="4">
-        <f>(D78-C78*$B$5)*$C$15*F78-B78*($C$9/$B$9)*$B$28-$B$16*$C$9*F78</f>
+        <f>(D78-C78*$B$5)*$C$15*F78-B78*($C$9/$B$9)*$B$28-I78*B78*$C$9*F78</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J78" s="4">
+        <f>D78*$B$15-C78*$B$5*$B$15-B78*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K78" s="4">
+        <f>G78-$B$17*MAX(0,J78)*F78</f>
+        <v/>
+      </c>
+      <c r="L78" s="4">
+        <f>D78*$C$15-C78*$B$5*$C$15-B78*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M78" s="4">
+        <f>H78-$B$17*MAX(0,L78)*F78</f>
         <v/>
       </c>
     </row>
@@ -8781,11 +9026,31 @@
         <v/>
       </c>
       <c r="G79" s="4">
-        <f>(D79-C79*$B$5)*$B$15*F79-B79*$B$28-$B$16*$B$9*F79</f>
+        <f>(D79-C79*$B$5)*$B$15*F79-B79*$B$28-I79*B79*$B$9*F79</f>
         <v/>
       </c>
       <c r="H79" s="4">
-        <f>(D79-C79*$B$5)*$C$15*F79-B79*($C$9/$B$9)*$B$28-$B$16*$C$9*F79</f>
+        <f>(D79-C79*$B$5)*$C$15*F79-B79*($C$9/$B$9)*$B$28-I79*B79*$C$9*F79</f>
+        <v/>
+      </c>
+      <c r="I79">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J79" s="4">
+        <f>D79*$B$15-C79*$B$5*$B$15-B79*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K79" s="4">
+        <f>G79-$B$17*MAX(0,J79)*F79</f>
+        <v/>
+      </c>
+      <c r="L79" s="4">
+        <f>D79*$C$15-C79*$B$5*$C$15-B79*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M79" s="4">
+        <f>H79-$B$17*MAX(0,L79)*F79</f>
         <v/>
       </c>
     </row>
@@ -8812,11 +9077,31 @@
         <v/>
       </c>
       <c r="G80" s="4">
-        <f>(D80-C80*$B$5)*$B$15*F80-B80*$B$28-$B$16*$B$9*F80</f>
+        <f>(D80-C80*$B$5)*$B$15*F80-B80*$B$28-I80*B80*$B$9*F80</f>
         <v/>
       </c>
       <c r="H80" s="4">
-        <f>(D80-C80*$B$5)*$C$15*F80-B80*($C$9/$B$9)*$B$28-$B$16*$C$9*F80</f>
+        <f>(D80-C80*$B$5)*$C$15*F80-B80*($C$9/$B$9)*$B$28-I80*B80*$C$9*F80</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J80" s="4">
+        <f>D80*$B$15-C80*$B$5*$B$15-B80*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K80" s="4">
+        <f>G80-$B$17*MAX(0,J80)*F80</f>
+        <v/>
+      </c>
+      <c r="L80" s="4">
+        <f>D80*$C$15-C80*$B$5*$C$15-B80*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M80" s="4">
+        <f>H80-$B$17*MAX(0,L80)*F80</f>
         <v/>
       </c>
     </row>
@@ -8843,11 +9128,31 @@
         <v/>
       </c>
       <c r="G81" s="4">
-        <f>(D81-C81*$B$5)*$B$15*F81-B81*$B$28-$B$16*$B$9*F81</f>
+        <f>(D81-C81*$B$5)*$B$15*F81-B81*$B$28-I81*B81*$B$9*F81</f>
         <v/>
       </c>
       <c r="H81" s="4">
-        <f>(D81-C81*$B$5)*$C$15*F81-B81*($C$9/$B$9)*$B$28-$B$16*$C$9*F81</f>
+        <f>(D81-C81*$B$5)*$C$15*F81-B81*($C$9/$B$9)*$B$28-I81*B81*$C$9*F81</f>
+        <v/>
+      </c>
+      <c r="I81">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J81" s="4">
+        <f>D81*$B$15-C81*$B$5*$B$15-B81*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K81" s="4">
+        <f>G81-$B$17*MAX(0,J81)*F81</f>
+        <v/>
+      </c>
+      <c r="L81" s="4">
+        <f>D81*$C$15-C81*$B$5*$C$15-B81*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M81" s="4">
+        <f>H81-$B$17*MAX(0,L81)*F81</f>
         <v/>
       </c>
     </row>
@@ -8874,11 +9179,31 @@
         <v/>
       </c>
       <c r="G82" s="4">
-        <f>(D82-C82*$B$5)*$B$15*F82-B82*$B$28-$B$16*$B$9*F82</f>
+        <f>(D82-C82*$B$5)*$B$15*F82-B82*$B$28-I82*B82*$B$9*F82</f>
         <v/>
       </c>
       <c r="H82" s="4">
-        <f>(D82-C82*$B$5)*$C$15*F82-B82*($C$9/$B$9)*$B$28-$B$16*$C$9*F82</f>
+        <f>(D82-C82*$B$5)*$C$15*F82-B82*($C$9/$B$9)*$B$28-I82*B82*$C$9*F82</f>
+        <v/>
+      </c>
+      <c r="I82">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J82" s="4">
+        <f>D82*$B$15-C82*$B$5*$B$15-B82*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K82" s="4">
+        <f>G82-$B$17*MAX(0,J82)*F82</f>
+        <v/>
+      </c>
+      <c r="L82" s="4">
+        <f>D82*$C$15-C82*$B$5*$C$15-B82*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M82" s="4">
+        <f>H82-$B$17*MAX(0,L82)*F82</f>
         <v/>
       </c>
     </row>
@@ -8905,11 +9230,31 @@
         <v/>
       </c>
       <c r="G83" s="4">
-        <f>(D83-C83*$B$5)*$B$15*F83-B83*$B$28-$B$16*$B$9*F83</f>
+        <f>(D83-C83*$B$5)*$B$15*F83-B83*$B$28-I83*B83*$B$9*F83</f>
         <v/>
       </c>
       <c r="H83" s="4">
-        <f>(D83-C83*$B$5)*$C$15*F83-B83*($C$9/$B$9)*$B$28-$B$16*$C$9*F83</f>
+        <f>(D83-C83*$B$5)*$C$15*F83-B83*($C$9/$B$9)*$B$28-I83*B83*$C$9*F83</f>
+        <v/>
+      </c>
+      <c r="I83">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J83" s="4">
+        <f>D83*$B$15-C83*$B$5*$B$15-B83*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K83" s="4">
+        <f>G83-$B$17*MAX(0,J83)*F83</f>
+        <v/>
+      </c>
+      <c r="L83" s="4">
+        <f>D83*$C$15-C83*$B$5*$C$15-B83*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M83" s="4">
+        <f>H83-$B$17*MAX(0,L83)*F83</f>
         <v/>
       </c>
     </row>
@@ -8936,11 +9281,31 @@
         <v/>
       </c>
       <c r="G84" s="4">
-        <f>(D84-C84*$B$5)*$B$15*F84-B84*$B$28-$B$16*$B$9*F84</f>
+        <f>(D84-C84*$B$5)*$B$15*F84-B84*$B$28-I84*B84*$B$9*F84</f>
         <v/>
       </c>
       <c r="H84" s="4">
-        <f>(D84-C84*$B$5)*$C$15*F84-B84*($C$9/$B$9)*$B$28-$B$16*$C$9*F84</f>
+        <f>(D84-C84*$B$5)*$C$15*F84-B84*($C$9/$B$9)*$B$28-I84*B84*$C$9*F84</f>
+        <v/>
+      </c>
+      <c r="I84">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J84" s="4">
+        <f>D84*$B$15-C84*$B$5*$B$15-B84*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K84" s="4">
+        <f>G84-$B$17*MAX(0,J84)*F84</f>
+        <v/>
+      </c>
+      <c r="L84" s="4">
+        <f>D84*$C$15-C84*$B$5*$C$15-B84*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M84" s="4">
+        <f>H84-$B$17*MAX(0,L84)*F84</f>
         <v/>
       </c>
     </row>
@@ -8967,11 +9332,31 @@
         <v/>
       </c>
       <c r="G85" s="4">
-        <f>(D85-C85*$B$5)*$B$15*F85-B85*$B$28-$B$16*$B$9*F85</f>
+        <f>(D85-C85*$B$5)*$B$15*F85-B85*$B$28-I85*B85*$B$9*F85</f>
         <v/>
       </c>
       <c r="H85" s="4">
-        <f>(D85-C85*$B$5)*$C$15*F85-B85*($C$9/$B$9)*$B$28-$B$16*$C$9*F85</f>
+        <f>(D85-C85*$B$5)*$C$15*F85-B85*($C$9/$B$9)*$B$28-I85*B85*$C$9*F85</f>
+        <v/>
+      </c>
+      <c r="I85">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J85" s="4">
+        <f>D85*$B$15-C85*$B$5*$B$15-B85*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K85" s="4">
+        <f>G85-$B$17*MAX(0,J85)*F85</f>
+        <v/>
+      </c>
+      <c r="L85" s="4">
+        <f>D85*$C$15-C85*$B$5*$C$15-B85*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M85" s="4">
+        <f>H85-$B$17*MAX(0,L85)*F85</f>
         <v/>
       </c>
     </row>
@@ -8998,11 +9383,31 @@
         <v/>
       </c>
       <c r="G86" s="4">
-        <f>(D86-C86*$B$5)*$B$15*F86-B86*$B$28-$B$16*$B$9*F86</f>
+        <f>(D86-C86*$B$5)*$B$15*F86-B86*$B$28-I86*B86*$B$9*F86</f>
         <v/>
       </c>
       <c r="H86" s="4">
-        <f>(D86-C86*$B$5)*$C$15*F86-B86*($C$9/$B$9)*$B$28-$B$16*$C$9*F86</f>
+        <f>(D86-C86*$B$5)*$C$15*F86-B86*($C$9/$B$9)*$B$28-I86*B86*$C$9*F86</f>
+        <v/>
+      </c>
+      <c r="I86">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J86" s="4">
+        <f>D86*$B$15-C86*$B$5*$B$15-B86*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K86" s="4">
+        <f>G86-$B$17*MAX(0,J86)*F86</f>
+        <v/>
+      </c>
+      <c r="L86" s="4">
+        <f>D86*$C$15-C86*$B$5*$C$15-B86*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M86" s="4">
+        <f>H86-$B$17*MAX(0,L86)*F86</f>
         <v/>
       </c>
     </row>
@@ -9029,11 +9434,31 @@
         <v/>
       </c>
       <c r="G87" s="4">
-        <f>(D87-C87*$B$5)*$B$15*F87-B87*$B$28-$B$16*$B$9*F87</f>
+        <f>(D87-C87*$B$5)*$B$15*F87-B87*$B$28-I87*B87*$B$9*F87</f>
         <v/>
       </c>
       <c r="H87" s="4">
-        <f>(D87-C87*$B$5)*$C$15*F87-B87*($C$9/$B$9)*$B$28-$B$16*$C$9*F87</f>
+        <f>(D87-C87*$B$5)*$C$15*F87-B87*($C$9/$B$9)*$B$28-I87*B87*$C$9*F87</f>
+        <v/>
+      </c>
+      <c r="I87">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J87" s="4">
+        <f>D87*$B$15-C87*$B$5*$B$15-B87*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K87" s="4">
+        <f>G87-$B$17*MAX(0,J87)*F87</f>
+        <v/>
+      </c>
+      <c r="L87" s="4">
+        <f>D87*$C$15-C87*$B$5*$C$15-B87*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M87" s="4">
+        <f>H87-$B$17*MAX(0,L87)*F87</f>
         <v/>
       </c>
     </row>
@@ -9060,11 +9485,31 @@
         <v/>
       </c>
       <c r="G88" s="4">
-        <f>(D88-C88*$B$5)*$B$15*F88-B88*$B$28-$B$16*$B$9*F88</f>
+        <f>(D88-C88*$B$5)*$B$15*F88-B88*$B$28-I88*B88*$B$9*F88</f>
         <v/>
       </c>
       <c r="H88" s="4">
-        <f>(D88-C88*$B$5)*$C$15*F88-B88*($C$9/$B$9)*$B$28-$B$16*$C$9*F88</f>
+        <f>(D88-C88*$B$5)*$C$15*F88-B88*($C$9/$B$9)*$B$28-I88*B88*$C$9*F88</f>
+        <v/>
+      </c>
+      <c r="I88">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J88" s="4">
+        <f>D88*$B$15-C88*$B$5*$B$15-B88*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K88" s="4">
+        <f>G88-$B$17*MAX(0,J88)*F88</f>
+        <v/>
+      </c>
+      <c r="L88" s="4">
+        <f>D88*$C$15-C88*$B$5*$C$15-B88*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M88" s="4">
+        <f>H88-$B$17*MAX(0,L88)*F88</f>
         <v/>
       </c>
     </row>
@@ -9091,11 +9536,31 @@
         <v/>
       </c>
       <c r="G89" s="4">
-        <f>(D89-C89*$B$5)*$B$15*F89-B89*$B$28-$B$16*$B$9*F89</f>
+        <f>(D89-C89*$B$5)*$B$15*F89-B89*$B$28-I89*B89*$B$9*F89</f>
         <v/>
       </c>
       <c r="H89" s="4">
-        <f>(D89-C89*$B$5)*$C$15*F89-B89*($C$9/$B$9)*$B$28-$B$16*$C$9*F89</f>
+        <f>(D89-C89*$B$5)*$C$15*F89-B89*($C$9/$B$9)*$B$28-I89*B89*$C$9*F89</f>
+        <v/>
+      </c>
+      <c r="I89">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J89" s="4">
+        <f>D89*$B$15-C89*$B$5*$B$15-B89*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K89" s="4">
+        <f>G89-$B$17*MAX(0,J89)*F89</f>
+        <v/>
+      </c>
+      <c r="L89" s="4">
+        <f>D89*$C$15-C89*$B$5*$C$15-B89*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M89" s="4">
+        <f>H89-$B$17*MAX(0,L89)*F89</f>
         <v/>
       </c>
     </row>
@@ -9122,11 +9587,31 @@
         <v/>
       </c>
       <c r="G90" s="4">
-        <f>(D90-C90*$B$5)*$B$15*F90-B90*$B$28-$B$16*$B$9*F90</f>
+        <f>(D90-C90*$B$5)*$B$15*F90-B90*$B$28-I90*B90*$B$9*F90</f>
         <v/>
       </c>
       <c r="H90" s="4">
-        <f>(D90-C90*$B$5)*$C$15*F90-B90*($C$9/$B$9)*$B$28-$B$16*$C$9*F90</f>
+        <f>(D90-C90*$B$5)*$C$15*F90-B90*($C$9/$B$9)*$B$28-I90*B90*$C$9*F90</f>
+        <v/>
+      </c>
+      <c r="I90">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J90" s="4">
+        <f>D90*$B$15-C90*$B$5*$B$15-B90*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K90" s="4">
+        <f>G90-$B$17*MAX(0,J90)*F90</f>
+        <v/>
+      </c>
+      <c r="L90" s="4">
+        <f>D90*$C$15-C90*$B$5*$C$15-B90*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M90" s="4">
+        <f>H90-$B$17*MAX(0,L90)*F90</f>
         <v/>
       </c>
     </row>
@@ -9153,11 +9638,31 @@
         <v/>
       </c>
       <c r="G91" s="4">
-        <f>(D91-C91*$B$5)*$B$15*F91-B91*$B$28-$B$16*$B$9*F91</f>
+        <f>(D91-C91*$B$5)*$B$15*F91-B91*$B$28-I91*B91*$B$9*F91</f>
         <v/>
       </c>
       <c r="H91" s="4">
-        <f>(D91-C91*$B$5)*$C$15*F91-B91*($C$9/$B$9)*$B$28-$B$16*$C$9*F91</f>
+        <f>(D91-C91*$B$5)*$C$15*F91-B91*($C$9/$B$9)*$B$28-I91*B91*$C$9*F91</f>
+        <v/>
+      </c>
+      <c r="I91">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J91" s="4">
+        <f>D91*$B$15-C91*$B$5*$B$15-B91*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K91" s="4">
+        <f>G91-$B$17*MAX(0,J91)*F91</f>
+        <v/>
+      </c>
+      <c r="L91" s="4">
+        <f>D91*$C$15-C91*$B$5*$C$15-B91*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M91" s="4">
+        <f>H91-$B$17*MAX(0,L91)*F91</f>
         <v/>
       </c>
     </row>
@@ -9184,11 +9689,31 @@
         <v/>
       </c>
       <c r="G92" s="4">
-        <f>(D92-C92*$B$5)*$B$15*F92-B92*$B$28-$B$16*$B$9*F92</f>
+        <f>(D92-C92*$B$5)*$B$15*F92-B92*$B$28-I92*B92*$B$9*F92</f>
         <v/>
       </c>
       <c r="H92" s="4">
-        <f>(D92-C92*$B$5)*$C$15*F92-B92*($C$9/$B$9)*$B$28-$B$16*$C$9*F92</f>
+        <f>(D92-C92*$B$5)*$C$15*F92-B92*($C$9/$B$9)*$B$28-I92*B92*$C$9*F92</f>
+        <v/>
+      </c>
+      <c r="I92">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J92" s="4">
+        <f>D92*$B$15-C92*$B$5*$B$15-B92*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K92" s="4">
+        <f>G92-$B$17*MAX(0,J92)*F92</f>
+        <v/>
+      </c>
+      <c r="L92" s="4">
+        <f>D92*$C$15-C92*$B$5*$C$15-B92*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M92" s="4">
+        <f>H92-$B$17*MAX(0,L92)*F92</f>
         <v/>
       </c>
     </row>
@@ -9215,26 +9740,113 @@
         <v/>
       </c>
       <c r="G93" s="4">
-        <f>(D93-C93*$B$5)*$B$15*F93-B93*$B$28-$B$16*$B$9*F93</f>
+        <f>(D93-C93*$B$5)*$B$15*F93-B93*$B$28-I93*B93*$B$9*F93</f>
         <v/>
       </c>
       <c r="H93" s="4">
-        <f>(D93-C93*$B$5)*$C$15*F93-B93*($C$9/$B$9)*$B$28-$B$16*$C$9*F93</f>
+        <f>(D93-C93*$B$5)*$C$15*F93-B93*($C$9/$B$9)*$B$28-I93*B93*$C$9*F93</f>
+        <v/>
+      </c>
+      <c r="I93">
+        <f>$B$16</f>
+        <v/>
+      </c>
+      <c r="J93" s="4">
+        <f>D93*$B$15-C93*$B$5*$B$15-B93*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K93" s="4">
+        <f>G93-$B$17*MAX(0,J93)*F93</f>
+        <v/>
+      </c>
+      <c r="L93" s="4">
+        <f>D93*$C$15-C93*$B$5*$C$15-B93*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M93" s="4">
+        <f>H93-$B$17*MAX(0,L93)*F93</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Check: base row less the primary NPV above (should be about 0)</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n"/>
+          <t>replacement capex at HK depreciation proxy (sensitivity, not sourced)</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <f>SUMPRODUCT($B$41:$B$63*($A$41:$A$63&gt;=$B$8+E94)*($A$41:$A$63&lt;$B$8+E94+$B$7))</f>
+        <v/>
+      </c>
       <c r="G94" s="4">
+        <f>(D94-C94*$B$5)*$B$15*F94-B94*$B$28-I94*B94*$B$9*F94</f>
+        <v/>
+      </c>
+      <c r="H94" s="4">
+        <f>(D94-C94*$B$5)*$C$15*F94-B94*($C$9/$B$9)*$B$28-I94*B94*$C$9*F94</f>
+        <v/>
+      </c>
+      <c r="I94">
+        <f>Inputs!$C$168</f>
+        <v/>
+      </c>
+      <c r="J94" s="4">
+        <f>D94*$B$15-C94*$B$5*$B$15-B94*$B$9/$B$18</f>
+        <v/>
+      </c>
+      <c r="K94" s="4">
+        <f>G94-$B$17*MAX(0,J94)*F94</f>
+        <v/>
+      </c>
+      <c r="L94" s="4">
+        <f>D94*$C$15-C94*$B$5*$C$15-B94*$C$9/$C$18</f>
+        <v/>
+      </c>
+      <c r="M94" s="4">
+        <f>H94-$B$17*MAX(0,L94)*F94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Check: base pre-tax NPV less B21 (about 0)</t>
+        </is>
+      </c>
+      <c r="G96" s="4">
         <f>G68-B21</f>
         <v/>
       </c>
-      <c r="H94" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Check: base after-tax NPV less B22 (about 0)</t>
+        </is>
+      </c>
+      <c r="K97" s="4">
+        <f>K68-B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tax note: the annual ledger uses cumulative taxable income with unlimited carry-forward. That is exact where taxable income has one sign over the operating years, as in the base and every sensitivity case. Replacement capex is not deductible for tax (conservative, flagged). Loss vintages with five-year expiry are not modelled.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -6376,11 +6376,11 @@
         </is>
       </c>
       <c r="B22" s="4">
-        <f>SUM(R41:R63)</f>
+        <f>IF($B$18&lt;$B$7,"not valid: tax depreciation ends before operations",SUM(R41:R63))</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>IF(C29&lt;=0,C21,"tax needed: not computed")</f>
+        <f>IF(C18&lt;C7,"not valid: tax depreciation ends before operations",IF(C29&lt;=0,C21,"tax needed: not computed"))</f>
         <v/>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>IRR(Q41:Q63,-0.1)</f>
+        <f>IF($B$18&lt;$B$7,"not valid",IRR(Q41:Q63,-0.1))</f>
         <v/>
       </c>
       <c r="C23" t="inlineStr">
@@ -6490,6 +6490,21 @@
       </c>
       <c r="C30" s="4">
         <f>C21--259.4197777456208</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tax validity guard: after-tax outputs are shown only when tax depreciation covers the operating life</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>IF(B18&lt;B7,"CHECK: tax depreciation ends before operations; after-tax outputs are not valid","OK: tax depreciation covers the operating life")</f>
+        <v/>
+      </c>
+      <c r="C32">
+        <f>IF(C18&lt;C7,"CHECK: tax depreciation ends before operations; after-tax outputs are not valid","OK: tax depreciation covers the operating life")</f>
         <v/>
       </c>
     </row>
@@ -8481,7 +8496,7 @@
         <v/>
       </c>
       <c r="K68" s="4">
-        <f>G68-$B$17*MAX(0,J68)*F68</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G68-$B$17*MAX(0,J68)*F68)</f>
         <v/>
       </c>
       <c r="L68" s="4">
@@ -8489,7 +8504,7 @@
         <v/>
       </c>
       <c r="M68" s="4">
-        <f>H68-$B$17*MAX(0,L68)*F68</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H68-$B$17*MAX(0,L68)*F68)</f>
         <v/>
       </c>
     </row>
@@ -8532,7 +8547,7 @@
         <v/>
       </c>
       <c r="K69" s="4">
-        <f>G69-$B$17*MAX(0,J69)*F69</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G69-$B$17*MAX(0,J69)*F69)</f>
         <v/>
       </c>
       <c r="L69" s="4">
@@ -8540,7 +8555,7 @@
         <v/>
       </c>
       <c r="M69" s="4">
-        <f>H69-$B$17*MAX(0,L69)*F69</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H69-$B$17*MAX(0,L69)*F69)</f>
         <v/>
       </c>
     </row>
@@ -8583,7 +8598,7 @@
         <v/>
       </c>
       <c r="K70" s="4">
-        <f>G70-$B$17*MAX(0,J70)*F70</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G70-$B$17*MAX(0,J70)*F70)</f>
         <v/>
       </c>
       <c r="L70" s="4">
@@ -8591,7 +8606,7 @@
         <v/>
       </c>
       <c r="M70" s="4">
-        <f>H70-$B$17*MAX(0,L70)*F70</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H70-$B$17*MAX(0,L70)*F70)</f>
         <v/>
       </c>
     </row>
@@ -8634,7 +8649,7 @@
         <v/>
       </c>
       <c r="K71" s="4">
-        <f>G71-$B$17*MAX(0,J71)*F71</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G71-$B$17*MAX(0,J71)*F71)</f>
         <v/>
       </c>
       <c r="L71" s="4">
@@ -8642,7 +8657,7 @@
         <v/>
       </c>
       <c r="M71" s="4">
-        <f>H71-$B$17*MAX(0,L71)*F71</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H71-$B$17*MAX(0,L71)*F71)</f>
         <v/>
       </c>
     </row>
@@ -8685,7 +8700,7 @@
         <v/>
       </c>
       <c r="K72" s="4">
-        <f>G72-$B$17*MAX(0,J72)*F72</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G72-$B$17*MAX(0,J72)*F72)</f>
         <v/>
       </c>
       <c r="L72" s="4">
@@ -8693,7 +8708,7 @@
         <v/>
       </c>
       <c r="M72" s="4">
-        <f>H72-$B$17*MAX(0,L72)*F72</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H72-$B$17*MAX(0,L72)*F72)</f>
         <v/>
       </c>
     </row>
@@ -8736,7 +8751,7 @@
         <v/>
       </c>
       <c r="K73" s="4">
-        <f>G73-$B$17*MAX(0,J73)*F73</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G73-$B$17*MAX(0,J73)*F73)</f>
         <v/>
       </c>
       <c r="L73" s="4">
@@ -8744,7 +8759,7 @@
         <v/>
       </c>
       <c r="M73" s="4">
-        <f>H73-$B$17*MAX(0,L73)*F73</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H73-$B$17*MAX(0,L73)*F73)</f>
         <v/>
       </c>
     </row>
@@ -8787,7 +8802,7 @@
         <v/>
       </c>
       <c r="K74" s="4">
-        <f>G74-$B$17*MAX(0,J74)*F74</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G74-$B$17*MAX(0,J74)*F74)</f>
         <v/>
       </c>
       <c r="L74" s="4">
@@ -8795,7 +8810,7 @@
         <v/>
       </c>
       <c r="M74" s="4">
-        <f>H74-$B$17*MAX(0,L74)*F74</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H74-$B$17*MAX(0,L74)*F74)</f>
         <v/>
       </c>
     </row>
@@ -8838,7 +8853,7 @@
         <v/>
       </c>
       <c r="K75" s="4">
-        <f>G75-$B$17*MAX(0,J75)*F75</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G75-$B$17*MAX(0,J75)*F75)</f>
         <v/>
       </c>
       <c r="L75" s="4">
@@ -8846,7 +8861,7 @@
         <v/>
       </c>
       <c r="M75" s="4">
-        <f>H75-$B$17*MAX(0,L75)*F75</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H75-$B$17*MAX(0,L75)*F75)</f>
         <v/>
       </c>
     </row>
@@ -8889,7 +8904,7 @@
         <v/>
       </c>
       <c r="K76" s="4">
-        <f>G76-$B$17*MAX(0,J76)*F76</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G76-$B$17*MAX(0,J76)*F76)</f>
         <v/>
       </c>
       <c r="L76" s="4">
@@ -8897,7 +8912,7 @@
         <v/>
       </c>
       <c r="M76" s="4">
-        <f>H76-$B$17*MAX(0,L76)*F76</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H76-$B$17*MAX(0,L76)*F76)</f>
         <v/>
       </c>
     </row>
@@ -8940,7 +8955,7 @@
         <v/>
       </c>
       <c r="K77" s="4">
-        <f>G77-$B$17*MAX(0,J77)*F77</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G77-$B$17*MAX(0,J77)*F77)</f>
         <v/>
       </c>
       <c r="L77" s="4">
@@ -8948,7 +8963,7 @@
         <v/>
       </c>
       <c r="M77" s="4">
-        <f>H77-$B$17*MAX(0,L77)*F77</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H77-$B$17*MAX(0,L77)*F77)</f>
         <v/>
       </c>
     </row>
@@ -8991,7 +9006,7 @@
         <v/>
       </c>
       <c r="K78" s="4">
-        <f>G78-$B$17*MAX(0,J78)*F78</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G78-$B$17*MAX(0,J78)*F78)</f>
         <v/>
       </c>
       <c r="L78" s="4">
@@ -8999,7 +9014,7 @@
         <v/>
       </c>
       <c r="M78" s="4">
-        <f>H78-$B$17*MAX(0,L78)*F78</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H78-$B$17*MAX(0,L78)*F78)</f>
         <v/>
       </c>
     </row>
@@ -9042,7 +9057,7 @@
         <v/>
       </c>
       <c r="K79" s="4">
-        <f>G79-$B$17*MAX(0,J79)*F79</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G79-$B$17*MAX(0,J79)*F79)</f>
         <v/>
       </c>
       <c r="L79" s="4">
@@ -9050,7 +9065,7 @@
         <v/>
       </c>
       <c r="M79" s="4">
-        <f>H79-$B$17*MAX(0,L79)*F79</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H79-$B$17*MAX(0,L79)*F79)</f>
         <v/>
       </c>
     </row>
@@ -9093,7 +9108,7 @@
         <v/>
       </c>
       <c r="K80" s="4">
-        <f>G80-$B$17*MAX(0,J80)*F80</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G80-$B$17*MAX(0,J80)*F80)</f>
         <v/>
       </c>
       <c r="L80" s="4">
@@ -9101,7 +9116,7 @@
         <v/>
       </c>
       <c r="M80" s="4">
-        <f>H80-$B$17*MAX(0,L80)*F80</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H80-$B$17*MAX(0,L80)*F80)</f>
         <v/>
       </c>
     </row>
@@ -9144,7 +9159,7 @@
         <v/>
       </c>
       <c r="K81" s="4">
-        <f>G81-$B$17*MAX(0,J81)*F81</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G81-$B$17*MAX(0,J81)*F81)</f>
         <v/>
       </c>
       <c r="L81" s="4">
@@ -9152,7 +9167,7 @@
         <v/>
       </c>
       <c r="M81" s="4">
-        <f>H81-$B$17*MAX(0,L81)*F81</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H81-$B$17*MAX(0,L81)*F81)</f>
         <v/>
       </c>
     </row>
@@ -9195,7 +9210,7 @@
         <v/>
       </c>
       <c r="K82" s="4">
-        <f>G82-$B$17*MAX(0,J82)*F82</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G82-$B$17*MAX(0,J82)*F82)</f>
         <v/>
       </c>
       <c r="L82" s="4">
@@ -9203,7 +9218,7 @@
         <v/>
       </c>
       <c r="M82" s="4">
-        <f>H82-$B$17*MAX(0,L82)*F82</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H82-$B$17*MAX(0,L82)*F82)</f>
         <v/>
       </c>
     </row>
@@ -9246,7 +9261,7 @@
         <v/>
       </c>
       <c r="K83" s="4">
-        <f>G83-$B$17*MAX(0,J83)*F83</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G83-$B$17*MAX(0,J83)*F83)</f>
         <v/>
       </c>
       <c r="L83" s="4">
@@ -9254,7 +9269,7 @@
         <v/>
       </c>
       <c r="M83" s="4">
-        <f>H83-$B$17*MAX(0,L83)*F83</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H83-$B$17*MAX(0,L83)*F83)</f>
         <v/>
       </c>
     </row>
@@ -9297,7 +9312,7 @@
         <v/>
       </c>
       <c r="K84" s="4">
-        <f>G84-$B$17*MAX(0,J84)*F84</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G84-$B$17*MAX(0,J84)*F84)</f>
         <v/>
       </c>
       <c r="L84" s="4">
@@ -9305,7 +9320,7 @@
         <v/>
       </c>
       <c r="M84" s="4">
-        <f>H84-$B$17*MAX(0,L84)*F84</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H84-$B$17*MAX(0,L84)*F84)</f>
         <v/>
       </c>
     </row>
@@ -9348,7 +9363,7 @@
         <v/>
       </c>
       <c r="K85" s="4">
-        <f>G85-$B$17*MAX(0,J85)*F85</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G85-$B$17*MAX(0,J85)*F85)</f>
         <v/>
       </c>
       <c r="L85" s="4">
@@ -9356,7 +9371,7 @@
         <v/>
       </c>
       <c r="M85" s="4">
-        <f>H85-$B$17*MAX(0,L85)*F85</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H85-$B$17*MAX(0,L85)*F85)</f>
         <v/>
       </c>
     </row>
@@ -9399,7 +9414,7 @@
         <v/>
       </c>
       <c r="K86" s="4">
-        <f>G86-$B$17*MAX(0,J86)*F86</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G86-$B$17*MAX(0,J86)*F86)</f>
         <v/>
       </c>
       <c r="L86" s="4">
@@ -9407,7 +9422,7 @@
         <v/>
       </c>
       <c r="M86" s="4">
-        <f>H86-$B$17*MAX(0,L86)*F86</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H86-$B$17*MAX(0,L86)*F86)</f>
         <v/>
       </c>
     </row>
@@ -9450,7 +9465,7 @@
         <v/>
       </c>
       <c r="K87" s="4">
-        <f>G87-$B$17*MAX(0,J87)*F87</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G87-$B$17*MAX(0,J87)*F87)</f>
         <v/>
       </c>
       <c r="L87" s="4">
@@ -9458,7 +9473,7 @@
         <v/>
       </c>
       <c r="M87" s="4">
-        <f>H87-$B$17*MAX(0,L87)*F87</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H87-$B$17*MAX(0,L87)*F87)</f>
         <v/>
       </c>
     </row>
@@ -9501,7 +9516,7 @@
         <v/>
       </c>
       <c r="K88" s="4">
-        <f>G88-$B$17*MAX(0,J88)*F88</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G88-$B$17*MAX(0,J88)*F88)</f>
         <v/>
       </c>
       <c r="L88" s="4">
@@ -9509,7 +9524,7 @@
         <v/>
       </c>
       <c r="M88" s="4">
-        <f>H88-$B$17*MAX(0,L88)*F88</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H88-$B$17*MAX(0,L88)*F88)</f>
         <v/>
       </c>
     </row>
@@ -9552,7 +9567,7 @@
         <v/>
       </c>
       <c r="K89" s="4">
-        <f>G89-$B$17*MAX(0,J89)*F89</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G89-$B$17*MAX(0,J89)*F89)</f>
         <v/>
       </c>
       <c r="L89" s="4">
@@ -9560,7 +9575,7 @@
         <v/>
       </c>
       <c r="M89" s="4">
-        <f>H89-$B$17*MAX(0,L89)*F89</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H89-$B$17*MAX(0,L89)*F89)</f>
         <v/>
       </c>
     </row>
@@ -9603,7 +9618,7 @@
         <v/>
       </c>
       <c r="K90" s="4">
-        <f>G90-$B$17*MAX(0,J90)*F90</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G90-$B$17*MAX(0,J90)*F90)</f>
         <v/>
       </c>
       <c r="L90" s="4">
@@ -9611,7 +9626,7 @@
         <v/>
       </c>
       <c r="M90" s="4">
-        <f>H90-$B$17*MAX(0,L90)*F90</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H90-$B$17*MAX(0,L90)*F90)</f>
         <v/>
       </c>
     </row>
@@ -9654,7 +9669,7 @@
         <v/>
       </c>
       <c r="K91" s="4">
-        <f>G91-$B$17*MAX(0,J91)*F91</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G91-$B$17*MAX(0,J91)*F91)</f>
         <v/>
       </c>
       <c r="L91" s="4">
@@ -9662,7 +9677,7 @@
         <v/>
       </c>
       <c r="M91" s="4">
-        <f>H91-$B$17*MAX(0,L91)*F91</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H91-$B$17*MAX(0,L91)*F91)</f>
         <v/>
       </c>
     </row>
@@ -9705,7 +9720,7 @@
         <v/>
       </c>
       <c r="K92" s="4">
-        <f>G92-$B$17*MAX(0,J92)*F92</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G92-$B$17*MAX(0,J92)*F92)</f>
         <v/>
       </c>
       <c r="L92" s="4">
@@ -9713,7 +9728,7 @@
         <v/>
       </c>
       <c r="M92" s="4">
-        <f>H92-$B$17*MAX(0,L92)*F92</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H92-$B$17*MAX(0,L92)*F92)</f>
         <v/>
       </c>
     </row>
@@ -9756,7 +9771,7 @@
         <v/>
       </c>
       <c r="K93" s="4">
-        <f>G93-$B$17*MAX(0,J93)*F93</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G93-$B$17*MAX(0,J93)*F93)</f>
         <v/>
       </c>
       <c r="L93" s="4">
@@ -9764,7 +9779,7 @@
         <v/>
       </c>
       <c r="M93" s="4">
-        <f>H93-$B$17*MAX(0,L93)*F93</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H93-$B$17*MAX(0,L93)*F93)</f>
         <v/>
       </c>
     </row>
@@ -9807,7 +9822,7 @@
         <v/>
       </c>
       <c r="K94" s="4">
-        <f>G94-$B$17*MAX(0,J94)*F94</f>
+        <f>IF($B$18&lt;$B$7,"not valid",G94-$B$17*MAX(0,J94)*F94)</f>
         <v/>
       </c>
       <c r="L94" s="4">
@@ -9815,7 +9830,7 @@
         <v/>
       </c>
       <c r="M94" s="4">
-        <f>H94-$B$17*MAX(0,L94)*F94</f>
+        <f>IF($C$18&lt;$C$7,"not valid",H94-$B$17*MAX(0,L94)*F94)</f>
         <v/>
       </c>
     </row>
@@ -9837,14 +9852,14 @@
         </is>
       </c>
       <c r="K97" s="4">
-        <f>K68-B22</f>
+        <f>IF(ISNUMBER(B22),K68-B22,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tax note: the annual ledger uses cumulative taxable income with unlimited carry-forward. That is exact where taxable income has one sign over the operating years, as in the base and every sensitivity case. Replacement capex is not deductible for tax (conservative, flagged). Loss vintages with five-year expiry are not modelled.</t>
+          <t>Tax limitations, kept visible: (1) the ledger uses cumulative taxable income with unlimited loss carry-forward; the Thai rule expires losses after five years, so an expiry-aware schedule can give a different tax; (2) replacement capex is not deductible for tax (conservative); (3) tax depreciation is assumed to run over the operating life. Row 32 flags a breach of (3), and the after-tax outputs then read not valid.</t>
         </is>
       </c>
     </row>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -6065,7 +6065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -6106,7 +6106,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Limits: the cash basis is a proxy from HK Disneyland FY2025 accounts. The replacement capex base is zero (no source). The tax loss rule is a proxy. Working capital, the capex and revenue boundary of the sports complex, and the public-funding flows are not in the operator ledger.</t>
+          <t>Limits: the cash basis is a proxy from HK Disneyland FY2025 accounts. The replacement capex base is zero (no source). The tax loss rule is a proxy. Working capital, the capex and revenue boundary of the sports complex, and the public-funding flows are not in the operator ledger. The cash basis and the park-only boundary are decisions by kamolpeen (21 October 2026), with the same weight as team approval.</t>
         </is>
       </c>
     </row>
@@ -9861,6 +9861,582 @@
         <is>
           <t>Tax limitations, kept visible: (1) the ledger uses cumulative taxable income with unlimited loss carry-forward; the Thai rule expires losses after five years, so an expiry-aware schedule can give a different tax; (2) replacement capex is not deductible for tax (conservative); (3) tax depreciation is assumed to run over the operating life. Row 32 flags a breach of (3), and the after-tax outputs then read not valid.</t>
         </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Scenario table (formula-based, pre-tax, closed form). Each row changes only the stated inputs. Row 103 must equal B21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Life (years)</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>On-site income (1 = yes)</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Replacement share</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>Total revenue (THB bn a year)</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Annuity factor AF</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>PV of capex (THB bn)</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>NPV pre-tax (THB bn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Base: primary, ticket-only revenue, 20-year life</t>
+        </is>
+      </c>
+      <c r="B103" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C103">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F103" s="4">
+        <f>$B$15+D103*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G103" s="3">
+        <f>(1+B103)^(-$B$8)*(1-(1+B103)^(-C103))/(1-1/(1+B103))</f>
+        <v/>
+      </c>
+      <c r="H103" s="4">
+        <f>($B$9/$B$8)*(1-(1+B103)^(-$B$8))/(1-1/(1+B103))</f>
+        <v/>
+      </c>
+      <c r="I103" s="4">
+        <f>(F103*(1-$B$5)-E103*$B$9)*G103-H103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>On-site income at 1,862 THB per operator visit (low-case benchmark), cash ratio on total revenue</t>
+        </is>
+      </c>
+      <c r="B104" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C104">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F104" s="4">
+        <f>$B$15+D104*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G104" s="3">
+        <f>(1+B104)^(-$B$8)*(1-(1+B104)^(-C104))/(1-1/(1+B104))</f>
+        <v/>
+      </c>
+      <c r="H104" s="4">
+        <f>($B$9/$B$8)*(1-(1+B104)^(-$B$8))/(1-1/(1+B104))</f>
+        <v/>
+      </c>
+      <c r="I104" s="4">
+        <f>(F104*(1-$B$5)-E104*$B$9)*G104-H104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Life 30 years</t>
+        </is>
+      </c>
+      <c r="B105" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C105" t="n">
+        <v>30</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F105" s="4">
+        <f>$B$15+D105*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G105" s="3">
+        <f>(1+B105)^(-$B$8)*(1-(1+B105)^(-C105))/(1-1/(1+B105))</f>
+        <v/>
+      </c>
+      <c r="H105" s="4">
+        <f>($B$9/$B$8)*(1-(1+B105)^(-$B$8))/(1-1/(1+B105))</f>
+        <v/>
+      </c>
+      <c r="I105" s="4">
+        <f>(F105*(1-$B$5)-E105*$B$9)*G105-H105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Life 40 years</t>
+        </is>
+      </c>
+      <c r="B106" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C106" t="n">
+        <v>40</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F106" s="4">
+        <f>$B$15+D106*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G106" s="3">
+        <f>(1+B106)^(-$B$8)*(1-(1+B106)^(-C106))/(1-1/(1+B106))</f>
+        <v/>
+      </c>
+      <c r="H106" s="4">
+        <f>($B$9/$B$8)*(1-(1+B106)^(-$B$8))/(1-1/(1+B106))</f>
+        <v/>
+      </c>
+      <c r="I106" s="4">
+        <f>(F106*(1-$B$5)-E106*$B$9)*G106-H106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>WACC 6 percent</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C107">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F107" s="4">
+        <f>$B$15+D107*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G107" s="3">
+        <f>(1+B107)^(-$B$8)*(1-(1+B107)^(-C107))/(1-1/(1+B107))</f>
+        <v/>
+      </c>
+      <c r="H107" s="4">
+        <f>($B$9/$B$8)*(1-(1+B107)^(-$B$8))/(1-1/(1+B107))</f>
+        <v/>
+      </c>
+      <c r="I107" s="4">
+        <f>(F107*(1-$B$5)-E107*$B$9)*G107-H107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>WACC 7 percent (high case)</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C108">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F108" s="4">
+        <f>$B$15+D108*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G108" s="3">
+        <f>(1+B108)^(-$B$8)*(1-(1+B108)^(-C108))/(1-1/(1+B108))</f>
+        <v/>
+      </c>
+      <c r="H108" s="4">
+        <f>($B$9/$B$8)*(1-(1+B108)^(-$B$8))/(1-1/(1+B108))</f>
+        <v/>
+      </c>
+      <c r="I108" s="4">
+        <f>(F108*(1-$B$5)-E108*$B$9)*G108-H108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WACC 10 percent (low case)</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C109">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3">
+        <f>B16</f>
+        <v/>
+      </c>
+      <c r="F109" s="4">
+        <f>$B$15+D109*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G109" s="3">
+        <f>(1+B109)^(-$B$8)*(1-(1+B109)^(-C109))/(1-1/(1+B109))</f>
+        <v/>
+      </c>
+      <c r="H109" s="4">
+        <f>($B$9/$B$8)*(1-(1+B109)^(-$B$8))/(1-1/(1+B109))</f>
+        <v/>
+      </c>
+      <c r="I109" s="4">
+        <f>(F109*(1-$B$5)-E109*$B$9)*G109-H109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Replacement at HK depreciation proxy (not sourced)</t>
+        </is>
+      </c>
+      <c r="B110" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C110">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3">
+        <f>Inputs!$C$168</f>
+        <v/>
+      </c>
+      <c r="F110" s="4">
+        <f>$B$15+D110*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G110" s="3">
+        <f>(1+B110)^(-$B$8)*(1-(1+B110)^(-C110))/(1-1/(1+B110))</f>
+        <v/>
+      </c>
+      <c r="H110" s="4">
+        <f>($B$9/$B$8)*(1-(1+B110)^(-$B$8))/(1-1/(1+B110))</f>
+        <v/>
+      </c>
+      <c r="I110" s="4">
+        <f>(F110*(1-$B$5)-E110*$B$9)*G110-H110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Life 30 years with replacement proxy</t>
+        </is>
+      </c>
+      <c r="B111" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C111" t="n">
+        <v>30</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3">
+        <f>Inputs!$C$168</f>
+        <v/>
+      </c>
+      <c r="F111" s="4">
+        <f>$B$15+D111*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G111" s="3">
+        <f>(1+B111)^(-$B$8)*(1-(1+B111)^(-C111))/(1-1/(1+B111))</f>
+        <v/>
+      </c>
+      <c r="H111" s="4">
+        <f>($B$9/$B$8)*(1-(1+B111)^(-$B$8))/(1-1/(1+B111))</f>
+        <v/>
+      </c>
+      <c r="I111" s="4">
+        <f>(F111*(1-$B$5)-E111*$B$9)*G111-H111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>On-site income with replacement proxy</t>
+        </is>
+      </c>
+      <c r="B112" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C112">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="3">
+        <f>Inputs!$C$168</f>
+        <v/>
+      </c>
+      <c r="F112" s="4">
+        <f>$B$15+D112*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G112" s="3">
+        <f>(1+B112)^(-$B$8)*(1-(1+B112)^(-C112))/(1-1/(1+B112))</f>
+        <v/>
+      </c>
+      <c r="H112" s="4">
+        <f>($B$9/$B$8)*(1-(1+B112)^(-$B$8))/(1-1/(1+B112))</f>
+        <v/>
+      </c>
+      <c r="I112" s="4">
+        <f>(F112*(1-$B$5)-E112*$B$9)*G112-H112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Combined: on-site income, life 30, replacement proxy</t>
+        </is>
+      </c>
+      <c r="B113" s="5">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C113" t="n">
+        <v>30</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="3">
+        <f>Inputs!$C$168</f>
+        <v/>
+      </c>
+      <c r="F113" s="4">
+        <f>$B$15+D113*$B$14*Inputs!$D$150/1000</f>
+        <v/>
+      </c>
+      <c r="G113" s="3">
+        <f>(1+B113)^(-$B$8)*(1-(1+B113)^(-C113))/(1-1/(1+B113))</f>
+        <v/>
+      </c>
+      <c r="H113" s="4">
+        <f>($B$9/$B$8)*(1-(1+B113)^(-$B$8))/(1-1/(1+B113))</f>
+        <v/>
+      </c>
+      <c r="I113" s="4">
+        <f>(F113*(1-$B$5)-E113*$B$9)*G113-H113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Check: base scenario less B21 (about 0)</t>
+        </is>
+      </c>
+      <c r="I115" s="4">
+        <f>I103-B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Scenarios are pre-tax. Where the life exceeds the tax depreciation years, tax is not computed (see the guard in row 32).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Two-way sensitivity: primary NPV pre-tax (THB bn), capital cost (rows) by cash operating-cost share (columns), ticket-only revenue, base WACC and life</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Capital cost (THB bn), rows; cash operating-cost share, columns</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C119" s="3">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="D119" s="3">
+        <f>Inputs!$C$153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>150</v>
+      </c>
+      <c r="B120" s="4">
+        <f>$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="C120" s="4">
+        <f>$B$15*(1-C$119)*$B$27-$A120*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="D120" s="4">
+        <f>$B$15*(1-D$119)*$B$27-$A120*($B$28/$B$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>200</v>
+      </c>
+      <c r="B121" s="4">
+        <f>$B$15*(1-B$119)*$B$27-$A121*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="C121" s="4">
+        <f>$B$15*(1-C$119)*$B$27-$A121*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="D121" s="4">
+        <f>$B$15*(1-D$119)*$B$27-$A121*($B$28/$B$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>250</v>
+      </c>
+      <c r="B122" s="4">
+        <f>$B$15*(1-B$119)*$B$27-$A122*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="C122" s="4">
+        <f>$B$15*(1-C$119)*$B$27-$A122*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="D122" s="4">
+        <f>$B$15*(1-D$119)*$B$27-$A122*($B$28/$B$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>300</v>
+      </c>
+      <c r="B123" s="4">
+        <f>$B$15*(1-B$119)*$B$27-$A123*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="C123" s="4">
+        <f>$B$15*(1-C$119)*$B$27-$A123*($B$28/$B$9)</f>
+        <v/>
+      </c>
+      <c r="D123" s="4">
+        <f>$B$15*(1-D$119)*$B$27-$A123*($B$28/$B$9)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -10349,14 +10349,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Two-way sensitivity: primary NPV pre-tax (THB bn), capital cost (rows) by cash operating-cost share (columns), ticket-only revenue, base WACC and life</t>
+          <t>Two-way sensitivity: primary NPV pre-tax (THB bn), capital cost (rows) by cost share (columns). Columns B and C are cash-cost cases; column D is the legacy total-cost reconciliation (includes D&amp;A, financing and tax). Ticket-only revenue, base WACC and life; replacement per B16.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Capital cost (THB bn), rows; cash operating-cost share, columns</t>
+          <t>Capital cost (THB bn), rows; cost share, columns (B, C cash; D legacy total-cost)</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
@@ -10376,15 +10376,15 @@
         <v>150</v>
       </c>
       <c r="B120" s="4">
-        <f>$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)</f>
+        <f>$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
         <v/>
       </c>
       <c r="C120" s="4">
-        <f>$B$15*(1-C$119)*$B$27-$A120*($B$28/$B$9)</f>
+        <f>$B$15*(1-C$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
         <v/>
       </c>
       <c r="D120" s="4">
-        <f>$B$15*(1-D$119)*$B$27-$A120*($B$28/$B$9)</f>
+        <f>$B$15*(1-D$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
         <v/>
       </c>
     </row>
@@ -10393,15 +10393,15 @@
         <v>200</v>
       </c>
       <c r="B121" s="4">
-        <f>$B$15*(1-B$119)*$B$27-$A121*($B$28/$B$9)</f>
+        <f>$B$15*(1-B$119)*$B$27-$A121*($B$28/$B$9)-$B$16*$A121*$B$27</f>
         <v/>
       </c>
       <c r="C121" s="4">
-        <f>$B$15*(1-C$119)*$B$27-$A121*($B$28/$B$9)</f>
+        <f>$B$15*(1-C$119)*$B$27-$A121*($B$28/$B$9)-$B$16*$A121*$B$27</f>
         <v/>
       </c>
       <c r="D121" s="4">
-        <f>$B$15*(1-D$119)*$B$27-$A121*($B$28/$B$9)</f>
+        <f>$B$15*(1-D$119)*$B$27-$A121*($B$28/$B$9)-$B$16*$A121*$B$27</f>
         <v/>
       </c>
     </row>
@@ -10410,15 +10410,15 @@
         <v>250</v>
       </c>
       <c r="B122" s="4">
-        <f>$B$15*(1-B$119)*$B$27-$A122*($B$28/$B$9)</f>
+        <f>$B$15*(1-B$119)*$B$27-$A122*($B$28/$B$9)-$B$16*$A122*$B$27</f>
         <v/>
       </c>
       <c r="C122" s="4">
-        <f>$B$15*(1-C$119)*$B$27-$A122*($B$28/$B$9)</f>
+        <f>$B$15*(1-C$119)*$B$27-$A122*($B$28/$B$9)-$B$16*$A122*$B$27</f>
         <v/>
       </c>
       <c r="D122" s="4">
-        <f>$B$15*(1-D$119)*$B$27-$A122*($B$28/$B$9)</f>
+        <f>$B$15*(1-D$119)*$B$27-$A122*($B$28/$B$9)-$B$16*$A122*$B$27</f>
         <v/>
       </c>
     </row>
@@ -10427,15 +10427,15 @@
         <v>300</v>
       </c>
       <c r="B123" s="4">
-        <f>$B$15*(1-B$119)*$B$27-$A123*($B$28/$B$9)</f>
+        <f>$B$15*(1-B$119)*$B$27-$A123*($B$28/$B$9)-$B$16*$A123*$B$27</f>
         <v/>
       </c>
       <c r="C123" s="4">
-        <f>$B$15*(1-C$119)*$B$27-$A123*($B$28/$B$9)</f>
+        <f>$B$15*(1-C$119)*$B$27-$A123*($B$28/$B$9)-$B$16*$A123*$B$27</f>
         <v/>
       </c>
       <c r="D123" s="4">
-        <f>$B$15*(1-D$119)*$B$27-$A123*($B$28/$B$9)</f>
+        <f>$B$15*(1-D$119)*$B$27-$A123*($B$28/$B$9)-$B$16*$A123*$B$27</f>
         <v/>
       </c>
     </row>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -58,7 +58,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -69,6 +69,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6065,7 +6066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S123"/>
+  <dimension ref="A1:S135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -6099,7 +6100,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Primary result: the park-only operator ledger, which matches the theme-park revenue. Legacy column: the 300 bn complex capex on the same revenue, kept as a reconciliation to the earlier model.</t>
+          <t>Primary result: the park-only operator ledger with ticket plus on-site income (decision by kamolpeen, 21 October 2026, with the same weight as team approval). Ticket-only is a memo in the scenario table. Legacy column: the 300 bn complex on ticket-only revenue, a reconciliation to the earlier model.</t>
         </is>
       </c>
     </row>
@@ -6284,11 +6285,11 @@
         </is>
       </c>
       <c r="B15">
-        <f>B14*B13/1000</f>
+        <f>B14*(B13+B19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="C15">
-        <f>B15</f>
+        <f>B14*(C13+C19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
     </row>
@@ -6337,6 +6338,19 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>On-site income included in revenue (1 = yes; 1,862 THB per operator visit, sourced benchmark)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -6422,7 +6436,7 @@
         </is>
       </c>
       <c r="B25" s="4">
-        <f>B10-B21/((1-B5)*B13/1000*(1-B11)*B27)</f>
+        <f>B10-B21/((1-B5)*(B13+B19*Inputs!$D$150)/1000*(1-B11)*B27)</f>
         <v/>
       </c>
       <c r="C25" s="4">
@@ -6637,7 +6651,7 @@
         <v/>
       </c>
       <c r="G41" s="4">
-        <f>F41*$B$13/1000</f>
+        <f>F41*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H41" s="4">
@@ -6714,7 +6728,7 @@
         <v/>
       </c>
       <c r="G42" s="4">
-        <f>F42*$B$13/1000</f>
+        <f>F42*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H42" s="4">
@@ -6791,7 +6805,7 @@
         <v/>
       </c>
       <c r="G43" s="4">
-        <f>F43*$B$13/1000</f>
+        <f>F43*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H43" s="4">
@@ -6868,7 +6882,7 @@
         <v/>
       </c>
       <c r="G44" s="4">
-        <f>F44*$B$13/1000</f>
+        <f>F44*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H44" s="4">
@@ -6945,7 +6959,7 @@
         <v/>
       </c>
       <c r="G45" s="4">
-        <f>F45*$B$13/1000</f>
+        <f>F45*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H45" s="4">
@@ -7022,7 +7036,7 @@
         <v/>
       </c>
       <c r="G46" s="4">
-        <f>F46*$B$13/1000</f>
+        <f>F46*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H46" s="4">
@@ -7099,7 +7113,7 @@
         <v/>
       </c>
       <c r="G47" s="4">
-        <f>F47*$B$13/1000</f>
+        <f>F47*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H47" s="4">
@@ -7176,7 +7190,7 @@
         <v/>
       </c>
       <c r="G48" s="4">
-        <f>F48*$B$13/1000</f>
+        <f>F48*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H48" s="4">
@@ -7253,7 +7267,7 @@
         <v/>
       </c>
       <c r="G49" s="4">
-        <f>F49*$B$13/1000</f>
+        <f>F49*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H49" s="4">
@@ -7330,7 +7344,7 @@
         <v/>
       </c>
       <c r="G50" s="4">
-        <f>F50*$B$13/1000</f>
+        <f>F50*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H50" s="4">
@@ -7407,7 +7421,7 @@
         <v/>
       </c>
       <c r="G51" s="4">
-        <f>F51*$B$13/1000</f>
+        <f>F51*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H51" s="4">
@@ -7484,7 +7498,7 @@
         <v/>
       </c>
       <c r="G52" s="4">
-        <f>F52*$B$13/1000</f>
+        <f>F52*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H52" s="4">
@@ -7561,7 +7575,7 @@
         <v/>
       </c>
       <c r="G53" s="4">
-        <f>F53*$B$13/1000</f>
+        <f>F53*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H53" s="4">
@@ -7638,7 +7652,7 @@
         <v/>
       </c>
       <c r="G54" s="4">
-        <f>F54*$B$13/1000</f>
+        <f>F54*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H54" s="4">
@@ -7715,7 +7729,7 @@
         <v/>
       </c>
       <c r="G55" s="4">
-        <f>F55*$B$13/1000</f>
+        <f>F55*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H55" s="4">
@@ -7792,7 +7806,7 @@
         <v/>
       </c>
       <c r="G56" s="4">
-        <f>F56*$B$13/1000</f>
+        <f>F56*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H56" s="4">
@@ -7869,7 +7883,7 @@
         <v/>
       </c>
       <c r="G57" s="4">
-        <f>F57*$B$13/1000</f>
+        <f>F57*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H57" s="4">
@@ -7946,7 +7960,7 @@
         <v/>
       </c>
       <c r="G58" s="4">
-        <f>F58*$B$13/1000</f>
+        <f>F58*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H58" s="4">
@@ -8023,7 +8037,7 @@
         <v/>
       </c>
       <c r="G59" s="4">
-        <f>F59*$B$13/1000</f>
+        <f>F59*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H59" s="4">
@@ -8100,7 +8114,7 @@
         <v/>
       </c>
       <c r="G60" s="4">
-        <f>F60*$B$13/1000</f>
+        <f>F60*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H60" s="4">
@@ -8177,7 +8191,7 @@
         <v/>
       </c>
       <c r="G61" s="4">
-        <f>F61*$B$13/1000</f>
+        <f>F61*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H61" s="4">
@@ -8254,7 +8268,7 @@
         <v/>
       </c>
       <c r="G62" s="4">
-        <f>F62*$B$13/1000</f>
+        <f>F62*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H62" s="4">
@@ -8331,7 +8345,7 @@
         <v/>
       </c>
       <c r="G63" s="4">
-        <f>F63*$B$13/1000</f>
+        <f>F63*($B$13+$B$19*Inputs!$D$150)/1000</f>
         <v/>
       </c>
       <c r="H63" s="4">
@@ -9863,6 +9877,13 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Validation of the HK depreciation proxy for replacement capex (21 October 2026): not appropriate as the base. It is depreciation over all noncurrent assets, including long-lived buildings and land, so it is not a replacement estimate. At 200 bn it gives about 15.8 bn a year, around two thirds of primary revenue. It is kept only as a labelled stress (rows 110 to 113).</t>
+        </is>
+      </c>
+    </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
@@ -9920,7 +9941,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Base: primary, ticket-only revenue, 20-year life</t>
+          <t>Primary: ticket plus on-site income, cash basis, 20-year life</t>
         </is>
       </c>
       <c r="B103" s="5">
@@ -9931,15 +9952,16 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="D103" t="n">
-        <v>0</v>
+      <c r="D103">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E103" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F103" s="4">
-        <f>$B$15+D103*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D103*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G103" s="3">
@@ -9958,7 +9980,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>On-site income at 1,862 THB per operator visit (low-case benchmark), cash ratio on total revenue</t>
+          <t>Ticket-only memo (earlier basis, reconciliation)</t>
         </is>
       </c>
       <c r="B104" s="5">
@@ -9970,14 +9992,14 @@
         <v/>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F104" s="4">
-        <f>$B$15+D104*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D104*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G104" s="3">
@@ -9996,7 +10018,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Life 30 years</t>
+          <t>Life 30 years (primary basis)</t>
         </is>
       </c>
       <c r="B105" s="5">
@@ -10006,15 +10028,16 @@
       <c r="C105" t="n">
         <v>30</v>
       </c>
-      <c r="D105" t="n">
-        <v>0</v>
+      <c r="D105">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E105" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F105" s="4">
-        <f>$B$15+D105*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D105*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G105" s="3">
@@ -10033,7 +10056,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Life 40 years</t>
+          <t>Life 40 years (primary basis)</t>
         </is>
       </c>
       <c r="B106" s="5">
@@ -10043,15 +10066,16 @@
       <c r="C106" t="n">
         <v>40</v>
       </c>
-      <c r="D106" t="n">
-        <v>0</v>
+      <c r="D106">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E106" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F106" s="4">
-        <f>$B$15+D106*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D106*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G106" s="3">
@@ -10070,7 +10094,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>WACC 6 percent</t>
+          <t>WACC 6 percent (primary basis)</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -10080,15 +10104,16 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="D107" t="n">
-        <v>0</v>
+      <c r="D107">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E107" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F107" s="4">
-        <f>$B$15+D107*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D107*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G107" s="3">
@@ -10107,7 +10132,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>WACC 7 percent (high case)</t>
+          <t>WACC 7 percent, high case (primary basis)</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -10117,15 +10142,16 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="D108" t="n">
-        <v>0</v>
+      <c r="D108">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E108" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F108" s="4">
-        <f>$B$15+D108*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D108*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G108" s="3">
@@ -10144,7 +10170,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>WACC 10 percent (low case)</t>
+          <t>WACC 10 percent, low case (primary basis)</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -10154,15 +10180,16 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="D109" t="n">
-        <v>0</v>
+      <c r="D109">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E109" s="3">
         <f>B16</f>
         <v/>
       </c>
       <c r="F109" s="4">
-        <f>$B$15+D109*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D109*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G109" s="3">
@@ -10181,7 +10208,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Replacement at HK depreciation proxy (not sourced)</t>
+          <t>Replacement at HK depreciation proxy (stress only; not a replacement estimate)</t>
         </is>
       </c>
       <c r="B110" s="5">
@@ -10192,15 +10219,16 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="D110" t="n">
-        <v>0</v>
+      <c r="D110">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E110" s="3">
         <f>Inputs!$C$168</f>
         <v/>
       </c>
       <c r="F110" s="4">
-        <f>$B$15+D110*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D110*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G110" s="3">
@@ -10219,7 +10247,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Life 30 years with replacement proxy</t>
+          <t>Life 30 years with replacement proxy (stress)</t>
         </is>
       </c>
       <c r="B111" s="5">
@@ -10229,15 +10257,16 @@
       <c r="C111" t="n">
         <v>30</v>
       </c>
-      <c r="D111" t="n">
-        <v>0</v>
+      <c r="D111">
+        <f>$B$19</f>
+        <v/>
       </c>
       <c r="E111" s="3">
         <f>Inputs!$C$168</f>
         <v/>
       </c>
       <c r="F111" s="4">
-        <f>$B$15+D111*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D111*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G111" s="3">
@@ -10256,7 +10285,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>On-site income with replacement proxy</t>
+          <t>Ticket-only with replacement proxy (stress)</t>
         </is>
       </c>
       <c r="B112" s="5">
@@ -10268,14 +10297,14 @@
         <v/>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="3">
         <f>Inputs!$C$168</f>
         <v/>
       </c>
       <c r="F112" s="4">
-        <f>$B$15+D112*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D112*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G112" s="3">
@@ -10294,7 +10323,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Combined: on-site income, life 30, replacement proxy</t>
+          <t>Combined: ticket-only, life 30, replacement proxy (stress)</t>
         </is>
       </c>
       <c r="B113" s="5">
@@ -10305,14 +10334,14 @@
         <v>30</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="3">
         <f>Inputs!$C$168</f>
         <v/>
       </c>
       <c r="F113" s="4">
-        <f>$B$15+D113*$B$14*Inputs!$D$150/1000</f>
+        <f>$B$14*$B$13/1000+D113*$B$14*Inputs!$D$150/1000</f>
         <v/>
       </c>
       <c r="G113" s="3">
@@ -10436,6 +10465,156 @@
       </c>
       <c r="D123" s="4">
         <f>$B$15*(1-D$119)*$B$27-$A123*($B$28/$B$9)-$B$16*$A123*$B$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Attendance benchmarks (million visits a year) against the primary break-even attendance</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Park</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Attendance (million)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Magic Kingdom (Walt Disney World)</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>TEA/AECOM ranking as reported by Disney Food Blog, 23 Oct 2025: https://disneyfoodblog.com/2025/10/23/magic-kingdom-is-the-1-most-visited-theme-park-in-the-world-but-the-rest-of-the-list-may-surprise-you</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Disneyland Park (California)</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TEA/AECOM ranking as summarised by BGT Safari, 11 Nov 2025: https://bgtsafari.com/2025/11/11/the-tea-rankings-are-out-of-for-the-top-25-theme-parks-worldwide-and-almost-half-are-in-asia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Hong Kong Disneyland</t>
+        </is>
+      </c>
+      <c r="B130">
+        <f>Inputs!$C$85</f>
+        <v/>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>inputs.csv (Hong Kong Disneyland press, 28 Apr 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Shanghai Disneyland (approximate)</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>14</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>TEA/AECOM 2023 index as summarised in the search result; approximate, not checked against the report</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Tokyo Disney Resort (two parks)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Not verified in this round</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Primary break-even attendance (B25, million visits a year)</t>
+        </is>
+      </c>
+      <c r="B134" s="4">
+        <f>B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Multiple of Magic Kingdom attendance</t>
+        </is>
+      </c>
+      <c r="B135" s="8">
+        <f>B25/B128</f>
         <v/>
       </c>
     </row>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\DisneyDiD\econ-disney-seminar\seminar\workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116124F0-F692-4717-9B5D-8D334BC020D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EECB300-5F20-4148-9761-803C73EF4FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2301,11 +2301,29 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.33920117521367521"/>
+          <c:y val="1.2121212121212121E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23303899572649572"/>
+          <c:y val="0.11515151515151516"/>
+          <c:w val="0.74859626068376073"/>
+          <c:h val="0.76363636363636367"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -2814,6 +2832,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27641452991452992"/>
+          <c:y val="0.96957134335480799"/>
+          <c:w val="0.44717083333333335"/>
+          <c:h val="2.739835361488905E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
       <c:txPr>
         <a:bodyPr/>
@@ -2950,7 +2978,7 @@
       <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9360000" cy="7200000"/>
+    <xdr:ext cx="9360000" cy="8382000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3">

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\DisneyDiD\econ-disney-seminar\seminar\workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\claude\C--Users-user-AppData-Roaming-Claude-scratch-workspaces-c7acaf2f-ed5f-4f26-814b-0755985b8641-704b7f5d-017e-4c68-a76d-e0c46600fd5a-scratch-2026-10-16-ee569e\885493fd-7279-48f0-8993-cb2538820dce\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EECB300-5F20-4148-9761-803C73EF4FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD1439-7B9B-42B1-9376-FFB27DA66F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="440">
   <si>
     <t>Parameter</t>
   </si>
@@ -1336,6 +1336,12 @@
   </si>
   <si>
     <t>Park-only operator appraisal: charts</t>
+  </si>
+  <si>
+    <t>Capital outflow, absolute (THB bn)</t>
+  </si>
+  <si>
+    <t>Operating cash flow (THB bn)</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1352,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1363,6 +1369,14 @@
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1385,7 +1399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1398,6 +1412,9 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1433,7 +1450,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="1300" b="1"/>
-              <a:t>Annual cash flow before tax, park-only (THB bn)</a:t>
+              <a:t>Annual cash flow before tax, park-only (THB bn, log scale)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1452,18 +1469,18 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Appraisal!$J$40</c:f>
+              <c:f>Appraisal!$U$40</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Cash flow before tax</c:v>
+                  <c:v>Capital outflow, absolute (THB bn)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1F3864"/>
+              <a:srgbClr val="C0504D"/>
             </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -1473,7 +1490,7 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:numFmt formatCode="\-#,##0.0" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -1508,7 +1525,7 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
-              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:numFmt formatCode="\-#,##0.0" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -1640,78 +1657,78 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Appraisal!$J$41:$J$63</c:f>
+              <c:f>Appraisal!$U$41:$U$63</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>-100</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-100</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1719,6 +1736,188 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-6E58-4402-AA0C-BC86BA6AC45A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Appraisal!$V$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Operating cash flow (THB bn)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F3864"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Appraisal!$A$41:$A$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Appraisal!$V$41:$V$63</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.3395922101449287</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D25F-44B6-B4FF-3F12DE3843DC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1731,6 +1930,7 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
         <c:axId val="10"/>
         <c:axId val="100"/>
       </c:barChart>
@@ -1762,9 +1962,10 @@
       <c:valAx>
         <c:axId val="100"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:max val="20"/>
-          <c:min val="-120"/>
+          <c:max val="1000"/>
+          <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1807,9 +2008,13 @@
         <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="20"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
@@ -5747,7 +5952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S135"/>
+  <dimension ref="A1:V135"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -5763,6 +5968,7 @@
     <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="18" width="16" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="21" max="22" width="18.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -6080,12 +6286,12 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>339</v>
       </c>
@@ -6143,8 +6349,14 @@
       <c r="S40" s="7" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U40" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="V40" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>0</v>
       </c>
@@ -6220,8 +6432,16 @@
         <f>SUM($Q$41:Q41)</f>
         <v>-100</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U41" s="5">
+        <f t="shared" ref="U41:U63" si="14">IF(J41&lt;0,-J41,NA())</f>
+        <v>100</v>
+      </c>
+      <c r="V41" s="5" t="e">
+        <f t="shared" ref="V41:V63" si="15">IF(J41&gt;0,J41,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1</v>
       </c>
@@ -6282,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="5">
-        <f t="shared" ref="P42:P63" si="14">MAX(0,O42-O41)</f>
+        <f t="shared" ref="P42:P63" si="16">MAX(0,O42-O41)</f>
         <v>0</v>
       </c>
       <c r="Q42" s="5">
@@ -6297,8 +6517,16 @@
         <f>SUM($Q$41:Q42)</f>
         <v>-200</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U42" s="5">
+        <f t="shared" si="14"/>
+        <v>100</v>
+      </c>
+      <c r="V42" s="5" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2</v>
       </c>
@@ -6359,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q43" s="5">
@@ -6374,8 +6602,16 @@
         <f>SUM($Q$41:Q43)</f>
         <v>-194.66040778985507</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U43" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V43" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>3</v>
       </c>
@@ -6436,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q44" s="5">
@@ -6451,8 +6687,16 @@
         <f>SUM($Q$41:Q44)</f>
         <v>-189.32081557971014</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U44" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V44" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6513,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q45" s="5">
@@ -6528,8 +6772,16 @@
         <f>SUM($Q$41:Q45)</f>
         <v>-183.98122336956521</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U45" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V45" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>5</v>
       </c>
@@ -6590,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q46" s="5">
@@ -6605,8 +6857,16 @@
         <f>SUM($Q$41:Q46)</f>
         <v>-178.64163115942029</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U46" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V46" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>6</v>
       </c>
@@ -6667,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q47" s="5">
@@ -6682,8 +6942,16 @@
         <f>SUM($Q$41:Q47)</f>
         <v>-173.30203894927536</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U47" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V47" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>7</v>
       </c>
@@ -6744,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q48" s="5">
@@ -6759,8 +7027,16 @@
         <f>SUM($Q$41:Q48)</f>
         <v>-167.96244673913043</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U48" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V48" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>8</v>
       </c>
@@ -6821,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q49" s="5">
@@ -6836,8 +7112,16 @@
         <f>SUM($Q$41:Q49)</f>
         <v>-162.6228545289855</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U49" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V49" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>9</v>
       </c>
@@ -6898,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q50" s="5">
@@ -6913,8 +7197,16 @@
         <f>SUM($Q$41:Q50)</f>
         <v>-157.28326231884057</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U50" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V50" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>10</v>
       </c>
@@ -6975,7 +7267,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q51" s="5">
@@ -6990,8 +7282,16 @@
         <f>SUM($Q$41:Q51)</f>
         <v>-151.94367010869564</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U51" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V51" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>11</v>
       </c>
@@ -7052,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q52" s="5">
@@ -7067,8 +7367,16 @@
         <f>SUM($Q$41:Q52)</f>
         <v>-146.60407789855071</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U52" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V52" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>12</v>
       </c>
@@ -7129,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q53" s="5">
@@ -7144,8 +7452,16 @@
         <f>SUM($Q$41:Q53)</f>
         <v>-141.26448568840578</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U53" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V53" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>13</v>
       </c>
@@ -7206,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q54" s="5">
@@ -7221,8 +7537,16 @@
         <f>SUM($Q$41:Q54)</f>
         <v>-135.92489347826086</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U54" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V54" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>14</v>
       </c>
@@ -7283,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q55" s="5">
@@ -7298,8 +7622,16 @@
         <f>SUM($Q$41:Q55)</f>
         <v>-130.58530126811593</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U55" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V55" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>15</v>
       </c>
@@ -7360,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q56" s="5">
@@ -7375,8 +7707,16 @@
         <f>SUM($Q$41:Q56)</f>
         <v>-125.245709057971</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U56" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V56" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>16</v>
       </c>
@@ -7437,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q57" s="5">
@@ -7452,8 +7792,16 @@
         <f>SUM($Q$41:Q57)</f>
         <v>-119.90611684782607</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U57" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V57" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>17</v>
       </c>
@@ -7514,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q58" s="5">
@@ -7529,8 +7877,16 @@
         <f>SUM($Q$41:Q58)</f>
         <v>-114.56652463768114</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U58" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V58" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>18</v>
       </c>
@@ -7591,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="P59" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q59" s="5">
@@ -7606,8 +7962,16 @@
         <f>SUM($Q$41:Q59)</f>
         <v>-109.22693242753621</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U59" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V59" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>19</v>
       </c>
@@ -7668,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q60" s="5">
@@ -7683,8 +8047,16 @@
         <f>SUM($Q$41:Q60)</f>
         <v>-103.88734021739128</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U60" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V60" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>20</v>
       </c>
@@ -7745,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q61" s="5">
@@ -7760,8 +8132,16 @@
         <f>SUM($Q$41:Q61)</f>
         <v>-98.547748007246355</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U61" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V61" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>21</v>
       </c>
@@ -7822,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q62" s="5">
@@ -7837,8 +8217,16 @@
         <f>SUM($Q$41:Q62)</f>
         <v>-93.208155797101426</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="U62" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V62" s="5">
+        <f t="shared" si="15"/>
+        <v>5.3395922101449287</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>22</v>
       </c>
@@ -7899,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q63" s="5">
@@ -7914,6 +8302,14 @@
         <f>SUM($Q$41:Q63)</f>
         <v>-93.208155797101426</v>
       </c>
+      <c r="U63" s="5" t="e">
+        <f t="shared" si="14"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V63" s="5" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
@@ -7981,35 +8377,35 @@
         <v>0</v>
       </c>
       <c r="F68" s="4">
-        <f t="shared" ref="F68:F94" si="15">SUMPRODUCT($B$41:$B$63*($A$41:$A$63&gt;=$B$8+E68)*($A$41:$A$63&lt;$B$8+E68+$B$7))</f>
+        <f t="shared" ref="F68:F94" si="17">SUMPRODUCT($B$41:$B$63*($A$41:$A$63&gt;=$B$8+E68)*($A$41:$A$63&lt;$B$8+E68+$B$7))</f>
         <v>9.0908772291197089</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" ref="G68:G94" si="16">(D68-C68*$B$5)*$B$15*F68-B68*$B$28-I68*B68*$B$9*F68</f>
+        <f t="shared" ref="G68:G94" si="18">(D68-C68*$B$5)*$B$15*F68-B68*$B$28-I68*B68*$B$9*F68</f>
         <v>-144.05101535660108</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" ref="H68:H94" si="17">(D68-C68*$B$5)*$C$15*F68-B68*($C$9/$B$9)*$B$28-I68*B68*$C$9*F68</f>
+        <f t="shared" ref="H68:H94" si="19">(D68-C68*$B$5)*$C$15*F68-B68*($C$9/$B$9)*$B$28-I68*B68*$C$9*F68</f>
         <v>-259.41977774562076</v>
       </c>
       <c r="I68" s="4">
-        <f t="shared" ref="I68:I93" si="18">$B$16</f>
+        <f t="shared" ref="I68:I93" si="20">$B$16</f>
         <v>0</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" ref="J68:J94" si="19">D68*$B$15-C68*$B$5*$B$15-B68*$B$9/$B$18</f>
+        <f t="shared" ref="J68:J94" si="21">D68*$B$15-C68*$B$5*$B$15-B68*$B$9/$B$18</f>
         <v>-4.6604077898550713</v>
       </c>
       <c r="K68" s="5">
-        <f t="shared" ref="K68:K94" si="20">IF($B$18&lt;$B$7,"n/a",G68-$B$17*MAX(0,J68)*F68)</f>
+        <f t="shared" ref="K68:K94" si="22">IF($B$18&lt;$B$7,"n/a",G68-$B$17*MAX(0,J68)*F68)</f>
         <v>-144.05101535660108</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" ref="L68:L94" si="21">D68*$C$15-C68*$B$5*$C$15-B68*$C$9/$C$18</f>
+        <f t="shared" ref="L68:L94" si="23">D68*$C$15-C68*$B$5*$C$15-B68*$C$9/$C$18</f>
         <v>-11.758386413043478</v>
       </c>
       <c r="M68" s="5">
-        <f t="shared" ref="M68:M94" si="22">IF($C$18&lt;$C$7,"n/a",H68-$B$17*MAX(0,L68)*F68)</f>
+        <f t="shared" ref="M68:M94" si="24">IF($C$18&lt;$C$7,"n/a",H68-$B$17*MAX(0,L68)*F68)</f>
         <v>-259.41977774562076</v>
       </c>
       <c r="N68" t="s">
@@ -8033,35 +8429,35 @@
         <v>0</v>
       </c>
       <c r="F69" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-153.68064498623073</v>
       </c>
       <c r="H69" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-273.86422219006528</v>
       </c>
       <c r="I69" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J69" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-5.1604077898550713</v>
       </c>
       <c r="K69" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-153.68064498623073</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-12.508386413043478</v>
       </c>
       <c r="M69" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-273.86422219006528</v>
       </c>
       <c r="N69" t="s">
@@ -8085,35 +8481,35 @@
         <v>0</v>
       </c>
       <c r="F70" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G70" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-134.42138572697144</v>
       </c>
       <c r="H70" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-244.97533330117631</v>
       </c>
       <c r="I70" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J70" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-4.1604077898550713</v>
       </c>
       <c r="K70" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-134.42138572697144</v>
       </c>
       <c r="L70" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-11.008386413043478</v>
       </c>
       <c r="M70" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-244.97533330117631</v>
       </c>
       <c r="N70" t="s">
@@ -8137,35 +8533,35 @@
         <v>0</v>
       </c>
       <c r="F71" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G71" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-163.31027461586035</v>
       </c>
       <c r="H71" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-288.30866663450968</v>
       </c>
       <c r="I71" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J71" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-5.6604077898550731</v>
       </c>
       <c r="K71" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-163.31027461586035</v>
       </c>
       <c r="L71" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-13.258386413043478</v>
       </c>
       <c r="M71" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-288.30866663450968</v>
       </c>
       <c r="N71" t="s">
@@ -8189,35 +8585,35 @@
         <v>0</v>
       </c>
       <c r="F72" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G72" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-124.79175609734182</v>
       </c>
       <c r="H72" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-230.53088885673191</v>
       </c>
       <c r="I72" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J72" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-3.6604077898550713</v>
       </c>
       <c r="K72" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-124.79175609734182</v>
       </c>
       <c r="L72" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-10.258386413043478</v>
       </c>
       <c r="M72" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-230.53088885673191</v>
       </c>
       <c r="N72" t="s">
@@ -8241,35 +8637,35 @@
         <v>0</v>
       </c>
       <c r="F73" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G73" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-182.56953387511959</v>
       </c>
       <c r="H73" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-317.19755552339853</v>
       </c>
       <c r="I73" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J73" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-6.6604077898550713</v>
       </c>
       <c r="K73" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-182.56953387511959</v>
       </c>
       <c r="L73" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-14.758386413043478</v>
       </c>
       <c r="M73" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-317.19755552339853</v>
       </c>
       <c r="N73" t="s">
@@ -8293,35 +8689,35 @@
         <v>0</v>
       </c>
       <c r="F74" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G74" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-105.53249683808258</v>
       </c>
       <c r="H74" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-201.64199996784305</v>
       </c>
       <c r="I74" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J74" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-2.6604077898550713</v>
       </c>
       <c r="K74" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-105.53249683808258</v>
       </c>
       <c r="L74" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-8.7583864130434783</v>
       </c>
       <c r="M74" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-201.64199996784305</v>
       </c>
       <c r="N74" t="s">
@@ -8345,35 +8741,35 @@
         <v>0</v>
       </c>
       <c r="F75" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G75" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-152.2327970400431</v>
       </c>
       <c r="H75" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-264.38685643379603</v>
       </c>
       <c r="I75" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J75" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-5.5604069293478275</v>
       </c>
       <c r="K75" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-152.2327970400431</v>
       </c>
       <c r="L75" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-12.304766983695652</v>
       </c>
       <c r="M75" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-264.38685643379603</v>
       </c>
       <c r="N75" t="s">
@@ -8397,35 +8793,35 @@
         <v>0</v>
       </c>
       <c r="F76" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G76" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-135.86923367315907</v>
       </c>
       <c r="H76" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-254.45269905744547</v>
       </c>
       <c r="I76" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J76" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-3.7604086503623186</v>
       </c>
       <c r="K76" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-135.86923367315907</v>
       </c>
       <c r="L76" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-11.212005842391305</v>
       </c>
       <c r="M76" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-254.45269905744547</v>
       </c>
       <c r="N76" t="s">
@@ -8449,35 +8845,35 @@
         <v>0</v>
       </c>
       <c r="F77" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G77" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-160.41457872348511</v>
       </c>
       <c r="H77" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-269.35393512197129</v>
       </c>
       <c r="I77" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J77" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-6.4604060688405802</v>
       </c>
       <c r="K77" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-160.41457872348511</v>
       </c>
       <c r="L77" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-12.851147554347827</v>
       </c>
       <c r="M77" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-269.35393512197129</v>
       </c>
       <c r="N77" t="s">
@@ -8501,35 +8897,35 @@
         <v>0</v>
       </c>
       <c r="F78" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G78" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-127.68745198971706</v>
       </c>
       <c r="H78" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-249.48562036927018</v>
       </c>
       <c r="I78" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J78" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-2.860409510869566</v>
       </c>
       <c r="K78" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-127.68745198971706</v>
       </c>
       <c r="L78" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-10.665625271739129</v>
       </c>
       <c r="M78" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-249.48562036927018</v>
       </c>
       <c r="N78" t="s">
@@ -8553,35 +8949,35 @@
         <v>0</v>
       </c>
       <c r="F79" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G79" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-176.7781420903691</v>
       </c>
       <c r="H79" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-279.28809249832187</v>
       </c>
       <c r="I79" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J79" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-8.2604043478260856</v>
       </c>
       <c r="K79" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-176.7781420903691</v>
       </c>
       <c r="L79" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-13.943908695652173</v>
       </c>
       <c r="M79" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-279.28809249832187</v>
       </c>
       <c r="N79" t="s">
@@ -8605,35 +9001,35 @@
         <v>0</v>
       </c>
       <c r="F80" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G80" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-111.32388862283307</v>
       </c>
       <c r="H80" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-239.55146299291965</v>
       </c>
       <c r="I80" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J80" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-1.0604112318840588</v>
       </c>
       <c r="K80" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-111.32388862283307</v>
       </c>
       <c r="L80" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-9.5728641304347821</v>
       </c>
       <c r="M80" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-239.55146299291965</v>
       </c>
       <c r="N80" t="s">
@@ -8657,35 +9053,35 @@
         <v>0</v>
       </c>
       <c r="F81" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G81" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-133.4421548113595</v>
       </c>
       <c r="H81" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-252.97924350028205</v>
       </c>
       <c r="I81" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J81" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-3.4934290398550694</v>
       </c>
       <c r="K81" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-133.4421548113595</v>
       </c>
       <c r="L81" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-11.049925163043477</v>
       </c>
       <c r="M81" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-252.97924350028205</v>
       </c>
       <c r="N81" t="s">
@@ -8709,35 +9105,35 @@
         <v>0</v>
       </c>
       <c r="F82" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G82" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-154.65987590184267</v>
       </c>
       <c r="H82" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-265.86031199095942</v>
       </c>
       <c r="I82" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J82" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-5.8273865398550733</v>
       </c>
       <c r="K82" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-154.65987590184267</v>
       </c>
       <c r="L82" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-12.466847663043479</v>
       </c>
       <c r="M82" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-265.86031199095942</v>
       </c>
       <c r="N82" t="s">
@@ -8761,35 +9157,35 @@
         <v>0</v>
       </c>
       <c r="F83" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G83" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-122.83329426611789</v>
       </c>
       <c r="H83" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-246.53870925494337</v>
       </c>
       <c r="I83" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J83" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-2.3264502898550674</v>
       </c>
       <c r="K83" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-122.83329426611789</v>
       </c>
       <c r="L83" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-10.341463913043476</v>
       </c>
       <c r="M83" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-246.53870925494337</v>
       </c>
       <c r="N83" t="s">
@@ -8813,35 +9209,35 @@
         <v>0</v>
       </c>
       <c r="F84" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G84" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-165.26873644708425</v>
       </c>
       <c r="H84" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-272.30084623629813</v>
       </c>
       <c r="I84" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J84" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-6.9943652898550717</v>
       </c>
       <c r="K84" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-165.26873644708425</v>
       </c>
       <c r="L84" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-13.175308913043478</v>
       </c>
       <c r="M84" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-272.30084623629813</v>
       </c>
       <c r="N84" t="s">
@@ -8865,35 +9261,35 @@
         <v>0</v>
       </c>
       <c r="F85" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G85" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-101.61557317563475</v>
       </c>
       <c r="H85" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-233.65764076426601</v>
       </c>
       <c r="I85" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J85" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>7.5072101449293882E-3</v>
       </c>
       <c r="K85" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-101.6292226007869</v>
       </c>
       <c r="L85" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-8.9245414130434799</v>
       </c>
       <c r="M85" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-233.65764076426601</v>
       </c>
       <c r="N85" t="s">
@@ -8917,35 +9313,35 @@
         <v>0</v>
       </c>
       <c r="F86" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G86" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-186.48645753756739</v>
       </c>
       <c r="H86" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-285.18191472697549</v>
       </c>
       <c r="I86" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J86" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-9.328322789855072</v>
       </c>
       <c r="K86" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-186.48645753756739</v>
       </c>
       <c r="L86" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-14.592231413043478</v>
       </c>
       <c r="M86" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-285.18191472697549</v>
       </c>
       <c r="N86" t="s">
@@ -8969,35 +9365,35 @@
         <v>0</v>
       </c>
       <c r="F87" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G87" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-164.28950553147232</v>
       </c>
       <c r="H87" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-280.30475643540393</v>
       </c>
       <c r="I87" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J87" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-6.3273865398550733</v>
       </c>
       <c r="K87" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-164.28950553147232</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-13.216847663043479</v>
       </c>
       <c r="M87" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-280.30475643540393</v>
       </c>
       <c r="N87" t="s">
@@ -9021,35 +9417,35 @@
         <v>0</v>
       </c>
       <c r="F88" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G88" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-123.81252518172984</v>
       </c>
       <c r="H88" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-238.5347990558376</v>
       </c>
       <c r="I88" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J88" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-2.9934290398550694</v>
       </c>
       <c r="K88" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-123.81252518172984</v>
       </c>
       <c r="L88" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-10.299925163043477</v>
       </c>
       <c r="M88" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-238.5347990558376</v>
       </c>
       <c r="N88" t="s">
@@ -9073,35 +9469,35 @@
         <v>0</v>
       </c>
       <c r="F89" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G89" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-184.52799570634352</v>
       </c>
       <c r="H89" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-301.18973512518704</v>
       </c>
       <c r="I89" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J89" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-7.9943652898550734</v>
       </c>
       <c r="K89" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-184.52799570634352</v>
       </c>
       <c r="L89" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-14.675308913043478</v>
       </c>
       <c r="M89" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-301.18973512518704</v>
       </c>
       <c r="N89" t="s">
@@ -9125,35 +9521,35 @@
         <v>0</v>
       </c>
       <c r="F90" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G90" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-103.57403500685862</v>
       </c>
       <c r="H90" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-217.64982036605451</v>
       </c>
       <c r="I90" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J90" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-1.3264502898550674</v>
       </c>
       <c r="K90" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-103.57403500685862</v>
       </c>
       <c r="L90" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-8.8414639130434765</v>
       </c>
       <c r="M90" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-217.64982036605451</v>
       </c>
       <c r="N90" t="s">
@@ -9177,35 +9573,35 @@
         <v>0</v>
       </c>
       <c r="F91" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G91" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-225.00497605608589</v>
       </c>
       <c r="H91" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-342.95969250475326</v>
       </c>
       <c r="I91" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J91" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-11.328322789855072</v>
       </c>
       <c r="K91" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-225.00497605608589</v>
       </c>
       <c r="L91" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-17.592231413043478</v>
       </c>
       <c r="M91" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-342.95969250475326</v>
       </c>
       <c r="N91" t="s">
@@ -9229,35 +9625,35 @@
         <v>0</v>
       </c>
       <c r="F92" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G92" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-63.097054657116246</v>
       </c>
       <c r="H92" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-175.87986298648829</v>
       </c>
       <c r="I92" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J92" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>2.0075072101449294</v>
       </c>
       <c r="K92" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-66.747054973916278</v>
       </c>
       <c r="L92" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-5.9245414130434799</v>
       </c>
       <c r="M92" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-175.87986298648829</v>
       </c>
       <c r="N92" t="s">
@@ -9281,35 +9677,35 @@
         <v>1</v>
       </c>
       <c r="F93" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.4174789158515821</v>
       </c>
       <c r="G93" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-147.64668774445229</v>
       </c>
       <c r="H93" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-261.60267486734432</v>
       </c>
       <c r="I93" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J93" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-4.6604077898550713</v>
       </c>
       <c r="K93" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-147.64668774445229</v>
       </c>
       <c r="L93" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-11.758386413043478</v>
       </c>
       <c r="M93" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-261.60267486734432</v>
       </c>
       <c r="N93" t="s">
@@ -9333,15 +9729,15 @@
         <v>0</v>
       </c>
       <c r="F94" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
       <c r="G94" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-287.85647706968189</v>
       </c>
       <c r="H94" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>-475.12797031524201</v>
       </c>
       <c r="I94" s="4">
@@ -9349,19 +9745,19 @@
         <v>7.9093281148075664E-2</v>
       </c>
       <c r="J94" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-4.6604077898550713</v>
       </c>
       <c r="K94" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-287.85647706968189</v>
       </c>
       <c r="L94" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-11.758386413043478</v>
       </c>
       <c r="M94" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-475.12797031524201</v>
       </c>
       <c r="N94" t="s">
@@ -9427,15 +9823,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G103" s="4">
-        <f t="shared" ref="G103:G113" si="23">(1+B103)^(-$B$8)*(1-(1+B103)^(-C103))/(1-1/(1+B103))</f>
+        <f t="shared" ref="G103:G113" si="25">(1+B103)^(-$B$8)*(1-(1+B103)^(-C103))/(1-1/(1+B103))</f>
         <v>9.0908772291197018</v>
       </c>
       <c r="H103" s="5">
-        <f t="shared" ref="H103:H113" si="24">($B$9/$B$8)*(1-(1+B103)^(-$B$8))/(1-1/(1+B103))</f>
+        <f t="shared" ref="H103:H113" si="26">($B$9/$B$8)*(1-(1+B103)^(-$B$8))/(1-1/(1+B103))</f>
         <v>192.59259259259238</v>
       </c>
       <c r="I103" s="5">
-        <f t="shared" ref="I103:I113" si="25">(F103*(1-$B$5)-E103*$B$9)*G103-H103</f>
+        <f t="shared" ref="I103:I113" si="27">(F103*(1-$B$5)-E103*$B$9)*G103-H103</f>
         <v>-144.05101535660091</v>
       </c>
     </row>
@@ -9463,15 +9859,15 @@
         <v>14.169225000000003</v>
       </c>
       <c r="G104" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.0908772291197018</v>
       </c>
       <c r="H104" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I104" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-163.12348144932429</v>
       </c>
     </row>
@@ -9487,7 +9883,7 @@
         <v>30</v>
       </c>
       <c r="D105">
-        <f t="shared" ref="D105:D111" si="26">$B$19</f>
+        <f t="shared" ref="D105:D111" si="28">$B$19</f>
         <v>1</v>
       </c>
       <c r="E105" s="4">
@@ -9499,15 +9895,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G105" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.423873465858767</v>
       </c>
       <c r="H105" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I105" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-136.93335903475651</v>
       </c>
     </row>
@@ -9523,7 +9919,7 @@
         <v>40</v>
       </c>
       <c r="D106">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E106" s="4">
@@ -9535,15 +9931,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G106" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>11.041308642357691</v>
       </c>
       <c r="H106" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I106" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-133.6365069760534</v>
       </c>
     </row>
@@ -9559,7 +9955,7 @@
         <v>20</v>
       </c>
       <c r="D107">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E107" s="4">
@@ -9571,15 +9967,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G107" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.820680394872868</v>
       </c>
       <c r="H107" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>194.33962264150929</v>
       </c>
       <c r="I107" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-136.5616018965782</v>
       </c>
     </row>
@@ -9595,7 +9991,7 @@
         <v>20</v>
       </c>
       <c r="D108">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E108" s="4">
@@ -9607,15 +10003,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G108" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.9009478930057568</v>
       </c>
       <c r="H108" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>193.45794392523374</v>
       </c>
       <c r="I108" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-140.59091968268936</v>
       </c>
     </row>
@@ -9631,7 +10027,7 @@
         <v>20</v>
       </c>
       <c r="D109">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E109" s="4">
@@ -9643,15 +10039,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G109" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7.7396033815986929</v>
       </c>
       <c r="H109" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>190.90909090909093</v>
       </c>
       <c r="I109" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-149.58276498309522</v>
       </c>
     </row>
@@ -9668,7 +10064,7 @@
         <v>20</v>
       </c>
       <c r="D110">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E110" s="4">
@@ -9680,15 +10076,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G110" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.0908772291197018</v>
       </c>
       <c r="H110" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I110" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-287.85647706968166</v>
       </c>
     </row>
@@ -9704,7 +10100,7 @@
         <v>30</v>
       </c>
       <c r="D111">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E111" s="4">
@@ -9716,15 +10112,15 @@
         <v>23.339575000000004</v>
       </c>
       <c r="G111" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.423873465858767</v>
       </c>
       <c r="H111" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I111" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-301.82502997218319</v>
       </c>
     </row>
@@ -9752,15 +10148,15 @@
         <v>14.169225000000003</v>
       </c>
       <c r="G112" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.0908772291197018</v>
       </c>
       <c r="H112" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I112" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-306.92894316240506</v>
       </c>
     </row>
@@ -9787,15 +10183,15 @@
         <v>14.169225000000003</v>
       </c>
       <c r="G113" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.423873465858767</v>
       </c>
       <c r="H113" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
       <c r="I113" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-323.69409367437572</v>
       </c>
     </row>
@@ -9825,15 +10221,15 @@
         <v>150</v>
       </c>
       <c r="B120" s="5">
-        <f t="shared" ref="B120:D123" si="27">$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
+        <f t="shared" ref="B120:D123" si="29">$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
         <v>-80.791281172994928</v>
       </c>
       <c r="C120" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-95.902867208452932</v>
       </c>
       <c r="D120" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-131.35311053161632</v>
       </c>
     </row>
@@ -9842,15 +10238,15 @@
         <v>200</v>
       </c>
       <c r="B121" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-128.93942932114308</v>
       </c>
       <c r="C121" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-144.05101535660108</v>
       </c>
       <c r="D121" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-179.50125867976448</v>
       </c>
     </row>
@@ -9859,15 +10255,15 @@
         <v>250</v>
       </c>
       <c r="B122" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-177.08757746929123</v>
       </c>
       <c r="C122" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-192.19916350474924</v>
       </c>
       <c r="D122" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-227.64940682791263</v>
       </c>
     </row>
@@ -9876,15 +10272,15 @@
         <v>300</v>
       </c>
       <c r="B123" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-225.23572561743936</v>
       </c>
       <c r="C123" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-240.34731165289736</v>
       </c>
       <c r="D123" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-275.79755497606072</v>
       </c>
     </row>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\claude\C--Users-user-AppData-Roaming-Claude-scratch-workspaces-c7acaf2f-ed5f-4f26-814b-0755985b8641-704b7f5d-017e-4c68-a76d-e0c46600fd5a-scratch-2026-10-16-ee569e\885493fd-7279-48f0-8993-cb2538820dce\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD1439-7B9B-42B1-9376-FFB27DA66F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE231D8-B9DB-4A00-8EF5-2DA226AA4BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1352,7 +1352,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1363,20 +1363,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1399,22 +1406,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1446,10 +1454,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="1"/>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1300" b="1"/>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
               <a:t>Annual cash flow before tax, park-only (THB bn, log scale)</a:t>
             </a:r>
           </a:p>
@@ -1499,9 +1511,7 @@
                 <a:effectLst/>
               </c:spPr>
               <c:txPr>
-                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
-                  <a:spAutoFit/>
-                </a:bodyPr>
+                <a:bodyPr/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
@@ -1534,9 +1544,7 @@
                 <a:effectLst/>
               </c:spPr>
               <c:txPr>
-                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
-                  <a:spAutoFit/>
-                </a:bodyPr>
+                <a:bodyPr/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
@@ -1941,6 +1949,28 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1952,6 +1982,20 @@
             </a:solidFill>
           </a:ln>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -1978,6 +2022,28 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>THB bn (log scale)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2005,6 +2071,20 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -2014,6 +2094,18 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -2054,7 +2146,7 @@
           <a:solidFill>
             <a:srgbClr val="404040"/>
           </a:solidFill>
-          <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -2082,10 +2174,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="1"/>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1300" b="1"/>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
               <a:t>Cumulative cash flow after tax, park-only (THB bn)</a:t>
             </a:r>
           </a:p>
@@ -2135,9 +2231,7 @@
                 <a:effectLst/>
               </c:spPr>
               <c:txPr>
-                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
-                  <a:spAutoFit/>
-                </a:bodyPr>
+                <a:bodyPr/>
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
@@ -2361,6 +2455,28 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2372,6 +2488,20 @@
             </a:solidFill>
           </a:ln>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -2397,6 +2527,28 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>THB bn</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2424,6 +2576,20 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -2469,7 +2635,7 @@
           <a:solidFill>
             <a:srgbClr val="404040"/>
           </a:solidFill>
-          <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -2497,10 +2663,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="1"/>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1300" b="1"/>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
               <a:t>NPV before tax by sensitivity case (THB bn)</a:t>
             </a:r>
           </a:p>
@@ -2968,6 +3138,28 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>Case</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2979,6 +3171,20 @@
             </a:solidFill>
           </a:ln>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -3002,6 +3208,28 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>THB bn</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3029,6 +3257,20 @@
             </a:ext>
           </a:extLst>
         </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="10"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
@@ -3053,7 +3295,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000"/>
+            <a:defRPr>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -3098,7 +3342,7 @@
           <a:solidFill>
             <a:srgbClr val="404040"/>
           </a:solidFill>
-          <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -3496,15 +3740,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F168"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="58" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="110" customWidth="1"/>
+    <col min="1" max="1" width="58" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16" style="2" customWidth="1"/>
+    <col min="6" max="6" width="110" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3524,2424 +3769,2424 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>300</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>200</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>100</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>150</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>0.09</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>0.06</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>0.12</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>0.7</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>20</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>0.08</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>7.5</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>0.3</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>0.3</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>10000</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>0.5</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>6.5421000000000007E-2</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>13.3</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>33.521000000000001</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>384881</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>370210</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>1665004</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>3700000</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>60000000</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>65425879</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="3">
         <v>62234693</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>30490635</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>41313439</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3">
         <v>30000000</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="3">
         <v>100058695</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>124033786</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="3">
         <v>956372</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="3">
         <v>30786</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="3">
         <v>719300</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3">
         <v>31581</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3">
         <v>31581</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <v>34743</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <v>71</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <v>80.42</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <v>65.5</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <v>80.400000000000006</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="3">
         <v>24780000</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="3">
         <v>10450000</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="3">
         <v>11689827</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="3">
         <v>9966574</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="3">
         <v>2031</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="3">
         <v>2031</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="3">
         <v>2029</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="2">
         <v>1.92</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="3">
         <v>2028</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="3">
         <v>2020</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="3">
         <v>50900</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="3">
         <v>88512</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3">
         <v>8834</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="3">
         <v>48580</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="3">
         <v>5172.29</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="2">
         <v>9.6</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="2">
         <v>9.4</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="3">
         <v>4000</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="3">
         <v>32974321</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="3">
         <v>35545714</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="3">
         <v>39916251</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="3">
         <v>6725000</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="3">
         <v>1587.2080000000001</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="3">
         <v>1612.6030000000001</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="2">
         <v>59.81</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="2">
         <v>14.198</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="3">
         <v>1400</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="2">
         <v>498</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="2">
         <v>76</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="2">
         <v>6.5</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="2">
         <v>7.7</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="2">
         <v>7.5</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="3">
         <v>8694</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <v>536</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <v>669</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="2">
         <v>939</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="2">
         <v>41</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="2">
         <v>33</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="2">
         <v>26</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="2">
         <v>3.46</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <v>1.25</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <v>5.7</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94" s="3">
         <v>1280</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="2">
         <v>274.7</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96" s="3">
         <v>1734.9</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="3">
         <v>1554.7</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F97" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="3">
         <v>1543.9</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="2">
         <v>498</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="3">
         <v>67000</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="2">
         <v>5.1929999999999996</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="2">
         <v>5.2569999999999997</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="2">
         <v>14.7</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="2">
         <v>11.21</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="2">
         <v>2.3199999999999998E-2</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="2">
         <v>0.2</v>
       </c>
-      <c r="F107" t="s">
+      <c r="F107" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="2">
         <v>0.1</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F108" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F109" t="s">
+      <c r="F109" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="2">
         <v>20</v>
       </c>
-      <c r="F110" t="s">
+      <c r="F110" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="2">
         <v>30</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F111" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="2">
         <v>20</v>
       </c>
-      <c r="F112" t="s">
+      <c r="F112" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="2">
         <v>25</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="2">
         <v>25</v>
       </c>
-      <c r="F114" t="s">
+      <c r="F114" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="2">
         <v>20</v>
       </c>
-      <c r="F115" t="s">
+      <c r="F115" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="2">
         <v>2</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F116" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="2">
         <v>30</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F117" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="2">
         <v>12</v>
       </c>
-      <c r="F118" t="s">
+      <c r="F118" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="2">
         <v>5</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="2">
         <v>5</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F120" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="2">
         <v>15</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F121" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="2">
         <v>1.33</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F122" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="2">
         <v>0.8</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F123" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="2">
         <v>6.5500000000000003E-2</v>
       </c>
-      <c r="F124" t="s">
+      <c r="F124" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="2">
         <v>7.5899999999999995E-2</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="2">
         <v>1</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F126" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="2">
         <v>20</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F127" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="2">
         <v>20</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="3">
         <v>428000</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F129" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130" s="3">
         <v>11153000</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="3">
         <v>28150000</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="2">
         <v>9.5</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F132" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="3">
         <v>6705</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="3">
         <v>1455</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="3">
         <v>18396</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="3">
         <v>1750</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="2">
         <v>0.79</v>
       </c>
-      <c r="F137" t="s">
+      <c r="F137" s="2" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="2">
         <v>4.2694000000000001</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139" s="3">
         <v>3449</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F139" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="2">
         <v>0.65500000000000003</v>
       </c>
-      <c r="F140" t="s">
+      <c r="F140" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="2">
         <v>20</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="2">
         <v>20</v>
       </c>
-      <c r="E141">
+      <c r="E141" s="2">
         <v>25</v>
       </c>
-      <c r="F141" t="s">
+      <c r="F141" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="2">
         <v>2</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="2">
         <v>3</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="2">
         <v>2</v>
       </c>
-      <c r="F142" t="s">
+      <c r="F142" s="2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="2">
         <v>0.08</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="2">
         <v>0.1</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F143" t="s">
+      <c r="F143" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="2">
         <v>7.5</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="2">
         <v>3.46</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="2">
         <v>14.7</v>
       </c>
-      <c r="F144" t="s">
+      <c r="F144" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="2">
         <v>0.59</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="2">
         <v>0.36</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="2">
         <v>0.75</v>
       </c>
-      <c r="F145" t="s">
+      <c r="F145" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="2">
         <v>0.3</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="2">
         <v>0.1</v>
       </c>
-      <c r="E146">
+      <c r="E146" s="2">
         <v>0.5</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F146" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="2">
         <v>0.3</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="2">
         <v>0.5</v>
       </c>
-      <c r="E147">
+      <c r="E147" s="2">
         <v>0.1</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F147" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148" s="3">
         <v>10000</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="3">
         <v>1862</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="3">
         <v>20000</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F148" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="2">
         <v>0.5</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="2">
         <v>0.3</v>
       </c>
-      <c r="E149">
+      <c r="E149" s="2">
         <v>0.7</v>
       </c>
-      <c r="F149" t="s">
+      <c r="F149" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="2">
         <v>6.5421000000000007E-2</v>
       </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="E150">
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" s="2">
         <v>9.0909000000000004E-2</v>
       </c>
-      <c r="F150" t="s">
+      <c r="F150" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="2">
         <v>0.93830000000000002</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="2">
         <v>1.2145999999999999</v>
       </c>
-      <c r="E151">
+      <c r="E151" s="2">
         <v>0.7</v>
       </c>
-      <c r="F151" t="s">
+      <c r="F151" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152" s="3">
         <v>2877</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="3">
         <v>2158</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="3">
         <v>4038</v>
       </c>
-      <c r="F152" t="s">
+      <c r="F152" s="2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="2">
         <v>10.66</v>
       </c>
-      <c r="D153">
+      <c r="D153" s="2">
         <v>12</v>
       </c>
-      <c r="E153">
+      <c r="E153" s="2">
         <v>5</v>
       </c>
-      <c r="F153" t="s">
+      <c r="F153" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="2">
         <v>2</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="2">
         <v>1.5</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="2">
         <v>2.5</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F154" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="2">
         <v>2</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="2">
         <v>2</v>
       </c>
-      <c r="E155">
+      <c r="E155" s="2">
         <v>1</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F155" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156" s="3">
         <v>370210</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="3">
         <v>1000000</v>
       </c>
-      <c r="E156" s="2">
+      <c r="E156" s="3">
         <v>100000</v>
       </c>
-      <c r="F156" t="s">
+      <c r="F156" s="2" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C157">
-        <v>0</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="E157" s="2">
+      <c r="C157" s="2">
+        <v>0</v>
+      </c>
+      <c r="D157" s="2">
+        <v>0</v>
+      </c>
+      <c r="E157" s="3">
         <v>3700000</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F157" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="2">
         <v>0.5</v>
       </c>
-      <c r="D158">
+      <c r="D158" s="2">
         <v>1</v>
       </c>
-      <c r="E158">
-        <v>0</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="E158" s="2">
+        <v>0</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C159" s="2">
+      <c r="C159" s="3">
         <v>31581</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="3">
         <v>31581</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="3">
         <v>31581</v>
       </c>
-      <c r="F159" t="s">
+      <c r="F159" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="2">
         <v>0.80420000000000003</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="2">
         <v>0.80420000000000003</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="2">
         <v>0.80420000000000003</v>
       </c>
-      <c r="F160" t="s">
+      <c r="F160" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="2">
         <v>0.85</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="2">
         <v>0.80420000000000003</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="2">
         <v>0.9</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F161" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="2">
         <f>C3</f>
         <v>200</v>
       </c>
-      <c r="F164" t="s">
+      <c r="F164" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C165">
-        <v>0</v>
-      </c>
-      <c r="F165" t="s">
+      <c r="C165" s="2">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="2">
         <f>C134/C135</f>
         <v>7.9093281148075664E-2</v>
       </c>
-      <c r="F166" t="s">
+      <c r="F166" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="2">
         <f>C107</f>
         <v>0.2</v>
       </c>
-      <c r="F167" t="s">
+      <c r="F167" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="2">
         <f>C127</f>
         <v>20</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F168" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5953,4343 +6198,4345 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V135"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="21" max="22" width="18.6328125" customWidth="1"/>
+    <col min="1" max="1" width="52" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="2" customWidth="1"/>
+    <col min="4" max="5" width="14" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18" style="2" customWidth="1"/>
+    <col min="12" max="15" width="16" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12" style="2" customWidth="1"/>
+    <col min="17" max="18" width="16" style="2" customWidth="1"/>
+    <col min="19" max="19" width="18" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" style="2"/>
+    <col min="21" max="22" width="18.6328125" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <f>Inputs!$C$133/Inputs!$C$84</f>
         <v>0.77122153209109734</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <f>B5</f>
         <v>0.77122153209109734</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <f>Inputs!$C$143</f>
         <v>0.08</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <f>B6</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <f>Inputs!$C$141</f>
         <v>20</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <f>Inputs!$C$142</f>
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <f>B8</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <f>Inputs!$C$164</f>
         <v>200</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <f>Inputs!$C$2</f>
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <f>Inputs!$C$144</f>
         <v>7.5</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <f>B10</f>
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <f>Inputs!$C$145</f>
         <v>0.59</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <f>B11</f>
         <v>0.59</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <f>MIN(Inputs!$C$26/Inputs!$C$155,Inputs!$C$159*365*Inputs!$C$154/Inputs!$C$153)/1000000</f>
         <v>1.85</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <f>B12</f>
         <v>1.85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <f>Inputs!$C$152</f>
         <v>2877</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <f>B13</f>
         <v>2877</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <f>B10-MAX(B10*B11-B12,0)</f>
         <v>4.9250000000000007</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <f>B14</f>
         <v>4.9250000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <f>B14*(B13+B19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <f>B14*(C13+C19*Inputs!$D$148)/1000</f>
         <v>14.169225000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <f>Inputs!$C$165</f>
         <v>0</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <f>B16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <f>Inputs!$C$167</f>
         <v>0.2</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <f>B17</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <f>Inputs!$C$168</f>
         <v>20</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="2">
         <f>B18</f>
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>1</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="6">
         <f>SUM(K41:K63)</f>
         <v>-144.05101535660106</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <f>(C15*(1-C5)-C16*C9)*B27-(C9/B9)*B28</f>
         <v>-259.41977774562076</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="6">
         <f>IF($B$18&lt;$B$7,"n/a",SUM(R41:R63))</f>
         <v>-144.05101535660106</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <f>IF(C18&lt;C7,"n/a",C21)</f>
         <v>-259.41977774562076</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <f>IF($B$18&lt;$B$7,"n/a",IRR(Q41:Q63,-0.1))</f>
         <v>-5.1509439628371956E-2</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="6">
         <f>B15*(1-B5)*B27/(B16*B27+B28/B9)</f>
         <v>50.408560975837332</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <f>B24</f>
         <v>50.408560975837332</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="6">
         <f>B10-B21/((1-B5)*(B13+B19*Inputs!$D$148)/1000*(1-B11)*B27)</f>
         <v>43.147150391637652</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="6">
         <f>B10-C21/((1-C5)*C13/1000*(1-C11)*B27)</f>
         <v>113.24465492439792</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <f>SUMPRODUCT(B41:B63,D41:D63)</f>
         <v>9.0908772291197089</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="6">
         <f>SUMPRODUCT(E41:E63,B41:B63)</f>
         <v>192.59259259259258</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B32" s="2" t="str">
         <f>IF(B18&lt;B7,"No","Yes")</f>
         <v>Yes</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C32" s="2" t="str">
         <f>IF(C18&lt;C7,"No","Yes")</f>
         <v>Yes</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:22" ht="28" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="L40" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M40" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="N40" s="7" t="s">
+      <c r="N40" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="O40" s="7" t="s">
+      <c r="O40" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="P40" s="7" t="s">
+      <c r="P40" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="Q40" s="7" t="s">
+      <c r="Q40" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="R40" s="7" t="s">
+      <c r="R40" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="S40" s="7" t="s">
+      <c r="S40" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="U40" s="10" t="s">
+      <c r="U40" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="V40" s="10" t="s">
+      <c r="V40" s="9" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>0</v>
-      </c>
-      <c r="B41" s="4">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="5">
         <f t="shared" ref="B41:B63" si="0">1/(1+$B$6)^A41</f>
         <v>1</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="2">
         <f t="shared" ref="C41:C63" si="1">IF(A41&lt;$B$8,1,0)</f>
         <v>1</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <f t="shared" ref="D41:D63" si="2">IF(AND(A41&gt;=$B$8,A41&lt;$B$8+$B$7),1,0)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="6">
         <f t="shared" ref="E41:E63" si="3">C41*$B$9/$B$8</f>
         <v>100</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="10">
         <f t="shared" ref="F41:F63" si="4">D41*$B$14</f>
         <v>0</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="6">
         <f>F41*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>0</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="6">
         <f t="shared" ref="H41:H63" si="5">$B$5*G41</f>
         <v>0</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="6">
         <f t="shared" ref="I41:I63" si="6">D41*$B$16*$B$9</f>
         <v>0</v>
       </c>
-      <c r="J41" s="5">
+      <c r="J41" s="6">
         <f t="shared" ref="J41:J63" si="7">G41-H41-E41-I41</f>
         <v>-100</v>
       </c>
-      <c r="K41" s="5">
+      <c r="K41" s="6">
         <f t="shared" ref="K41:K63" si="8">J41*B41</f>
         <v>-100</v>
       </c>
-      <c r="L41" s="5">
+      <c r="L41" s="6">
         <f t="shared" ref="L41:L63" si="9">IF(AND(A41&gt;=$B$8,A41&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="5">
+      <c r="M41" s="6">
         <f t="shared" ref="M41:M63" si="10">G41-H41-L41</f>
         <v>0</v>
       </c>
-      <c r="N41" s="5">
+      <c r="N41" s="6">
         <f>SUM($M$41:M41)</f>
         <v>0</v>
       </c>
-      <c r="O41" s="5">
+      <c r="O41" s="6">
         <f t="shared" ref="O41:O63" si="11">$B$17*MAX(0,N41)</f>
         <v>0</v>
       </c>
-      <c r="P41" s="5">
+      <c r="P41" s="6">
         <f>MAX(0,O41)</f>
         <v>0</v>
       </c>
-      <c r="Q41" s="5">
+      <c r="Q41" s="6">
         <f t="shared" ref="Q41:Q63" si="12">J41-P41</f>
         <v>-100</v>
       </c>
-      <c r="R41" s="5">
+      <c r="R41" s="6">
         <f t="shared" ref="R41:R63" si="13">Q41*B41</f>
         <v>-100</v>
       </c>
-      <c r="S41" s="5">
+      <c r="S41" s="6">
         <f>SUM($Q$41:Q41)</f>
         <v>-100</v>
       </c>
-      <c r="U41" s="5">
+      <c r="U41" s="6">
         <f t="shared" ref="U41:U63" si="14">IF(J41&lt;0,-J41,NA())</f>
         <v>100</v>
       </c>
-      <c r="V41" s="5" t="e">
+      <c r="V41" s="6" t="e">
         <f t="shared" ref="V41:V63" si="15">IF(J41&gt;0,J41,NA())</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
         <v>1</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <f t="shared" si="0"/>
         <v>0.92592592592592582</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="6">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="6">
         <f>F42*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>0</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="6">
         <f t="shared" si="7"/>
         <v>-100</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="6">
         <f t="shared" si="8"/>
         <v>-92.592592592592581</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42" s="6">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="6">
         <f>SUM($M$41:M42)</f>
         <v>0</v>
       </c>
-      <c r="O42" s="5">
+      <c r="O42" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P42" s="5">
+      <c r="P42" s="6">
         <f t="shared" ref="P42:P63" si="16">MAX(0,O42-O41)</f>
         <v>0</v>
       </c>
-      <c r="Q42" s="5">
+      <c r="Q42" s="6">
         <f t="shared" si="12"/>
         <v>-100</v>
       </c>
-      <c r="R42" s="5">
+      <c r="R42" s="6">
         <f t="shared" si="13"/>
         <v>-92.592592592592581</v>
       </c>
-      <c r="S42" s="5">
+      <c r="S42" s="6">
         <f>SUM($Q$41:Q42)</f>
         <v>-200</v>
       </c>
-      <c r="U42" s="5">
+      <c r="U42" s="6">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="V42" s="5" t="e">
+      <c r="V42" s="6" t="e">
         <f t="shared" si="15"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
         <v>2</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <f t="shared" si="0"/>
         <v>0.85733882030178321</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="6">
         <f>F43*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J43" s="5">
+      <c r="J43" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K43" s="6">
         <f t="shared" si="8"/>
         <v>4.5778396863382449</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M43" s="5">
+      <c r="M43" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N43" s="5">
+      <c r="N43" s="6">
         <f>SUM($M$41:M43)</f>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="O43" s="5">
+      <c r="O43" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P43" s="5">
+      <c r="P43" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="Q43" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R43" s="5">
+      <c r="R43" s="6">
         <f t="shared" si="13"/>
         <v>4.5778396863382449</v>
       </c>
-      <c r="S43" s="5">
+      <c r="S43" s="6">
         <f>SUM($Q$41:Q43)</f>
         <v>-194.66040778985507</v>
       </c>
-      <c r="U43" s="5" t="e">
+      <c r="U43" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V43" s="5">
+      <c r="V43" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>3</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <f t="shared" si="0"/>
         <v>0.79383224102016958</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="6">
         <f>F44*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K44" s="6">
         <f t="shared" si="8"/>
         <v>4.2387404503131894</v>
       </c>
-      <c r="L44" s="5">
+      <c r="L44" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M44" s="5">
+      <c r="M44" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N44" s="5">
+      <c r="N44" s="6">
         <f>SUM($M$41:M44)</f>
         <v>-9.3208155797101426</v>
       </c>
-      <c r="O44" s="5">
+      <c r="O44" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P44" s="5">
+      <c r="P44" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q44" s="5">
+      <c r="Q44" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R44" s="5">
+      <c r="R44" s="6">
         <f t="shared" si="13"/>
         <v>4.2387404503131894</v>
       </c>
-      <c r="S44" s="5">
+      <c r="S44" s="6">
         <f>SUM($Q$41:Q44)</f>
         <v>-189.32081557971014</v>
       </c>
-      <c r="U44" s="5" t="e">
+      <c r="U44" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V44" s="5">
+      <c r="V44" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
         <v>4</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <f t="shared" si="0"/>
         <v>0.73502985279645328</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="6">
         <f>F45*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J45" s="5">
+      <c r="J45" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K45" s="5">
+      <c r="K45" s="6">
         <f t="shared" si="8"/>
         <v>3.9247596762159156</v>
       </c>
-      <c r="L45" s="5">
+      <c r="L45" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M45" s="5">
+      <c r="M45" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N45" s="5">
+      <c r="N45" s="6">
         <f>SUM($M$41:M45)</f>
         <v>-13.981223369565214</v>
       </c>
-      <c r="O45" s="5">
+      <c r="O45" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P45" s="5">
+      <c r="P45" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q45" s="5">
+      <c r="Q45" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R45" s="5">
+      <c r="R45" s="6">
         <f t="shared" si="13"/>
         <v>3.9247596762159156</v>
       </c>
-      <c r="S45" s="5">
+      <c r="S45" s="6">
         <f>SUM($Q$41:Q45)</f>
         <v>-183.98122336956521</v>
       </c>
-      <c r="U45" s="5" t="e">
+      <c r="U45" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V45" s="5">
+      <c r="V45" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>5</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <f t="shared" si="0"/>
         <v>0.68058319703375303</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="6">
         <f>F46*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K46" s="5">
+      <c r="K46" s="6">
         <f t="shared" si="8"/>
         <v>3.6340367372369586</v>
       </c>
-      <c r="L46" s="5">
+      <c r="L46" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M46" s="5">
+      <c r="M46" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N46" s="5">
+      <c r="N46" s="6">
         <f>SUM($M$41:M46)</f>
         <v>-18.641631159420285</v>
       </c>
-      <c r="O46" s="5">
+      <c r="O46" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P46" s="5">
+      <c r="P46" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="5">
+      <c r="Q46" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R46" s="5">
+      <c r="R46" s="6">
         <f t="shared" si="13"/>
         <v>3.6340367372369586</v>
       </c>
-      <c r="S46" s="5">
+      <c r="S46" s="6">
         <f>SUM($Q$41:Q46)</f>
         <v>-178.64163115942029</v>
       </c>
-      <c r="U46" s="5" t="e">
+      <c r="U46" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V46" s="5">
+      <c r="V46" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
         <v>6</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <f t="shared" si="0"/>
         <v>0.63016962688310452</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="6">
         <f>F47*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H47" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J47" s="5">
+      <c r="J47" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K47" s="6">
         <f t="shared" si="8"/>
         <v>3.3648488307749611</v>
       </c>
-      <c r="L47" s="5">
+      <c r="L47" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M47" s="5">
+      <c r="M47" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N47" s="5">
+      <c r="N47" s="6">
         <f>SUM($M$41:M47)</f>
         <v>-23.302038949275357</v>
       </c>
-      <c r="O47" s="5">
+      <c r="O47" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P47" s="5">
+      <c r="P47" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="5">
+      <c r="Q47" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R47" s="5">
+      <c r="R47" s="6">
         <f t="shared" si="13"/>
         <v>3.3648488307749611</v>
       </c>
-      <c r="S47" s="5">
+      <c r="S47" s="6">
         <f>SUM($Q$41:Q47)</f>
         <v>-173.30203894927536</v>
       </c>
-      <c r="U47" s="5" t="e">
+      <c r="U47" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V47" s="5">
+      <c r="V47" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
         <v>7</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="5">
         <f t="shared" si="0"/>
         <v>0.58349039526213387</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="6">
         <f>F48*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H48" s="5">
+      <c r="H48" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K48" s="5">
+      <c r="K48" s="6">
         <f t="shared" si="8"/>
         <v>3.1156007692360754</v>
       </c>
-      <c r="L48" s="5">
+      <c r="L48" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M48" s="5">
+      <c r="M48" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N48" s="5">
+      <c r="N48" s="6">
         <f>SUM($M$41:M48)</f>
         <v>-27.962446739130428</v>
       </c>
-      <c r="O48" s="5">
+      <c r="O48" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P48" s="5">
+      <c r="P48" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="5">
+      <c r="Q48" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R48" s="5">
+      <c r="R48" s="6">
         <f t="shared" si="13"/>
         <v>3.1156007692360754</v>
       </c>
-      <c r="S48" s="5">
+      <c r="S48" s="6">
         <f>SUM($Q$41:Q48)</f>
         <v>-167.96244673913043</v>
       </c>
-      <c r="U48" s="5" t="e">
+      <c r="U48" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V48" s="5">
+      <c r="V48" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
         <v>8</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="5">
         <f t="shared" si="0"/>
         <v>0.54026888450197574</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="6">
         <f>F49*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H49" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J49" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K49" s="5">
+      <c r="K49" s="6">
         <f t="shared" si="8"/>
         <v>2.8848155270704399</v>
       </c>
-      <c r="L49" s="5">
+      <c r="L49" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M49" s="5">
+      <c r="M49" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N49" s="5">
+      <c r="N49" s="6">
         <f>SUM($M$41:M49)</f>
         <v>-32.622854528985499</v>
       </c>
-      <c r="O49" s="5">
+      <c r="O49" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P49" s="5">
+      <c r="P49" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q49" s="5">
+      <c r="Q49" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R49" s="5">
+      <c r="R49" s="6">
         <f t="shared" si="13"/>
         <v>2.8848155270704399</v>
       </c>
-      <c r="S49" s="5">
+      <c r="S49" s="6">
         <f>SUM($Q$41:Q49)</f>
         <v>-162.6228545289855</v>
       </c>
-      <c r="U49" s="5" t="e">
+      <c r="U49" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V49" s="5">
+      <c r="V49" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A50">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
         <v>9</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="5">
         <f t="shared" si="0"/>
         <v>0.50024896713145905</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="6">
         <f>F50*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H50" s="5">
+      <c r="H50" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J50" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K50" s="5">
+      <c r="K50" s="6">
         <f t="shared" si="8"/>
         <v>2.6711254880281854</v>
       </c>
-      <c r="L50" s="5">
+      <c r="L50" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M50" s="5">
+      <c r="M50" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N50" s="5">
+      <c r="N50" s="6">
         <f>SUM($M$41:M50)</f>
         <v>-37.283262318840571</v>
       </c>
-      <c r="O50" s="5">
+      <c r="O50" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="5">
+      <c r="Q50" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R50" s="5">
+      <c r="R50" s="6">
         <f t="shared" si="13"/>
         <v>2.6711254880281854</v>
       </c>
-      <c r="S50" s="5">
+      <c r="S50" s="6">
         <f>SUM($Q$41:Q50)</f>
         <v>-157.28326231884057</v>
       </c>
-      <c r="U50" s="5" t="e">
+      <c r="U50" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V50" s="5">
+      <c r="V50" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A51">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
         <v>10</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="5">
         <f t="shared" si="0"/>
         <v>0.46319348808468425</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="6">
         <f>F51*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H51" s="5">
+      <c r="H51" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J51" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K51" s="5">
+      <c r="K51" s="6">
         <f t="shared" si="8"/>
         <v>2.4732643407668378</v>
       </c>
-      <c r="L51" s="5">
+      <c r="L51" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M51" s="5">
+      <c r="M51" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N51" s="5">
+      <c r="N51" s="6">
         <f>SUM($M$41:M51)</f>
         <v>-41.943670108695642</v>
       </c>
-      <c r="O51" s="5">
+      <c r="O51" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P51" s="5">
+      <c r="P51" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q51" s="5">
+      <c r="Q51" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R51" s="5">
+      <c r="R51" s="6">
         <f t="shared" si="13"/>
         <v>2.4732643407668378</v>
       </c>
-      <c r="S51" s="5">
+      <c r="S51" s="6">
         <f>SUM($Q$41:Q51)</f>
         <v>-151.94367010869564</v>
       </c>
-      <c r="U51" s="5" t="e">
+      <c r="U51" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V51" s="5">
+      <c r="V51" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A52">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
         <v>11</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="5">
         <f t="shared" si="0"/>
         <v>0.42888285933767062</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="6">
         <f>F52*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H52" s="5">
+      <c r="H52" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J52" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K52" s="5">
+      <c r="K52" s="6">
         <f t="shared" si="8"/>
         <v>2.290059574784109</v>
       </c>
-      <c r="L52" s="5">
+      <c r="L52" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M52" s="5">
+      <c r="M52" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N52" s="5">
+      <c r="N52" s="6">
         <f>SUM($M$41:M52)</f>
         <v>-46.604077898550713</v>
       </c>
-      <c r="O52" s="5">
+      <c r="O52" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P52" s="5">
+      <c r="P52" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q52" s="5">
+      <c r="Q52" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R52" s="5">
+      <c r="R52" s="6">
         <f t="shared" si="13"/>
         <v>2.290059574784109</v>
       </c>
-      <c r="S52" s="5">
+      <c r="S52" s="6">
         <f>SUM($Q$41:Q52)</f>
         <v>-146.60407789855071</v>
       </c>
-      <c r="U52" s="5" t="e">
+      <c r="U52" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V52" s="5">
+      <c r="V52" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A53">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
         <v>12</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="5">
         <f t="shared" si="0"/>
         <v>0.39711375864599124</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="6">
         <f>F53*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H53" s="5">
+      <c r="H53" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J53" s="5">
+      <c r="J53" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K53" s="5">
+      <c r="K53" s="6">
         <f t="shared" si="8"/>
         <v>2.1204255322075083</v>
       </c>
-      <c r="L53" s="5">
+      <c r="L53" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M53" s="5">
+      <c r="M53" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N53" s="5">
+      <c r="N53" s="6">
         <f>SUM($M$41:M53)</f>
         <v>-51.264485688405784</v>
       </c>
-      <c r="O53" s="5">
+      <c r="O53" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P53" s="5">
+      <c r="P53" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q53" s="5">
+      <c r="Q53" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R53" s="5">
+      <c r="R53" s="6">
         <f t="shared" si="13"/>
         <v>2.1204255322075083</v>
       </c>
-      <c r="S53" s="5">
+      <c r="S53" s="6">
         <f>SUM($Q$41:Q53)</f>
         <v>-141.26448568840578</v>
       </c>
-      <c r="U53" s="5" t="e">
+      <c r="U53" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V53" s="5">
+      <c r="V53" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
         <v>13</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="5">
         <f t="shared" si="0"/>
         <v>0.36769792467221413</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="6">
         <f>F54*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H54" s="5">
+      <c r="H54" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J54" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K54" s="5">
+      <c r="K54" s="6">
         <f t="shared" si="8"/>
         <v>1.9633569742662114</v>
       </c>
-      <c r="L54" s="5">
+      <c r="L54" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M54" s="5">
+      <c r="M54" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N54" s="5">
+      <c r="N54" s="6">
         <f>SUM($M$41:M54)</f>
         <v>-55.924893478260856</v>
       </c>
-      <c r="O54" s="5">
+      <c r="O54" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P54" s="5">
+      <c r="P54" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q54" s="5">
+      <c r="Q54" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R54" s="5">
+      <c r="R54" s="6">
         <f t="shared" si="13"/>
         <v>1.9633569742662114</v>
       </c>
-      <c r="S54" s="5">
+      <c r="S54" s="6">
         <f>SUM($Q$41:Q54)</f>
         <v>-135.92489347826086</v>
       </c>
-      <c r="U54" s="5" t="e">
+      <c r="U54" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V54" s="5">
+      <c r="V54" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
         <v>14</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="5">
         <f t="shared" si="0"/>
         <v>0.34046104136316119</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="6">
         <f>F55*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H55" s="5">
+      <c r="H55" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J55" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K55" s="5">
+      <c r="K55" s="6">
         <f t="shared" si="8"/>
         <v>1.8179231243205658</v>
       </c>
-      <c r="L55" s="5">
+      <c r="L55" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M55" s="5">
+      <c r="M55" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N55" s="5">
+      <c r="N55" s="6">
         <f>SUM($M$41:M55)</f>
         <v>-60.585301268115927</v>
       </c>
-      <c r="O55" s="5">
+      <c r="O55" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P55" s="5">
+      <c r="P55" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q55" s="5">
+      <c r="Q55" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R55" s="5">
+      <c r="R55" s="6">
         <f t="shared" si="13"/>
         <v>1.8179231243205658</v>
       </c>
-      <c r="S55" s="5">
+      <c r="S55" s="6">
         <f>SUM($Q$41:Q55)</f>
         <v>-130.58530126811593</v>
       </c>
-      <c r="U55" s="5" t="e">
+      <c r="U55" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V55" s="5">
+      <c r="V55" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
         <v>15</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="5">
         <f t="shared" si="0"/>
         <v>0.31524170496588994</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="6">
         <f>F56*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H56" s="5">
+      <c r="H56" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J56" s="5">
+      <c r="J56" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K56" s="5">
+      <c r="K56" s="6">
         <f t="shared" si="8"/>
         <v>1.6832621521486717</v>
       </c>
-      <c r="L56" s="5">
+      <c r="L56" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M56" s="5">
+      <c r="M56" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N56" s="5">
+      <c r="N56" s="6">
         <f>SUM($M$41:M56)</f>
         <v>-65.245709057970998</v>
       </c>
-      <c r="O56" s="5">
+      <c r="O56" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P56" s="5">
+      <c r="P56" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q56" s="5">
+      <c r="Q56" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R56" s="5">
+      <c r="R56" s="6">
         <f t="shared" si="13"/>
         <v>1.6832621521486717</v>
       </c>
-      <c r="S56" s="5">
+      <c r="S56" s="6">
         <f>SUM($Q$41:Q56)</f>
         <v>-125.245709057971</v>
       </c>
-      <c r="U56" s="5" t="e">
+      <c r="U56" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V56" s="5">
+      <c r="V56" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A57">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
         <v>16</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="5">
         <f t="shared" si="0"/>
         <v>0.29189046756100923</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="6">
         <f>F57*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H57" s="5">
+      <c r="H57" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J57" s="5">
+      <c r="J57" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K57" s="5">
+      <c r="K57" s="6">
         <f t="shared" si="8"/>
         <v>1.5585760668043258</v>
       </c>
-      <c r="L57" s="5">
+      <c r="L57" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M57" s="5">
+      <c r="M57" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N57" s="5">
+      <c r="N57" s="6">
         <f>SUM($M$41:M57)</f>
         <v>-69.90611684782607</v>
       </c>
-      <c r="O57" s="5">
+      <c r="O57" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P57" s="5">
+      <c r="P57" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q57" s="5">
+      <c r="Q57" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R57" s="5">
+      <c r="R57" s="6">
         <f t="shared" si="13"/>
         <v>1.5585760668043258</v>
       </c>
-      <c r="S57" s="5">
+      <c r="S57" s="6">
         <f>SUM($Q$41:Q57)</f>
         <v>-119.90611684782607</v>
       </c>
-      <c r="U57" s="5" t="e">
+      <c r="U57" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V57" s="5">
+      <c r="V57" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A58">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
         <v>17</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="5">
         <f t="shared" si="0"/>
         <v>0.27026895144537894</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="6">
         <f>F58*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H58" s="5">
+      <c r="H58" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J58" s="5">
+      <c r="J58" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K58" s="5">
+      <c r="K58" s="6">
         <f t="shared" si="8"/>
         <v>1.4431259877817832</v>
       </c>
-      <c r="L58" s="5">
+      <c r="L58" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M58" s="5">
+      <c r="M58" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N58" s="5">
+      <c r="N58" s="6">
         <f>SUM($M$41:M58)</f>
         <v>-74.566524637681141</v>
       </c>
-      <c r="O58" s="5">
+      <c r="O58" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P58" s="5">
+      <c r="P58" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q58" s="5">
+      <c r="Q58" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R58" s="5">
+      <c r="R58" s="6">
         <f t="shared" si="13"/>
         <v>1.4431259877817832</v>
       </c>
-      <c r="S58" s="5">
+      <c r="S58" s="6">
         <f>SUM($Q$41:Q58)</f>
         <v>-114.56652463768114</v>
       </c>
-      <c r="U58" s="5" t="e">
+      <c r="U58" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V58" s="5">
+      <c r="V58" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A59">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
         <v>18</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="5">
         <f t="shared" si="0"/>
         <v>0.25024902911609154</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="6">
         <f>F59*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H59" s="5">
+      <c r="H59" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K59" s="5">
+      <c r="K59" s="6">
         <f t="shared" si="8"/>
         <v>1.3362277664646138</v>
       </c>
-      <c r="L59" s="5">
+      <c r="L59" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M59" s="5">
+      <c r="M59" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N59" s="5">
+      <c r="N59" s="6">
         <f>SUM($M$41:M59)</f>
         <v>-79.226932427536212</v>
       </c>
-      <c r="O59" s="5">
+      <c r="O59" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P59" s="5">
+      <c r="P59" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q59" s="5">
+      <c r="Q59" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R59" s="5">
+      <c r="R59" s="6">
         <f t="shared" si="13"/>
         <v>1.3362277664646138</v>
       </c>
-      <c r="S59" s="5">
+      <c r="S59" s="6">
         <f>SUM($Q$41:Q59)</f>
         <v>-109.22693242753621</v>
       </c>
-      <c r="U59" s="5" t="e">
+      <c r="U59" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V59" s="5">
+      <c r="V59" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A60">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
         <v>19</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="5">
         <f t="shared" si="0"/>
         <v>0.23171206399638106</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="6">
         <f>F60*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H60" s="5">
+      <c r="H60" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K60" s="6">
         <f t="shared" si="8"/>
         <v>1.2372479319116796</v>
       </c>
-      <c r="L60" s="5">
+      <c r="L60" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M60" s="5">
+      <c r="M60" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N60" s="5">
+      <c r="N60" s="6">
         <f>SUM($M$41:M60)</f>
         <v>-83.887340217391284</v>
       </c>
-      <c r="O60" s="5">
+      <c r="O60" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P60" s="5">
+      <c r="P60" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q60" s="5">
+      <c r="Q60" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R60" s="5">
+      <c r="R60" s="6">
         <f t="shared" si="13"/>
         <v>1.2372479319116796</v>
       </c>
-      <c r="S60" s="5">
+      <c r="S60" s="6">
         <f>SUM($Q$41:Q60)</f>
         <v>-103.88734021739128</v>
       </c>
-      <c r="U60" s="5" t="e">
+      <c r="U60" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V60" s="5">
+      <c r="V60" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A61">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
         <v>20</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="5">
         <f t="shared" si="0"/>
         <v>0.21454820740405653</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="6">
         <f>F61*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H61" s="5">
+      <c r="H61" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K61" s="5">
+      <c r="K61" s="6">
         <f t="shared" si="8"/>
         <v>1.1455999369552587</v>
       </c>
-      <c r="L61" s="5">
+      <c r="L61" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M61" s="5">
+      <c r="M61" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N61" s="5">
+      <c r="N61" s="6">
         <f>SUM($M$41:M61)</f>
         <v>-88.547748007246355</v>
       </c>
-      <c r="O61" s="5">
+      <c r="O61" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P61" s="5">
+      <c r="P61" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="5">
+      <c r="Q61" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R61" s="5">
+      <c r="R61" s="6">
         <f t="shared" si="13"/>
         <v>1.1455999369552587</v>
       </c>
-      <c r="S61" s="5">
+      <c r="S61" s="6">
         <f>SUM($Q$41:Q61)</f>
         <v>-98.547748007246355</v>
       </c>
-      <c r="U61" s="5" t="e">
+      <c r="U61" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V61" s="5">
+      <c r="V61" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A62">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
         <v>21</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="5">
         <f t="shared" si="0"/>
         <v>0.19865574759634863</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="10">
         <f t="shared" si="4"/>
         <v>4.9250000000000007</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="6">
         <f>F62*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="H62" s="5">
+      <c r="H62" s="6">
         <f t="shared" si="5"/>
         <v>17.999982789855075</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="6">
         <f t="shared" si="7"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="K62" s="5">
+      <c r="K62" s="6">
         <f t="shared" si="8"/>
         <v>1.0607406823659802</v>
       </c>
-      <c r="L62" s="5">
+      <c r="L62" s="6">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="M62" s="5">
+      <c r="M62" s="6">
         <f t="shared" si="10"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="N62" s="5">
+      <c r="N62" s="6">
         <f>SUM($M$41:M62)</f>
         <v>-93.208155797101426</v>
       </c>
-      <c r="O62" s="5">
+      <c r="O62" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P62" s="5">
+      <c r="P62" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q62" s="5">
+      <c r="Q62" s="6">
         <f t="shared" si="12"/>
         <v>5.3395922101449287</v>
       </c>
-      <c r="R62" s="5">
+      <c r="R62" s="6">
         <f t="shared" si="13"/>
         <v>1.0607406823659802</v>
       </c>
-      <c r="S62" s="5">
+      <c r="S62" s="6">
         <f>SUM($Q$41:Q62)</f>
         <v>-93.208155797101426</v>
       </c>
-      <c r="U62" s="5" t="e">
+      <c r="U62" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V62" s="5">
+      <c r="V62" s="6">
         <f t="shared" si="15"/>
         <v>5.3395922101449287</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A63">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
         <v>22</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="5">
         <f t="shared" si="0"/>
         <v>0.18394050703365611</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="6">
         <f>F63*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>0</v>
       </c>
-      <c r="H63" s="5">
+      <c r="H63" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="6">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K63" s="5">
+      <c r="K63" s="6">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L63" s="5">
+      <c r="L63" s="6">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M63" s="5">
+      <c r="M63" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N63" s="5">
+      <c r="N63" s="6">
         <f>SUM($M$41:M63)</f>
         <v>-93.208155797101426</v>
       </c>
-      <c r="O63" s="5">
+      <c r="O63" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P63" s="5">
+      <c r="P63" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="Q63" s="5">
+      <c r="Q63" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R63" s="5">
+      <c r="R63" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S63" s="5">
+      <c r="S63" s="6">
         <f>SUM($Q$41:Q63)</f>
         <v>-93.208155797101426</v>
       </c>
-      <c r="U63" s="5" t="e">
+      <c r="U63" s="6" t="e">
         <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
-      <c r="V63" s="5" t="e">
+      <c r="V63" s="6" t="e">
         <f t="shared" si="15"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="7" t="s">
+    <row r="67" spans="1:14" ht="28" x14ac:dyDescent="0.3">
+      <c r="A67" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I67" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="J67" s="7" t="s">
+      <c r="J67" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="K67" s="7" t="s">
+      <c r="K67" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="L67" s="7" t="s">
+      <c r="L67" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="M67" s="7" t="s">
+      <c r="M67" s="8" t="s">
         <v>371</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="2">
         <v>1</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="2">
         <v>1</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <v>1</v>
       </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68" s="4">
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5">
         <f t="shared" ref="F68:F94" si="17">SUMPRODUCT($B$41:$B$63*($A$41:$A$63&gt;=$B$8+E68)*($A$41:$A$63&lt;$B$8+E68+$B$7))</f>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="6">
         <f t="shared" ref="G68:G94" si="18">(D68-C68*$B$5)*$B$15*F68-B68*$B$28-I68*B68*$B$9*F68</f>
         <v>-144.05101535660108</v>
       </c>
-      <c r="H68" s="5">
+      <c r="H68" s="6">
         <f t="shared" ref="H68:H94" si="19">(D68-C68*$B$5)*$C$15*F68-B68*($C$9/$B$9)*$B$28-I68*B68*$C$9*F68</f>
         <v>-259.41977774562076</v>
       </c>
-      <c r="I68" s="4">
+      <c r="I68" s="5">
         <f t="shared" ref="I68:I93" si="20">$B$16</f>
         <v>0</v>
       </c>
-      <c r="J68" s="5">
+      <c r="J68" s="6">
         <f t="shared" ref="J68:J94" si="21">D68*$B$15-C68*$B$5*$B$15-B68*$B$9/$B$18</f>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="K68" s="5">
+      <c r="K68" s="6">
         <f t="shared" ref="K68:K94" si="22">IF($B$18&lt;$B$7,"n/a",G68-$B$17*MAX(0,J68)*F68)</f>
         <v>-144.05101535660108</v>
       </c>
-      <c r="L68" s="5">
+      <c r="L68" s="6">
         <f t="shared" ref="L68:L94" si="23">D68*$C$15-C68*$B$5*$C$15-B68*$C$9/$C$18</f>
         <v>-11.758386413043478</v>
       </c>
-      <c r="M68" s="5">
+      <c r="M68" s="6">
         <f t="shared" ref="M68:M94" si="24">IF($C$18&lt;$C$7,"n/a",H68-$B$17*MAX(0,L68)*F68)</f>
         <v>-259.41977774562076</v>
       </c>
-      <c r="N68" t="s">
+      <c r="N68" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="2">
         <v>1.05</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="2">
         <v>1</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <v>1</v>
       </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69" s="4">
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="6">
         <f t="shared" si="18"/>
         <v>-153.68064498623073</v>
       </c>
-      <c r="H69" s="5">
+      <c r="H69" s="6">
         <f t="shared" si="19"/>
         <v>-273.86422219006528</v>
       </c>
-      <c r="I69" s="4">
+      <c r="I69" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="6">
         <f t="shared" si="21"/>
         <v>-5.1604077898550713</v>
       </c>
-      <c r="K69" s="5">
+      <c r="K69" s="6">
         <f t="shared" si="22"/>
         <v>-153.68064498623073</v>
       </c>
-      <c r="L69" s="5">
+      <c r="L69" s="6">
         <f t="shared" si="23"/>
         <v>-12.508386413043478</v>
       </c>
-      <c r="M69" s="5">
+      <c r="M69" s="6">
         <f t="shared" si="24"/>
         <v>-273.86422219006528</v>
       </c>
-      <c r="N69" t="s">
+      <c r="N69" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="2">
         <v>0.95</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="2">
         <v>1</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <v>1</v>
       </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70" s="4">
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="6">
         <f t="shared" si="18"/>
         <v>-134.42138572697144</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H70" s="6">
         <f t="shared" si="19"/>
         <v>-244.97533330117631</v>
       </c>
-      <c r="I70" s="4">
+      <c r="I70" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="6">
         <f t="shared" si="21"/>
         <v>-4.1604077898550713</v>
       </c>
-      <c r="K70" s="5">
+      <c r="K70" s="6">
         <f t="shared" si="22"/>
         <v>-134.42138572697144</v>
       </c>
-      <c r="L70" s="5">
+      <c r="L70" s="6">
         <f t="shared" si="23"/>
         <v>-11.008386413043478</v>
       </c>
-      <c r="M70" s="5">
+      <c r="M70" s="6">
         <f t="shared" si="24"/>
         <v>-244.97533330117631</v>
       </c>
-      <c r="N70" t="s">
+      <c r="N70" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="2">
         <v>1</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <v>1</v>
       </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4">
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="6">
         <f t="shared" si="18"/>
         <v>-163.31027461586035</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H71" s="6">
         <f t="shared" si="19"/>
         <v>-288.30866663450968</v>
       </c>
-      <c r="I71" s="4">
+      <c r="I71" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="6">
         <f t="shared" si="21"/>
         <v>-5.6604077898550731</v>
       </c>
-      <c r="K71" s="5">
+      <c r="K71" s="6">
         <f t="shared" si="22"/>
         <v>-163.31027461586035</v>
       </c>
-      <c r="L71" s="5">
+      <c r="L71" s="6">
         <f t="shared" si="23"/>
         <v>-13.258386413043478</v>
       </c>
-      <c r="M71" s="5">
+      <c r="M71" s="6">
         <f t="shared" si="24"/>
         <v>-288.30866663450968</v>
       </c>
-      <c r="N71" t="s">
+      <c r="N71" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="2">
         <v>0.9</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="2">
         <v>1</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="2">
         <v>1</v>
       </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4">
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="6">
         <f t="shared" si="18"/>
         <v>-124.79175609734182</v>
       </c>
-      <c r="H72" s="5">
+      <c r="H72" s="6">
         <f t="shared" si="19"/>
         <v>-230.53088885673191</v>
       </c>
-      <c r="I72" s="4">
+      <c r="I72" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="6">
         <f t="shared" si="21"/>
         <v>-3.6604077898550713</v>
       </c>
-      <c r="K72" s="5">
+      <c r="K72" s="6">
         <f t="shared" si="22"/>
         <v>-124.79175609734182</v>
       </c>
-      <c r="L72" s="5">
+      <c r="L72" s="6">
         <f t="shared" si="23"/>
         <v>-10.258386413043478</v>
       </c>
-      <c r="M72" s="5">
+      <c r="M72" s="6">
         <f t="shared" si="24"/>
         <v>-230.53088885673191</v>
       </c>
-      <c r="N72" t="s">
+      <c r="N72" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="2">
         <v>1.2</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="2">
         <v>1</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>1</v>
       </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73" s="4">
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="6">
         <f t="shared" si="18"/>
         <v>-182.56953387511959</v>
       </c>
-      <c r="H73" s="5">
+      <c r="H73" s="6">
         <f t="shared" si="19"/>
         <v>-317.19755552339853</v>
       </c>
-      <c r="I73" s="4">
+      <c r="I73" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J73" s="5">
+      <c r="J73" s="6">
         <f t="shared" si="21"/>
         <v>-6.6604077898550713</v>
       </c>
-      <c r="K73" s="5">
+      <c r="K73" s="6">
         <f t="shared" si="22"/>
         <v>-182.56953387511959</v>
       </c>
-      <c r="L73" s="5">
+      <c r="L73" s="6">
         <f t="shared" si="23"/>
         <v>-14.758386413043478</v>
       </c>
-      <c r="M73" s="5">
+      <c r="M73" s="6">
         <f t="shared" si="24"/>
         <v>-317.19755552339853</v>
       </c>
-      <c r="N73" t="s">
+      <c r="N73" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="2">
         <v>0.8</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="2">
         <v>1</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="2">
         <v>1</v>
       </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74" s="4">
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="6">
         <f t="shared" si="18"/>
         <v>-105.53249683808258</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H74" s="6">
         <f t="shared" si="19"/>
         <v>-201.64199996784305</v>
       </c>
-      <c r="I74" s="4">
+      <c r="I74" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J74" s="5">
+      <c r="J74" s="6">
         <f t="shared" si="21"/>
         <v>-2.6604077898550713</v>
       </c>
-      <c r="K74" s="5">
+      <c r="K74" s="6">
         <f t="shared" si="22"/>
         <v>-105.53249683808258</v>
       </c>
-      <c r="L74" s="5">
+      <c r="L74" s="6">
         <f t="shared" si="23"/>
         <v>-8.7583864130434783</v>
       </c>
-      <c r="M74" s="5">
+      <c r="M74" s="6">
         <f t="shared" si="24"/>
         <v>-201.64199996784305</v>
       </c>
-      <c r="N74" t="s">
+      <c r="N74" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="2">
         <v>1</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="2">
         <v>1.05</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="2">
         <v>1</v>
       </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75" s="4">
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G75" s="5">
+      <c r="G75" s="6">
         <f t="shared" si="18"/>
         <v>-152.2327970400431</v>
       </c>
-      <c r="H75" s="5">
+      <c r="H75" s="6">
         <f t="shared" si="19"/>
         <v>-264.38685643379603</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I75" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J75" s="5">
+      <c r="J75" s="6">
         <f t="shared" si="21"/>
         <v>-5.5604069293478275</v>
       </c>
-      <c r="K75" s="5">
+      <c r="K75" s="6">
         <f t="shared" si="22"/>
         <v>-152.2327970400431</v>
       </c>
-      <c r="L75" s="5">
+      <c r="L75" s="6">
         <f t="shared" si="23"/>
         <v>-12.304766983695652</v>
       </c>
-      <c r="M75" s="5">
+      <c r="M75" s="6">
         <f t="shared" si="24"/>
         <v>-264.38685643379603</v>
       </c>
-      <c r="N75" t="s">
+      <c r="N75" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="2">
         <v>1</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="2">
         <v>0.95</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>1</v>
       </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4">
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="6">
         <f t="shared" si="18"/>
         <v>-135.86923367315907</v>
       </c>
-      <c r="H76" s="5">
+      <c r="H76" s="6">
         <f t="shared" si="19"/>
         <v>-254.45269905744547</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J76" s="5">
+      <c r="J76" s="6">
         <f t="shared" si="21"/>
         <v>-3.7604086503623186</v>
       </c>
-      <c r="K76" s="5">
+      <c r="K76" s="6">
         <f t="shared" si="22"/>
         <v>-135.86923367315907</v>
       </c>
-      <c r="L76" s="5">
+      <c r="L76" s="6">
         <f t="shared" si="23"/>
         <v>-11.212005842391305</v>
       </c>
-      <c r="M76" s="5">
+      <c r="M76" s="6">
         <f t="shared" si="24"/>
         <v>-254.45269905744547</v>
       </c>
-      <c r="N76" t="s">
+      <c r="N76" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="2">
         <v>1</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="2">
         <v>1</v>
       </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4">
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G77" s="6">
         <f t="shared" si="18"/>
         <v>-160.41457872348511</v>
       </c>
-      <c r="H77" s="5">
+      <c r="H77" s="6">
         <f t="shared" si="19"/>
         <v>-269.35393512197129</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J77" s="5">
+      <c r="J77" s="6">
         <f t="shared" si="21"/>
         <v>-6.4604060688405802</v>
       </c>
-      <c r="K77" s="5">
+      <c r="K77" s="6">
         <f t="shared" si="22"/>
         <v>-160.41457872348511</v>
       </c>
-      <c r="L77" s="5">
+      <c r="L77" s="6">
         <f t="shared" si="23"/>
         <v>-12.851147554347827</v>
       </c>
-      <c r="M77" s="5">
+      <c r="M77" s="6">
         <f t="shared" si="24"/>
         <v>-269.35393512197129</v>
       </c>
-      <c r="N77" t="s">
+      <c r="N77" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="2">
         <v>1</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="2">
         <v>0.9</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>1</v>
       </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78" s="4">
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G78" s="6">
         <f t="shared" si="18"/>
         <v>-127.68745198971706</v>
       </c>
-      <c r="H78" s="5">
+      <c r="H78" s="6">
         <f t="shared" si="19"/>
         <v>-249.48562036927018</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J78" s="5">
+      <c r="J78" s="6">
         <f t="shared" si="21"/>
         <v>-2.860409510869566</v>
       </c>
-      <c r="K78" s="5">
+      <c r="K78" s="6">
         <f t="shared" si="22"/>
         <v>-127.68745198971706</v>
       </c>
-      <c r="L78" s="5">
+      <c r="L78" s="6">
         <f t="shared" si="23"/>
         <v>-10.665625271739129</v>
       </c>
-      <c r="M78" s="5">
+      <c r="M78" s="6">
         <f t="shared" si="24"/>
         <v>-249.48562036927018</v>
       </c>
-      <c r="N78" t="s">
+      <c r="N78" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="2">
         <v>1</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="2">
         <v>1.2</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="2">
         <v>1</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79" s="4">
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="6">
         <f t="shared" si="18"/>
         <v>-176.7781420903691</v>
       </c>
-      <c r="H79" s="5">
+      <c r="H79" s="6">
         <f t="shared" si="19"/>
         <v>-279.28809249832187</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J79" s="5">
+      <c r="J79" s="6">
         <f t="shared" si="21"/>
         <v>-8.2604043478260856</v>
       </c>
-      <c r="K79" s="5">
+      <c r="K79" s="6">
         <f t="shared" si="22"/>
         <v>-176.7781420903691</v>
       </c>
-      <c r="L79" s="5">
+      <c r="L79" s="6">
         <f t="shared" si="23"/>
         <v>-13.943908695652173</v>
       </c>
-      <c r="M79" s="5">
+      <c r="M79" s="6">
         <f t="shared" si="24"/>
         <v>-279.28809249832187</v>
       </c>
-      <c r="N79" t="s">
+      <c r="N79" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="2">
         <v>1</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="2">
         <v>0.8</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="2">
         <v>1</v>
       </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80" s="4">
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G80" s="6">
         <f t="shared" si="18"/>
         <v>-111.32388862283307</v>
       </c>
-      <c r="H80" s="5">
+      <c r="H80" s="6">
         <f t="shared" si="19"/>
         <v>-239.55146299291965</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J80" s="5">
+      <c r="J80" s="6">
         <f t="shared" si="21"/>
         <v>-1.0604112318840588</v>
       </c>
-      <c r="K80" s="5">
+      <c r="K80" s="6">
         <f t="shared" si="22"/>
         <v>-111.32388862283307</v>
       </c>
-      <c r="L80" s="5">
+      <c r="L80" s="6">
         <f t="shared" si="23"/>
         <v>-9.5728641304347821</v>
       </c>
-      <c r="M80" s="5">
+      <c r="M80" s="6">
         <f t="shared" si="24"/>
         <v>-239.55146299291965</v>
       </c>
-      <c r="N80" t="s">
+      <c r="N80" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="2">
         <v>1</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="2">
         <v>1</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="2">
         <v>1.05</v>
       </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81" s="4">
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G81" s="5">
+      <c r="G81" s="6">
         <f t="shared" si="18"/>
         <v>-133.4421548113595</v>
       </c>
-      <c r="H81" s="5">
+      <c r="H81" s="6">
         <f t="shared" si="19"/>
         <v>-252.97924350028205</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J81" s="5">
+      <c r="J81" s="6">
         <f t="shared" si="21"/>
         <v>-3.4934290398550694</v>
       </c>
-      <c r="K81" s="5">
+      <c r="K81" s="6">
         <f t="shared" si="22"/>
         <v>-133.4421548113595</v>
       </c>
-      <c r="L81" s="5">
+      <c r="L81" s="6">
         <f t="shared" si="23"/>
         <v>-11.049925163043477</v>
       </c>
-      <c r="M81" s="5">
+      <c r="M81" s="6">
         <f t="shared" si="24"/>
         <v>-252.97924350028205</v>
       </c>
-      <c r="N81" t="s">
+      <c r="N81" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="2">
         <v>1</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="2">
         <v>1</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>0.95</v>
       </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82" s="4">
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G82" s="5">
+      <c r="G82" s="6">
         <f t="shared" si="18"/>
         <v>-154.65987590184267</v>
       </c>
-      <c r="H82" s="5">
+      <c r="H82" s="6">
         <f t="shared" si="19"/>
         <v>-265.86031199095942</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J82" s="5">
+      <c r="J82" s="6">
         <f t="shared" si="21"/>
         <v>-5.8273865398550733</v>
       </c>
-      <c r="K82" s="5">
+      <c r="K82" s="6">
         <f t="shared" si="22"/>
         <v>-154.65987590184267</v>
       </c>
-      <c r="L82" s="5">
+      <c r="L82" s="6">
         <f t="shared" si="23"/>
         <v>-12.466847663043479</v>
       </c>
-      <c r="M82" s="5">
+      <c r="M82" s="6">
         <f t="shared" si="24"/>
         <v>-265.86031199095942</v>
       </c>
-      <c r="N82" t="s">
+      <c r="N82" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="2">
         <v>1</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="2">
         <v>1</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83" s="4">
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G83" s="5">
+      <c r="G83" s="6">
         <f t="shared" si="18"/>
         <v>-122.83329426611789</v>
       </c>
-      <c r="H83" s="5">
+      <c r="H83" s="6">
         <f t="shared" si="19"/>
         <v>-246.53870925494337</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J83" s="5">
+      <c r="J83" s="6">
         <f t="shared" si="21"/>
         <v>-2.3264502898550674</v>
       </c>
-      <c r="K83" s="5">
+      <c r="K83" s="6">
         <f t="shared" si="22"/>
         <v>-122.83329426611789</v>
       </c>
-      <c r="L83" s="5">
+      <c r="L83" s="6">
         <f t="shared" si="23"/>
         <v>-10.341463913043476</v>
       </c>
-      <c r="M83" s="5">
+      <c r="M83" s="6">
         <f t="shared" si="24"/>
         <v>-246.53870925494337</v>
       </c>
-      <c r="N83" t="s">
+      <c r="N83" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="2">
         <v>1</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="2">
         <v>1</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="2">
         <v>0.9</v>
       </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84" s="4">
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G84" s="5">
+      <c r="G84" s="6">
         <f t="shared" si="18"/>
         <v>-165.26873644708425</v>
       </c>
-      <c r="H84" s="5">
+      <c r="H84" s="6">
         <f t="shared" si="19"/>
         <v>-272.30084623629813</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I84" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J84" s="5">
+      <c r="J84" s="6">
         <f t="shared" si="21"/>
         <v>-6.9943652898550717</v>
       </c>
-      <c r="K84" s="5">
+      <c r="K84" s="6">
         <f t="shared" si="22"/>
         <v>-165.26873644708425</v>
       </c>
-      <c r="L84" s="5">
+      <c r="L84" s="6">
         <f t="shared" si="23"/>
         <v>-13.175308913043478</v>
       </c>
-      <c r="M84" s="5">
+      <c r="M84" s="6">
         <f t="shared" si="24"/>
         <v>-272.30084623629813</v>
       </c>
-      <c r="N84" t="s">
+      <c r="N84" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="2">
         <v>1</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="2">
         <v>1</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="2">
         <v>1.2</v>
       </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85" s="4">
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G85" s="5">
+      <c r="G85" s="6">
         <f t="shared" si="18"/>
         <v>-101.61557317563475</v>
       </c>
-      <c r="H85" s="5">
+      <c r="H85" s="6">
         <f t="shared" si="19"/>
         <v>-233.65764076426601</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I85" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J85" s="5">
+      <c r="J85" s="6">
         <f t="shared" si="21"/>
         <v>7.5072101449293882E-3</v>
       </c>
-      <c r="K85" s="5">
+      <c r="K85" s="6">
         <f t="shared" si="22"/>
         <v>-101.6292226007869</v>
       </c>
-      <c r="L85" s="5">
+      <c r="L85" s="6">
         <f t="shared" si="23"/>
         <v>-8.9245414130434799</v>
       </c>
-      <c r="M85" s="5">
+      <c r="M85" s="6">
         <f t="shared" si="24"/>
         <v>-233.65764076426601</v>
       </c>
-      <c r="N85" t="s">
+      <c r="N85" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="2">
         <v>1</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="2">
         <v>1</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="2">
         <v>0.8</v>
       </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" s="4">
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G86" s="5">
+      <c r="G86" s="6">
         <f t="shared" si="18"/>
         <v>-186.48645753756739</v>
       </c>
-      <c r="H86" s="5">
+      <c r="H86" s="6">
         <f t="shared" si="19"/>
         <v>-285.18191472697549</v>
       </c>
-      <c r="I86" s="4">
+      <c r="I86" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J86" s="5">
+      <c r="J86" s="6">
         <f t="shared" si="21"/>
         <v>-9.328322789855072</v>
       </c>
-      <c r="K86" s="5">
+      <c r="K86" s="6">
         <f t="shared" si="22"/>
         <v>-186.48645753756739</v>
       </c>
-      <c r="L86" s="5">
+      <c r="L86" s="6">
         <f t="shared" si="23"/>
         <v>-14.592231413043478</v>
       </c>
-      <c r="M86" s="5">
+      <c r="M86" s="6">
         <f t="shared" si="24"/>
         <v>-285.18191472697549</v>
       </c>
-      <c r="N86" t="s">
+      <c r="N86" s="2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="2">
         <v>1.05</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="2">
         <v>1</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="2">
         <v>0.95</v>
       </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87" s="4">
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G87" s="5">
+      <c r="G87" s="6">
         <f t="shared" si="18"/>
         <v>-164.28950553147232</v>
       </c>
-      <c r="H87" s="5">
+      <c r="H87" s="6">
         <f t="shared" si="19"/>
         <v>-280.30475643540393</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I87" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J87" s="5">
+      <c r="J87" s="6">
         <f t="shared" si="21"/>
         <v>-6.3273865398550733</v>
       </c>
-      <c r="K87" s="5">
+      <c r="K87" s="6">
         <f t="shared" si="22"/>
         <v>-164.28950553147232</v>
       </c>
-      <c r="L87" s="5">
+      <c r="L87" s="6">
         <f t="shared" si="23"/>
         <v>-13.216847663043479</v>
       </c>
-      <c r="M87" s="5">
+      <c r="M87" s="6">
         <f t="shared" si="24"/>
         <v>-280.30475643540393</v>
       </c>
-      <c r="N87" t="s">
+      <c r="N87" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="2">
         <v>0.95</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="2">
         <v>1</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <v>1.05</v>
       </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-      <c r="F88" s="4">
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G88" s="5">
+      <c r="G88" s="6">
         <f t="shared" si="18"/>
         <v>-123.81252518172984</v>
       </c>
-      <c r="H88" s="5">
+      <c r="H88" s="6">
         <f t="shared" si="19"/>
         <v>-238.5347990558376</v>
       </c>
-      <c r="I88" s="4">
+      <c r="I88" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J88" s="5">
+      <c r="J88" s="6">
         <f t="shared" si="21"/>
         <v>-2.9934290398550694</v>
       </c>
-      <c r="K88" s="5">
+      <c r="K88" s="6">
         <f t="shared" si="22"/>
         <v>-123.81252518172984</v>
       </c>
-      <c r="L88" s="5">
+      <c r="L88" s="6">
         <f t="shared" si="23"/>
         <v>-10.299925163043477</v>
       </c>
-      <c r="M88" s="5">
+      <c r="M88" s="6">
         <f t="shared" si="24"/>
         <v>-238.5347990558376</v>
       </c>
-      <c r="N88" t="s">
+      <c r="N88" s="2" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="2">
         <v>1</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="2">
         <v>0.9</v>
       </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89" s="4">
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G89" s="6">
         <f t="shared" si="18"/>
         <v>-184.52799570634352</v>
       </c>
-      <c r="H89" s="5">
+      <c r="H89" s="6">
         <f t="shared" si="19"/>
         <v>-301.18973512518704</v>
       </c>
-      <c r="I89" s="4">
+      <c r="I89" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J89" s="5">
+      <c r="J89" s="6">
         <f t="shared" si="21"/>
         <v>-7.9943652898550734</v>
       </c>
-      <c r="K89" s="5">
+      <c r="K89" s="6">
         <f t="shared" si="22"/>
         <v>-184.52799570634352</v>
       </c>
-      <c r="L89" s="5">
+      <c r="L89" s="6">
         <f t="shared" si="23"/>
         <v>-14.675308913043478</v>
       </c>
-      <c r="M89" s="5">
+      <c r="M89" s="6">
         <f t="shared" si="24"/>
         <v>-301.18973512518704</v>
       </c>
-      <c r="N89" t="s">
+      <c r="N89" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="2">
         <v>0.9</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="2">
         <v>1</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90" s="4">
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G90" s="5">
+      <c r="G90" s="6">
         <f t="shared" si="18"/>
         <v>-103.57403500685862</v>
       </c>
-      <c r="H90" s="5">
+      <c r="H90" s="6">
         <f t="shared" si="19"/>
         <v>-217.64982036605451</v>
       </c>
-      <c r="I90" s="4">
+      <c r="I90" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J90" s="5">
+      <c r="J90" s="6">
         <f t="shared" si="21"/>
         <v>-1.3264502898550674</v>
       </c>
-      <c r="K90" s="5">
+      <c r="K90" s="6">
         <f t="shared" si="22"/>
         <v>-103.57403500685862</v>
       </c>
-      <c r="L90" s="5">
+      <c r="L90" s="6">
         <f t="shared" si="23"/>
         <v>-8.8414639130434765</v>
       </c>
-      <c r="M90" s="5">
+      <c r="M90" s="6">
         <f t="shared" si="24"/>
         <v>-217.64982036605451</v>
       </c>
-      <c r="N90" t="s">
+      <c r="N90" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="2">
         <v>1.2</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="2">
         <v>1</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="2">
         <v>0.8</v>
       </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91" s="4">
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G91" s="5">
+      <c r="G91" s="6">
         <f t="shared" si="18"/>
         <v>-225.00497605608589</v>
       </c>
-      <c r="H91" s="5">
+      <c r="H91" s="6">
         <f t="shared" si="19"/>
         <v>-342.95969250475326</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I91" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J91" s="5">
+      <c r="J91" s="6">
         <f t="shared" si="21"/>
         <v>-11.328322789855072</v>
       </c>
-      <c r="K91" s="5">
+      <c r="K91" s="6">
         <f t="shared" si="22"/>
         <v>-225.00497605608589</v>
       </c>
-      <c r="L91" s="5">
+      <c r="L91" s="6">
         <f t="shared" si="23"/>
         <v>-17.592231413043478</v>
       </c>
-      <c r="M91" s="5">
+      <c r="M91" s="6">
         <f t="shared" si="24"/>
         <v>-342.95969250475326</v>
       </c>
-      <c r="N91" t="s">
+      <c r="N91" s="2" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="2">
         <v>0.8</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="2">
         <v>1</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <v>1.2</v>
       </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92" s="4">
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G92" s="5">
+      <c r="G92" s="6">
         <f t="shared" si="18"/>
         <v>-63.097054657116246</v>
       </c>
-      <c r="H92" s="5">
+      <c r="H92" s="6">
         <f t="shared" si="19"/>
         <v>-175.87986298648829</v>
       </c>
-      <c r="I92" s="4">
+      <c r="I92" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J92" s="5">
+      <c r="J92" s="6">
         <f t="shared" si="21"/>
         <v>2.0075072101449294</v>
       </c>
-      <c r="K92" s="5">
+      <c r="K92" s="6">
         <f t="shared" si="22"/>
         <v>-66.747054973916278</v>
       </c>
-      <c r="L92" s="5">
+      <c r="L92" s="6">
         <f t="shared" si="23"/>
         <v>-5.9245414130434799</v>
       </c>
-      <c r="M92" s="5">
+      <c r="M92" s="6">
         <f t="shared" si="24"/>
         <v>-175.87986298648829</v>
       </c>
-      <c r="N92" t="s">
+      <c r="N92" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="2">
         <v>1</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="2">
         <v>1</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>1</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="2">
         <v>1</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="5">
         <f t="shared" si="17"/>
         <v>8.4174789158515821</v>
       </c>
-      <c r="G93" s="5">
+      <c r="G93" s="6">
         <f t="shared" si="18"/>
         <v>-147.64668774445229</v>
       </c>
-      <c r="H93" s="5">
+      <c r="H93" s="6">
         <f t="shared" si="19"/>
         <v>-261.60267486734432</v>
       </c>
-      <c r="I93" s="4">
+      <c r="I93" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="J93" s="5">
+      <c r="J93" s="6">
         <f t="shared" si="21"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="K93" s="5">
+      <c r="K93" s="6">
         <f t="shared" si="22"/>
         <v>-147.64668774445229</v>
       </c>
-      <c r="L93" s="5">
+      <c r="L93" s="6">
         <f t="shared" si="23"/>
         <v>-11.758386413043478</v>
       </c>
-      <c r="M93" s="5">
+      <c r="M93" s="6">
         <f t="shared" si="24"/>
         <v>-261.60267486734432</v>
       </c>
-      <c r="N93" t="s">
+      <c r="N93" s="2" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="2">
         <v>1</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="2">
         <v>1</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="2">
         <v>1</v>
       </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94" s="4">
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5">
         <f t="shared" si="17"/>
         <v>9.0908772291197089</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="6">
         <f t="shared" si="18"/>
         <v>-287.85647706968189</v>
       </c>
-      <c r="H94" s="5">
+      <c r="H94" s="6">
         <f t="shared" si="19"/>
         <v>-475.12797031524201</v>
       </c>
-      <c r="I94" s="4">
+      <c r="I94" s="5">
         <f>Inputs!$C$166</f>
         <v>7.9093281148075664E-2</v>
       </c>
-      <c r="J94" s="5">
+      <c r="J94" s="6">
         <f t="shared" si="21"/>
         <v>-4.6604077898550713</v>
       </c>
-      <c r="K94" s="5">
+      <c r="K94" s="6">
         <f t="shared" si="22"/>
         <v>-287.85647706968189</v>
       </c>
-      <c r="L94" s="5">
+      <c r="L94" s="6">
         <f t="shared" si="23"/>
         <v>-11.758386413043478</v>
       </c>
-      <c r="M94" s="5">
+      <c r="M94" s="6">
         <f t="shared" si="24"/>
         <v>-475.12797031524201</v>
       </c>
-      <c r="N94" t="s">
+      <c r="N94" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A102" s="7" t="s">
+    <row r="102" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A102" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F102" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G102" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="H102" s="7" t="s">
+      <c r="H102" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="I102" s="7" t="s">
+      <c r="I102" s="8" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <f>$B$19</f>
         <v>1</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F103" s="5">
+      <c r="F103" s="6">
         <f>$B$14*$B$13/1000+D103*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G103" s="4">
+      <c r="G103" s="5">
         <f t="shared" ref="G103:G113" si="25">(1+B103)^(-$B$8)*(1-(1+B103)^(-C103))/(1-1/(1+B103))</f>
         <v>9.0908772291197018</v>
       </c>
-      <c r="H103" s="5">
+      <c r="H103" s="6">
         <f t="shared" ref="H103:H113" si="26">($B$9/$B$8)*(1-(1+B103)^(-$B$8))/(1-1/(1+B103))</f>
         <v>192.59259259259238</v>
       </c>
-      <c r="I103" s="5">
+      <c r="I103" s="6">
         <f t="shared" ref="I103:I113" si="27">(F103*(1-$B$5)-E103*$B$9)*G103-H103</f>
         <v>-144.05101535660091</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B104" s="6">
+      <c r="B104" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-      <c r="E104" s="4">
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="6">
         <f>$B$14*$B$13/1000+D104*$B$14*Inputs!$D$148/1000</f>
         <v>14.169225000000003</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="5">
         <f t="shared" si="25"/>
         <v>9.0908772291197018</v>
       </c>
-      <c r="H104" s="5">
+      <c r="H104" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I104" s="5">
+      <c r="I104" s="6">
         <f t="shared" si="27"/>
         <v>-163.12348144932429</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="2">
         <v>30</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="2">
         <f t="shared" ref="D105:D111" si="28">$B$19</f>
         <v>1</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="6">
         <f>$B$14*$B$13/1000+D105*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G105" s="4">
+      <c r="G105" s="5">
         <f t="shared" si="25"/>
         <v>10.423873465858767</v>
       </c>
-      <c r="H105" s="5">
+      <c r="H105" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I105" s="5">
+      <c r="I105" s="6">
         <f t="shared" si="27"/>
         <v>-136.93335903475651</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B106" s="6">
+      <c r="B106" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="2">
         <v>40</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="2">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E106" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="6">
         <f>$B$14*$B$13/1000+D106*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G106" s="4">
+      <c r="G106" s="5">
         <f t="shared" si="25"/>
         <v>11.041308642357691</v>
       </c>
-      <c r="H106" s="5">
+      <c r="H106" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I106" s="5">
+      <c r="I106" s="6">
         <f t="shared" si="27"/>
         <v>-133.6365069760534</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107" s="7">
         <v>0.06</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E107" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="6">
         <f>$B$14*$B$13/1000+D107*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G107" s="4">
+      <c r="G107" s="5">
         <f t="shared" si="25"/>
         <v>10.820680394872868</v>
       </c>
-      <c r="H107" s="5">
+      <c r="H107" s="6">
         <f t="shared" si="26"/>
         <v>194.33962264150929</v>
       </c>
-      <c r="I107" s="5">
+      <c r="I107" s="6">
         <f t="shared" si="27"/>
         <v>-136.5616018965782</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B108" s="6">
+      <c r="B108" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F108" s="5">
+      <c r="F108" s="6">
         <f>$B$14*$B$13/1000+D108*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G108" s="4">
+      <c r="G108" s="5">
         <f t="shared" si="25"/>
         <v>9.9009478930057568</v>
       </c>
-      <c r="H108" s="5">
+      <c r="H108" s="6">
         <f t="shared" si="26"/>
         <v>193.45794392523374</v>
       </c>
-      <c r="I108" s="5">
+      <c r="I108" s="6">
         <f t="shared" si="27"/>
         <v>-140.59091968268936</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B109" s="7">
         <v>0.1</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="2">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="5">
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="F109" s="5">
+      <c r="F109" s="6">
         <f>$B$14*$B$13/1000+D109*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G109" s="4">
+      <c r="G109" s="5">
         <f t="shared" si="25"/>
         <v>7.7396033815986929</v>
       </c>
-      <c r="H109" s="5">
+      <c r="H109" s="6">
         <f t="shared" si="26"/>
         <v>190.90909090909093</v>
       </c>
-      <c r="I109" s="5">
+      <c r="I109" s="6">
         <f t="shared" si="27"/>
         <v>-149.58276498309522</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B110" s="6">
+      <c r="B110" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="2">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="5">
         <f>Inputs!$C$166</f>
         <v>7.9093281148075664E-2</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="6">
         <f>$B$14*$B$13/1000+D110*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G110" s="5">
         <f t="shared" si="25"/>
         <v>9.0908772291197018</v>
       </c>
-      <c r="H110" s="5">
+      <c r="H110" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I110" s="5">
+      <c r="I110" s="6">
         <f t="shared" si="27"/>
         <v>-287.85647706968166</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B111" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="2">
         <v>30</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="2">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="5">
         <f>Inputs!$C$166</f>
         <v>7.9093281148075664E-2</v>
       </c>
-      <c r="F111" s="5">
+      <c r="F111" s="6">
         <f>$B$14*$B$13/1000+D111*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="5">
         <f t="shared" si="25"/>
         <v>10.423873465858767</v>
       </c>
-      <c r="H111" s="5">
+      <c r="H111" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I111" s="5">
+      <c r="I111" s="6">
         <f t="shared" si="27"/>
         <v>-301.82502997218319</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B112" s="6">
+      <c r="B112" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="2">
         <f>B7</f>
         <v>20</v>
       </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="E112" s="4">
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112" s="5">
         <f>Inputs!$C$166</f>
         <v>7.9093281148075664E-2</v>
       </c>
-      <c r="F112" s="5">
+      <c r="F112" s="6">
         <f>$B$14*$B$13/1000+D112*$B$14*Inputs!$D$148/1000</f>
         <v>14.169225000000003</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G112" s="5">
         <f t="shared" si="25"/>
         <v>9.0908772291197018</v>
       </c>
-      <c r="H112" s="5">
+      <c r="H112" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I112" s="5">
+      <c r="I112" s="6">
         <f t="shared" si="27"/>
         <v>-306.92894316240506</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B113" s="6">
+      <c r="B113" s="7">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="2">
         <v>30</v>
       </c>
-      <c r="D113">
-        <v>0</v>
-      </c>
-      <c r="E113" s="4">
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+      <c r="E113" s="5">
         <f>Inputs!$C$166</f>
         <v>7.9093281148075664E-2</v>
       </c>
-      <c r="F113" s="5">
+      <c r="F113" s="6">
         <f>$B$14*$B$13/1000+D113*$B$14*Inputs!$D$148/1000</f>
         <v>14.169225000000003</v>
       </c>
-      <c r="G113" s="4">
+      <c r="G113" s="5">
         <f t="shared" si="25"/>
         <v>10.423873465858767</v>
       </c>
-      <c r="H113" s="5">
+      <c r="H113" s="6">
         <f t="shared" si="26"/>
         <v>192.59259259259238</v>
       </c>
-      <c r="I113" s="5">
+      <c r="I113" s="6">
         <f t="shared" si="27"/>
         <v>-323.69409367437572</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="5">
         <v>0.7</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="5">
         <f>B5</f>
         <v>0.77122153209109734</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119" s="5">
         <f>Inputs!$C$151</f>
         <v>0.93830000000000002</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A120">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
         <v>150</v>
       </c>
-      <c r="B120" s="5">
+      <c r="B120" s="6">
         <f t="shared" ref="B120:D123" si="29">$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
         <v>-80.791281172994928</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="6">
         <f t="shared" si="29"/>
         <v>-95.902867208452932</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D120" s="6">
         <f t="shared" si="29"/>
         <v>-131.35311053161632</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A121">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
         <v>200</v>
       </c>
-      <c r="B121" s="5">
+      <c r="B121" s="6">
         <f t="shared" si="29"/>
         <v>-128.93942932114308</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121" s="6">
         <f t="shared" si="29"/>
         <v>-144.05101535660108</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="6">
         <f t="shared" si="29"/>
         <v>-179.50125867976448</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A122">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
         <v>250</v>
       </c>
-      <c r="B122" s="5">
+      <c r="B122" s="6">
         <f t="shared" si="29"/>
         <v>-177.08757746929123</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C122" s="6">
         <f t="shared" si="29"/>
         <v>-192.19916350474924</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D122" s="6">
         <f t="shared" si="29"/>
         <v>-227.64940682791263</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A123">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
         <v>300</v>
       </c>
-      <c r="B123" s="5">
+      <c r="B123" s="6">
         <f t="shared" si="29"/>
         <v>-225.23572561743936</v>
       </c>
-      <c r="C123" s="5">
+      <c r="C123" s="6">
         <f t="shared" si="29"/>
         <v>-240.34731165289736</v>
       </c>
-      <c r="D123" s="5">
+      <c r="D123" s="6">
         <f t="shared" si="29"/>
         <v>-275.79755497606072</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>420</v>
       </c>
@@ -10303,88 +10550,88 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="2">
         <v>17.8</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="2" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="2">
         <v>17.3</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="2">
         <f>Inputs!$C$83</f>
         <v>7.5</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="2" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="2">
         <v>14</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134" s="6">
         <f>B25</f>
         <v>43.147150391637652</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B135" s="9">
+      <c r="B135" s="11">
         <f>B25/B128</f>
         <v>2.4239972130133514</v>
       </c>
@@ -10397,10 +10644,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>437</v>
       </c>
     </row>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\claude\C--Users-user-AppData-Roaming-Claude-scratch-workspaces-c7acaf2f-ed5f-4f26-814b-0755985b8641-704b7f5d-017e-4c68-a76d-e0c46600fd5a-scratch-2026-10-16-ee569e\885493fd-7279-48f0-8993-cb2538820dce\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE231D8-B9DB-4A00-8EF5-2DA226AA4BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E680D22-5C87-486E-9428-8E01C66D3393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="445">
   <si>
     <t>Parameter</t>
   </si>
@@ -1342,15 +1342,31 @@
   </si>
   <si>
     <t>Operating cash flow (THB bn)</t>
+  </si>
+  <si>
+    <t>Cumulative cash flow over the operating life, before tax (THB bn)</t>
+  </si>
+  <si>
+    <t>Years of operation needed for nominal payback</t>
+  </si>
+  <si>
+    <t>Estimated nominal payback year (from start of construction)</t>
+  </si>
+  <si>
+    <t>Nominal payback within the operating life</t>
+  </si>
+  <si>
+    <t>Estimated discounted payback year at WACC (from start of construction)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1406,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1423,6 +1439,16 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6533,6 +6559,71 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="B33" s="12">
+        <f>SUM(J41:J63)</f>
+        <v>-93.208155797101426</v>
+      </c>
+      <c r="C33" s="12">
+        <f>(C15*(1-C5)-C16*C9)*B7-C9</f>
+        <v>-235.16772826086958</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="B34" s="13">
+        <f>IF(B15*(1-B5)-B16*B9&lt;=0,"never",B9/(B15*(1-B5)-B16*B9))</f>
+        <v>37.456043856684623</v>
+      </c>
+      <c r="C34" s="13">
+        <f>IF(C15*(1-C5)-C16*C9&lt;=0,"never",C9/(C15*(1-C5)-C16*C9))</f>
+        <v>92.546502521808364</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B35" s="13">
+        <f>IF(ISNUMBER(B34),B8+B34,"never")</f>
+        <v>39.456043856684623</v>
+      </c>
+      <c r="C35" s="13">
+        <f>IF(ISNUMBER(C34),C8+C34,"never")</f>
+        <v>94.546502521808364</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="B36" s="14" t="str">
+        <f>IF(ISNUMBER(B34),IF(B34&lt;=B7,"Yes","No"),"No")</f>
+        <v>No</v>
+      </c>
+      <c r="C36" s="14" t="str">
+        <f>IF(ISNUMBER(C34),IF(C34&lt;=C7,"Yes","No"),"No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="B37" s="13" t="str">
+        <f>IF(B15*(1-B5)-B16*B9&lt;=0,"never",IF(B28*B6*(1+B6)^(B8-1)/(B15*(1-B5)-B16*B9)&gt;=1,"never",B8-LN(1-B28*B6*(1+B6)^(B8-1)/(B15*(1-B5)-B16*B9))/LN(1+B6)))</f>
+        <v>never</v>
+      </c>
+      <c r="C37" s="13" t="str">
+        <f>IF(C15*(1-C5)-C16*C9&lt;=0,"never",IF((C9/B9)*B28*C6*(1+C6)^(C8-1)/(C15*(1-C5)-C16*C9)&gt;=1,"never",C8-LN(1-(C9/B9)*B28*C6*(1+C6)^(C8-1)/(C15*(1-C5)-C16*C9))/LN(1+C6)))</f>
+        <v>never</v>
+      </c>
+    </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>338</v>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\claude\C--Users-user-AppData-Roaming-Claude-scratch-workspaces-c7acaf2f-ed5f-4f26-814b-0755985b8641-704b7f5d-017e-4c68-a76d-e0c46600fd5a-scratch-2026-10-16-ee569e\885493fd-7279-48f0-8993-cb2538820dce\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E680D22-5C87-486E-9428-8E01C66D3393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F8D39A-960E-47E5-B79E-1AB96DC013C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1422,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1448,7 +1448,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2752,6 +2751,46 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700">
+                    <a:solidFill>
+                      <a:srgbClr val="404040"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Appraisal!$N$68:$N$94</c:f>
@@ -2960,6 +2999,46 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="700">
+                    <a:solidFill>
+                      <a:srgbClr val="404040"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Appraisal!$N$68:$N$94</c:f>
@@ -6560,7 +6639,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="2" t="s">
         <v>440</v>
       </c>
       <c r="B33" s="12">
@@ -6573,7 +6652,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="2" t="s">
         <v>441</v>
       </c>
       <c r="B34" s="13">
@@ -6586,7 +6665,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="2" t="s">
         <v>442</v>
       </c>
       <c r="B35" s="13">
@@ -6599,7 +6678,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="2" t="s">
         <v>443</v>
       </c>
       <c r="B36" s="14" t="str">
@@ -6612,7 +6691,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="2" t="s">
         <v>444</v>
       </c>
       <c r="B37" s="13" t="str">

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\claude\C--Users-user-AppData-Roaming-Claude-scratch-workspaces-c7acaf2f-ed5f-4f26-814b-0755985b8641-704b7f5d-017e-4c68-a76d-e0c46600fd5a-scratch-2026-10-16-ee569e\885493fd-7279-48f0-8993-cb2538820dce\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E7F13-21F4-4103-B9F9-F8F90C4DA915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508BAA86-9B43-4AD2-9502-D3077BD120C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1802,6 +1802,886 @@
             </a:solidFill>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="14"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="15"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="16"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="17"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="18"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="19"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="20"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="21"/>
+              <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="800">
+                      <a:solidFill>
+                        <a:srgbClr val="404040"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                      <a:ea typeface="Times New Roman"/>
+                      <a:cs typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-C1E0-44CC-9963-210863B94866}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Appraisal!$A$41:$A$63</c:f>

--- a/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
+++ b/seminar/workbook/Phase1_financial_appraisal_v2.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Appraisal" sheetId="2" r:id="rId2"/>
     <sheet name="Charts" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1622,156 +1622,159 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Appraisal!$A$41:$A$63</c:f>
+              <c:f>Appraisal!$A$41:$A$85</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23.0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24.0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25.0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26.0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27.0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28.0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30.0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31.0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32.0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33.0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34.0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35.0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36.0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38.0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39.0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40.0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41.0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42.0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43.0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Appraisal!$U$41:$U$63</c:f>
+              <c:f>Appraisal!$U$41:$U$85</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>100.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>#N/A</c:v>
+                  <c:v>100.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2684,156 +2687,213 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Appraisal!$A$41:$A$63</c:f>
+              <c:f>Appraisal!$A$41:$A$85</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23.0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24.0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25.0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26.0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27.0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28.0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30.0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31.0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32.0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33.0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34.0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35.0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36.0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38.0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39.0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40.0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41.0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42.0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43.0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Appraisal!$V$41:$V$63</c:f>
+              <c:f>Appraisal!$V$41:$V$85</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="23"/>
-                <c:pt idx="0">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>#N/A</c:v>
-                </c:pt>
+                <c:ptCount val="45"/>
                 <c:pt idx="2">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.3395922101449287</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.3395922101449287</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>#N/A</c:v>
+                  <c:v>5.339592210144929</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3202,93 +3262,159 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Appraisal!$A$41:$A$63</c:f>
+              <c:f>Appraisal!$A$41:$A$85</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>2.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7</c:v>
+                  <c:v>7.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>8.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12</c:v>
+                  <c:v>12.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15</c:v>
+                  <c:v>15.0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16</c:v>
+                  <c:v>16.0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17</c:v>
+                  <c:v>17.0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>18</c:v>
+                  <c:v>18.0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>19</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>21</c:v>
+                  <c:v>21.0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>22</c:v>
+                  <c:v>22.0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23.0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24.0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25.0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26.0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27.0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28.0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30.0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31.0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32.0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33.0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34.0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35.0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36.0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38.0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39.0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40.0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41.0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42.0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43.0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Appraisal!$S$41:$S$63</c:f>
+              <c:f>Appraisal!$S$41:$S$85</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
-                <c:ptCount val="23"/>
+                <c:ptCount val="45"/>
                 <c:pt idx="0">
-                  <c:v>-100</c:v>
+                  <c:v>-100.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-200</c:v>
+                  <c:v>-200.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>-194.66040778985507</c:v>
@@ -3297,7 +3423,7 @@
                   <c:v>-189.32081557971014</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-183.98122336956521</c:v>
+                  <c:v>-183.9812233695652</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>-178.64163115942029</c:v>
@@ -3318,7 +3444,7 @@
                   <c:v>-151.94367010869564</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-146.60407789855071</c:v>
+                  <c:v>-146.6040778985507</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-141.26448568840578</c:v>
@@ -3345,13 +3471,79 @@
                   <c:v>-103.88734021739128</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-98.547748007246355</c:v>
+                  <c:v>-98.54774800724635</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-93.208155797101426</c:v>
+                  <c:v>-93.20815579710143</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-93.208155797101426</c:v>
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-93.20815579710143</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-93.20815579710143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3641,7 +3833,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Appraisal!$G$67</c:f>
+              <c:f>Appraisal!$G$89</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4697,7 +4889,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Appraisal!$N$68:$N$94</c:f>
+              <c:f>Appraisal!$N$90:$N$116</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -4786,7 +4978,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Appraisal!$G$68:$G$94</c:f>
+              <c:f>Appraisal!$G$90:$G$116</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
@@ -4806,7 +4998,7 @@
                   <c:v>-124.79175609734182</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-182.56953387511959</c:v>
+                  <c:v>-182.5695338751196</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-105.53249683808258</c:v>
@@ -4818,7 +5010,7 @@
                   <c:v>-135.86923367315907</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-160.41457872348511</c:v>
+                  <c:v>-160.4145787234851</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-127.68745198971706</c:v>
@@ -4845,7 +5037,7 @@
                   <c:v>-101.61557317563475</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-186.48645753756739</c:v>
+                  <c:v>-186.4864575375674</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-164.28950553147232</c:v>
@@ -4860,16 +5052,16 @@
                   <c:v>-103.57403500685862</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-225.00497605608589</c:v>
+                  <c:v>-225.0049760560859</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>-63.097054657116246</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-147.64668774445229</c:v>
+                  <c:v>-147.6466877444523</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-287.85647706968189</c:v>
+                  <c:v>-287.8564770696819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4885,7 +5077,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Appraisal!$H$67</c:f>
+              <c:f>Appraisal!$H$89</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5941,7 +6133,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Appraisal!$N$68:$N$94</c:f>
+              <c:f>Appraisal!$N$90:$N$116</c:f>
               <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
@@ -6030,7 +6222,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Appraisal!$H$68:$H$94</c:f>
+              <c:f>Appraisal!$H$90:$H$116</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
@@ -6038,16 +6230,16 @@
                   <c:v>-259.41977774562076</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-273.86422219006528</c:v>
+                  <c:v>-273.8642221900653</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-244.97533330117631</c:v>
+                  <c:v>-244.9753333011763</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-288.30866663450968</c:v>
+                  <c:v>-288.3086666345097</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-230.53088885673191</c:v>
+                  <c:v>-230.5308888567319</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>-317.19755552339853</c:v>
@@ -6056,19 +6248,19 @@
                   <c:v>-201.64199996784305</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-264.38685643379603</c:v>
+                  <c:v>-264.386856433796</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-254.45269905744547</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-269.35393512197129</c:v>
+                  <c:v>-269.3539351219713</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-249.48562036927018</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-279.28809249832187</c:v>
+                  <c:v>-279.2880924983219</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-239.55146299291965</c:v>
@@ -6077,19 +6269,19 @@
                   <c:v>-252.97924350028205</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-265.86031199095942</c:v>
+                  <c:v>-265.8603119909594</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>-246.53870925494337</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-272.30084623629813</c:v>
+                  <c:v>-272.3008462362981</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-233.65764076426601</c:v>
+                  <c:v>-233.657640764266</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-285.18191472697549</c:v>
+                  <c:v>-285.1819147269755</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-280.30475643540393</c:v>
@@ -6101,19 +6293,19 @@
                   <c:v>-301.18973512518704</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-217.64982036605451</c:v>
+                  <c:v>-217.6498203660545</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>-342.95969250475326</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-175.87986298648829</c:v>
+                  <c:v>-175.8798629864883</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-261.60267486734432</c:v>
+                  <c:v>-261.6026748673443</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-475.12797031524201</c:v>
+                  <c:v>-475.127970315242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9209,7 +9401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V135"/>
+  <dimension ref="A1:V157"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -9250,11 +9442,11 @@
       </c>
       <c r="B5" s="6">
         <f>Inputs!$C$133/Inputs!$C$84</f>
-        <v>0.77122153209109734</v>
+        <v>0.7712215320910973</v>
       </c>
       <c r="C5" s="6">
         <f>B5</f>
-        <v>0.77122153209109734</v>
+        <v>0.7712215320910973</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -9276,11 +9468,11 @@
       </c>
       <c r="B7">
         <f>Inputs!$C$141</f>
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C7">
         <f>B7</f>
-        <v>20</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -9289,11 +9481,11 @@
       </c>
       <c r="B8">
         <f>Inputs!$C$142</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="C8">
         <f>B8</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -9302,11 +9494,11 @@
       </c>
       <c r="B9">
         <f>Inputs!$C$164</f>
-        <v>200</v>
+        <v>200.0</v>
       </c>
       <c r="C9">
         <f>Inputs!$C$2</f>
-        <v>300</v>
+        <v>300.0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -9354,11 +9546,11 @@
       </c>
       <c r="B13">
         <f>Inputs!$C$152</f>
-        <v>2877</v>
+        <v>2877.0</v>
       </c>
       <c r="C13">
         <f>B13</f>
-        <v>2877</v>
+        <v>2877.0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -9367,11 +9559,11 @@
       </c>
       <c r="B14">
         <f>B10-MAX(B10*B11-B12,0)</f>
-        <v>4.9250000000000007</v>
+        <v>4.925000000000001</v>
       </c>
       <c r="C14">
         <f>B14</f>
-        <v>4.9250000000000007</v>
+        <v>4.925000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -9393,11 +9585,11 @@
       </c>
       <c r="B16">
         <f>Inputs!$C$165</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="C16">
         <f>B16</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -9419,11 +9611,11 @@
       </c>
       <c r="B18">
         <f>Inputs!$C$168</f>
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="C18">
         <f>B18</f>
-        <v>20</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -9453,8 +9645,8 @@
         <v>329</v>
       </c>
       <c r="B21" s="7">
-        <f>SUM(K41:K63)</f>
-        <v>-144.05101535660106</v>
+        <f>SUM(K41:K85)</f>
+        <v>-144.05101535660108</v>
       </c>
       <c r="C21" s="7">
         <f>(C15*(1-C5)-C16*C9)*B27-(C9/B9)*B28</f>
@@ -9466,8 +9658,8 @@
         <v>330</v>
       </c>
       <c r="B22" s="7">
-        <f>IF($B$18&lt;$B$7,"n/a",SUM(R41:R63))</f>
-        <v>-144.05101535660106</v>
+        <f>IF($B$18&lt;$B$7,"n/a",SUM(R41:R85))</f>
+        <v>-144.05101535660108</v>
       </c>
       <c r="C22" s="7">
         <f>IF(C18&lt;C7,"n/a",C21)</f>
@@ -9479,8 +9671,8 @@
         <v>331</v>
       </c>
       <c r="B23" s="8">
-        <f>IF($B$18&lt;$B$7,"n/a",IRR(Q41:Q63,-0.1))</f>
-        <v>-5.1509439628371956E-2</v>
+        <f>IF($B$18&lt;$B$7,"n/a",IRR(Q41:Q85,-0.1))</f>
+        <v>-0.05150943962837129</v>
       </c>
       <c r="C23" t="s">
         <v>332</v>
@@ -9492,11 +9684,11 @@
       </c>
       <c r="B24" s="7">
         <f>B15*(1-B5)*B27/(B16*B27+B28/B9)</f>
-        <v>50.408560975837332</v>
+        <v>50.40856097583733</v>
       </c>
       <c r="C24" s="7">
         <f>B24</f>
-        <v>50.408560975837332</v>
+        <v>50.40856097583733</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -9505,7 +9697,7 @@
       </c>
       <c r="B25" s="7">
         <f>B10-B21/((1-B5)*(B13+B19*Inputs!$D$148)/1000*(1-B11)*B27)</f>
-        <v>43.147150391637652</v>
+        <v>43.14715039163766</v>
       </c>
       <c r="C25" s="7">
         <f>B10-C21/((1-C5)*C13/1000*(1-C11)*B27)</f>
@@ -9517,8 +9709,8 @@
         <v>335</v>
       </c>
       <c r="B27">
-        <f>SUMPRODUCT(B41:B63,D41:D63)</f>
-        <v>9.0908772291197089</v>
+        <f>SUMPRODUCT(B41:B85,D41:D85)</f>
+        <v>9.090877229119709</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -9526,8 +9718,19 @@
         <v>336</v>
       </c>
       <c r="B28" s="7">
-        <f>SUMPRODUCT(E41:E63,B41:B63)</f>
+        <f>SUMPRODUCT(E41:E85,B41:B85)</f>
         <v>192.59259259259258</v>
+      </c>
+    </row>
+    <row spans="1:3" x14ac:dyDescent="0.3" r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ledger covers the operating life</t>
+        </is>
+      </c>
+      <c r="B31" t="str">
+        <f>IF($B$8+$B$7-1&lt;=MAX($A$41:$A$85),"Yes","No")</f>
+        <v>Yes</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -9548,8 +9751,8 @@
         <v>440</v>
       </c>
       <c r="B33" s="9">
-        <f>SUM(J41:J63)</f>
-        <v>-93.208155797101426</v>
+        <f>SUM(J41:J85)</f>
+        <v>-93.20815579710143</v>
       </c>
       <c r="C33" s="9">
         <f>(C15*(1-C5)-C16*C9)*B7-C9</f>
@@ -9562,11 +9765,11 @@
       </c>
       <c r="B34" s="10">
         <f>IF(B15*(1-B5)-B16*B9&lt;=0,"never",B9/(B15*(1-B5)-B16*B9))</f>
-        <v>37.456043856684623</v>
+        <v>37.45604385668462</v>
       </c>
       <c r="C34" s="10">
         <f>IF(C15*(1-C5)-C16*C9&lt;=0,"never",C9/(C15*(1-C5)-C16*C9))</f>
-        <v>92.546502521808364</v>
+        <v>92.54650252180836</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
@@ -9575,11 +9778,11 @@
       </c>
       <c r="B35" s="10">
         <f>IF(ISNUMBER(B34),B8+B34,"never")</f>
-        <v>39.456043856684623</v>
+        <v>39.45604385668462</v>
       </c>
       <c r="C35" s="10">
         <f>IF(ISNUMBER(C34),C8+C34,"never")</f>
-        <v>94.546502521808364</v>
+        <v>94.54650252180836</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
@@ -9683,83 +9886,83 @@
         <v>0</v>
       </c>
       <c r="B41" s="6">
-        <f t="shared" ref="B41:B63" si="0">1/(1+$B$6)^A41</f>
-        <v>1</v>
+        <f>1/(1+$B$6)^A41</f>
+        <v>1.0</v>
       </c>
       <c r="C41">
-        <f t="shared" ref="C41:C63" si="1">IF(A41&lt;$B$8,1,0)</f>
-        <v>1</v>
+        <f>IF(A41&lt;$B$8,1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="D41">
-        <f t="shared" ref="D41:D63" si="2">IF(AND(A41&gt;=$B$8,A41&lt;$B$8+$B$7),1,0)</f>
-        <v>0</v>
+        <f>IF(AND(A41&gt;=$B$8,A41&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="E41" s="7">
-        <f t="shared" ref="E41:E63" si="3">C41*$B$9/$B$8</f>
-        <v>100</v>
+        <f>C41*$B$9/$B$8</f>
+        <v>100.0</v>
       </c>
       <c r="F41" s="12">
-        <f t="shared" ref="F41:F63" si="4">D41*$B$14</f>
-        <v>0</v>
+        <f>D41*$B$14</f>
+        <v>0.0</v>
       </c>
       <c r="G41" s="7">
         <f>F41*($B$13+$B$19*Inputs!$D$148)/1000</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" ref="H41:H63" si="5">$B$5*G41</f>
-        <v>0</v>
+        <f>$B$5*G41</f>
+        <v>0.0</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" ref="I41:I63" si="6">D41*$B$16*$B$9</f>
-        <v>0</v>
+        <f>D41*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J41" s="7">
-        <f t="shared" ref="J41:J63" si="7">G41-H41-E41-I41</f>
-        <v>-100</v>
+        <f>G41-H41-E41-I41</f>
+        <v>-100.0</v>
       </c>
       <c r="K41" s="7">
-        <f t="shared" ref="K41:K63" si="8">J41*B41</f>
-        <v>-100</v>
+        <f>J41*B41</f>
+        <v>-100.0</v>
       </c>
       <c r="L41" s="7">
-        <f t="shared" ref="L41:L63" si="9">IF(AND(A41&gt;=$B$8,A41&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
-        <v>0</v>
+        <f>IF(AND(A41&gt;=$B$8,A41&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
       </c>
       <c r="M41" s="7">
-        <f t="shared" ref="M41:M63" si="10">G41-H41-L41</f>
-        <v>0</v>
+        <f>G41-H41-L41</f>
+        <v>0.0</v>
       </c>
       <c r="N41" s="7">
         <f>SUM($M$41:M41)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O41" s="7">
-        <f t="shared" ref="O41:O63" si="11">$B$17*MAX(0,N41)</f>
-        <v>0</v>
+        <f>$B$17*MAX(0,N41)</f>
+        <v>0.0</v>
       </c>
       <c r="P41" s="7">
         <f>MAX(0,O41)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q41" s="7">
-        <f t="shared" ref="Q41:Q63" si="12">J41-P41</f>
-        <v>-100</v>
+        <f>J41-P41</f>
+        <v>-100.0</v>
       </c>
       <c r="R41" s="7">
-        <f t="shared" ref="R41:R63" si="13">Q41*B41</f>
-        <v>-100</v>
+        <f>Q41*B41</f>
+        <v>-100.0</v>
       </c>
       <c r="S41" s="7">
         <f>SUM($Q$41:Q41)</f>
-        <v>-100</v>
+        <v>-100.0</v>
       </c>
       <c r="U41" s="7">
-        <f t="shared" ref="U41:U63" si="14">IF(J41&lt;0,-J41,NA())</f>
-        <v>100</v>
+        <f>IF(J41&lt;0,-J41,NA())</f>
+        <v>100.0</v>
       </c>
       <c r="V41" s="7" t="e">
-        <f t="shared" ref="V41:V63" si="15">IF(J41&gt;0,J41,NA())</f>
+        <f>IF(J41&gt;0,J41,NA())</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -9768,83 +9971,83 @@
         <v>1</v>
       </c>
       <c r="B42" s="6">
-        <f t="shared" si="0"/>
-        <v>0.92592592592592582</v>
+        <f>1/(1+$B$6)^A42</f>
+        <v>0.9259259259259258</v>
       </c>
       <c r="C42">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>IF(A42&lt;$B$8,1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="D42">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF(AND(A42&gt;=$B$8,A42&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="E42" s="7">
-        <f t="shared" si="3"/>
-        <v>100</v>
+        <f>C42*$B$9/$B$8</f>
+        <v>100.0</v>
       </c>
       <c r="F42" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>D42*$B$14</f>
+        <v>0.0</v>
       </c>
       <c r="G42" s="7">
         <f>F42*($B$13+$B$19*Inputs!$D$148)/1000</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>$B$5*G42</f>
+        <v>0.0</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D42*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" si="7"/>
-        <v>-100</v>
+        <f>G42-H42-E42-I42</f>
+        <v>-100.0</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="8"/>
-        <v>-92.592592592592581</v>
+        <f>J42*B42</f>
+        <v>-92.59259259259258</v>
       </c>
       <c r="L42" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>IF(AND(A42&gt;=$B$8,A42&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
       </c>
       <c r="M42" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>G42-H42-L42</f>
+        <v>0.0</v>
       </c>
       <c r="N42" s="7">
         <f>SUM($M$41:M42)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O42" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N42)</f>
+        <v>0.0</v>
       </c>
       <c r="P42" s="7">
-        <f t="shared" ref="P42:P63" si="16">MAX(0,O42-O41)</f>
-        <v>0</v>
+        <f>MAX(0,O42-O41)</f>
+        <v>0.0</v>
       </c>
       <c r="Q42" s="7">
-        <f t="shared" si="12"/>
-        <v>-100</v>
+        <f>J42-P42</f>
+        <v>-100.0</v>
       </c>
       <c r="R42" s="7">
-        <f t="shared" si="13"/>
-        <v>-92.592592592592581</v>
+        <f>Q42*B42</f>
+        <v>-92.59259259259258</v>
       </c>
       <c r="S42" s="7">
         <f>SUM($Q$41:Q42)</f>
-        <v>-200</v>
+        <v>-200.0</v>
       </c>
       <c r="U42" s="7">
-        <f t="shared" si="14"/>
-        <v>100</v>
+        <f>IF(J42&lt;0,-J42,NA())</f>
+        <v>100.0</v>
       </c>
       <c r="V42" s="7" t="e">
-        <f t="shared" si="15"/>
+        <f>IF(J42&gt;0,J42,NA())</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -9853,84 +10056,84 @@
         <v>2</v>
       </c>
       <c r="B43" s="6">
-        <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <f>1/(1+$B$6)^A43</f>
+        <v>0.8573388203017832</v>
       </c>
       <c r="C43">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A43&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D43">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A43&gt;=$B$8,A43&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E43" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C43*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F43" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D43*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G43" s="7">
         <f>F43*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G43</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I43" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D43*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J43" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G43-H43-E43-I43</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K43" s="7">
-        <f t="shared" si="8"/>
-        <v>4.5778396863382449</v>
+        <f>J43*B43</f>
+        <v>4.577839686338245</v>
       </c>
       <c r="L43" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A43&gt;=$B$8,A43&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M43" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G43-H43-L43</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N43" s="7">
         <f>SUM($M$41:M43)</f>
-        <v>-4.6604077898550713</v>
+        <v>-4.660407789855071</v>
       </c>
       <c r="O43" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N43)</f>
+        <v>0.0</v>
       </c>
       <c r="P43" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O43-O42)</f>
+        <v>0.0</v>
       </c>
       <c r="Q43" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J43-P43</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R43" s="7">
-        <f t="shared" si="13"/>
-        <v>4.5778396863382449</v>
+        <f>Q43*B43</f>
+        <v>4.577839686338245</v>
       </c>
       <c r="S43" s="7">
         <f>SUM($Q$41:Q43)</f>
         <v>-194.66040778985507</v>
       </c>
       <c r="U43" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J43&lt;0,-J43,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V43" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J43&gt;0,J43,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
@@ -9938,84 +10141,84 @@
         <v>3</v>
       </c>
       <c r="B44" s="6">
-        <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <f>1/(1+$B$6)^A44</f>
+        <v>0.7938322410201696</v>
       </c>
       <c r="C44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A44&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D44">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A44&gt;=$B$8,A44&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E44" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C44*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F44" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D44*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G44" s="7">
         <f>F44*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H44" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G44</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I44" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D44*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J44" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G44-H44-E44-I44</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K44" s="7">
-        <f t="shared" si="8"/>
-        <v>4.2387404503131894</v>
+        <f>J44*B44</f>
+        <v>4.238740450313189</v>
       </c>
       <c r="L44" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A44&gt;=$B$8,A44&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M44" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G44-H44-L44</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N44" s="7">
         <f>SUM($M$41:M44)</f>
-        <v>-9.3208155797101426</v>
+        <v>-9.320815579710143</v>
       </c>
       <c r="O44" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N44)</f>
+        <v>0.0</v>
       </c>
       <c r="P44" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O44-O43)</f>
+        <v>0.0</v>
       </c>
       <c r="Q44" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J44-P44</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R44" s="7">
-        <f t="shared" si="13"/>
-        <v>4.2387404503131894</v>
+        <f>Q44*B44</f>
+        <v>4.238740450313189</v>
       </c>
       <c r="S44" s="7">
         <f>SUM($Q$41:Q44)</f>
         <v>-189.32081557971014</v>
       </c>
       <c r="U44" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J44&lt;0,-J44,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V44" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J44&gt;0,J44,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.3">
@@ -10023,84 +10226,84 @@
         <v>4</v>
       </c>
       <c r="B45" s="6">
-        <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <f>1/(1+$B$6)^A45</f>
+        <v>0.7350298527964533</v>
       </c>
       <c r="C45">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A45&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D45">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A45&gt;=$B$8,A45&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E45" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C45*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F45" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D45*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G45" s="7">
         <f>F45*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G45</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I45" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D45*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J45" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G45-H45-E45-I45</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K45" s="7">
-        <f t="shared" si="8"/>
+        <f>J45*B45</f>
         <v>3.9247596762159156</v>
       </c>
       <c r="L45" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A45&gt;=$B$8,A45&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M45" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G45-H45-L45</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N45" s="7">
         <f>SUM($M$41:M45)</f>
         <v>-13.981223369565214</v>
       </c>
       <c r="O45" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N45)</f>
+        <v>0.0</v>
       </c>
       <c r="P45" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O45-O44)</f>
+        <v>0.0</v>
       </c>
       <c r="Q45" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J45-P45</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R45" s="7">
-        <f t="shared" si="13"/>
+        <f>Q45*B45</f>
         <v>3.9247596762159156</v>
       </c>
       <c r="S45" s="7">
         <f>SUM($Q$41:Q45)</f>
-        <v>-183.98122336956521</v>
+        <v>-183.9812233695652</v>
       </c>
       <c r="U45" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J45&lt;0,-J45,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V45" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J45&gt;0,J45,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.3">
@@ -10108,84 +10311,84 @@
         <v>5</v>
       </c>
       <c r="B46" s="6">
-        <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <f>1/(1+$B$6)^A46</f>
+        <v>0.6805831970337529</v>
       </c>
       <c r="C46">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A46&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D46">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A46&gt;=$B$8,A46&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E46" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C46*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F46" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D46*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G46" s="7">
         <f>F46*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H46" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G46</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I46" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D46*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J46" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G46-H46-E46-I46</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K46" s="7">
-        <f t="shared" si="8"/>
-        <v>3.6340367372369586</v>
+        <f>J46*B46</f>
+        <v>3.634036737236958</v>
       </c>
       <c r="L46" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A46&gt;=$B$8,A46&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M46" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G46-H46-L46</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N46" s="7">
         <f>SUM($M$41:M46)</f>
         <v>-18.641631159420285</v>
       </c>
       <c r="O46" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N46)</f>
+        <v>0.0</v>
       </c>
       <c r="P46" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O46-O45)</f>
+        <v>0.0</v>
       </c>
       <c r="Q46" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J46-P46</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R46" s="7">
-        <f t="shared" si="13"/>
-        <v>3.6340367372369586</v>
+        <f>Q46*B46</f>
+        <v>3.634036737236958</v>
       </c>
       <c r="S46" s="7">
         <f>SUM($Q$41:Q46)</f>
         <v>-178.64163115942029</v>
       </c>
       <c r="U46" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J46&lt;0,-J46,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V46" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J46&gt;0,J46,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
@@ -10193,84 +10396,84 @@
         <v>6</v>
       </c>
       <c r="B47" s="6">
-        <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <f>1/(1+$B$6)^A47</f>
+        <v>0.6301696268831045</v>
       </c>
       <c r="C47">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A47&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D47">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A47&gt;=$B$8,A47&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E47" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C47*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F47" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D47*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G47" s="7">
         <f>F47*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H47" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G47</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I47" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D47*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J47" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G47-H47-E47-I47</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K47" s="7">
-        <f t="shared" si="8"/>
-        <v>3.3648488307749611</v>
+        <f>J47*B47</f>
+        <v>3.364848830774961</v>
       </c>
       <c r="L47" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A47&gt;=$B$8,A47&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M47" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G47-H47-L47</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N47" s="7">
         <f>SUM($M$41:M47)</f>
         <v>-23.302038949275357</v>
       </c>
       <c r="O47" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N47)</f>
+        <v>0.0</v>
       </c>
       <c r="P47" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O47-O46)</f>
+        <v>0.0</v>
       </c>
       <c r="Q47" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J47-P47</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R47" s="7">
-        <f t="shared" si="13"/>
-        <v>3.3648488307749611</v>
+        <f>Q47*B47</f>
+        <v>3.364848830774961</v>
       </c>
       <c r="S47" s="7">
         <f>SUM($Q$41:Q47)</f>
         <v>-173.30203894927536</v>
       </c>
       <c r="U47" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J47&lt;0,-J47,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V47" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J47&gt;0,J47,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
@@ -10278,84 +10481,84 @@
         <v>7</v>
       </c>
       <c r="B48" s="6">
-        <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <f>1/(1+$B$6)^A48</f>
+        <v>0.5834903952621338</v>
       </c>
       <c r="C48">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A48&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D48">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A48&gt;=$B$8,A48&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E48" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C48*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F48" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D48*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G48" s="7">
         <f>F48*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G48</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I48" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D48*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J48" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G48-H48-E48-I48</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K48" s="7">
-        <f t="shared" si="8"/>
-        <v>3.1156007692360754</v>
+        <f>J48*B48</f>
+        <v>3.115600769236075</v>
       </c>
       <c r="L48" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A48&gt;=$B$8,A48&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M48" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G48-H48-L48</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N48" s="7">
         <f>SUM($M$41:M48)</f>
         <v>-27.962446739130428</v>
       </c>
       <c r="O48" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N48)</f>
+        <v>0.0</v>
       </c>
       <c r="P48" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O48-O47)</f>
+        <v>0.0</v>
       </c>
       <c r="Q48" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J48-P48</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R48" s="7">
-        <f t="shared" si="13"/>
-        <v>3.1156007692360754</v>
+        <f>Q48*B48</f>
+        <v>3.115600769236075</v>
       </c>
       <c r="S48" s="7">
         <f>SUM($Q$41:Q48)</f>
         <v>-167.96244673913043</v>
       </c>
       <c r="U48" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J48&lt;0,-J48,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V48" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J48&gt;0,J48,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.3">
@@ -10363,84 +10566,84 @@
         <v>8</v>
       </c>
       <c r="B49" s="6">
-        <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <f>1/(1+$B$6)^A49</f>
+        <v>0.5402688845019757</v>
       </c>
       <c r="C49">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A49&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D49">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A49&gt;=$B$8,A49&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E49" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C49*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F49" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D49*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G49" s="7">
         <f>F49*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G49</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I49" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D49*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J49" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G49-H49-E49-I49</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K49" s="7">
-        <f t="shared" si="8"/>
-        <v>2.8848155270704399</v>
+        <f>J49*B49</f>
+        <v>2.88481552707044</v>
       </c>
       <c r="L49" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A49&gt;=$B$8,A49&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M49" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G49-H49-L49</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N49" s="7">
         <f>SUM($M$41:M49)</f>
-        <v>-32.622854528985499</v>
+        <v>-32.6228545289855</v>
       </c>
       <c r="O49" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N49)</f>
+        <v>0.0</v>
       </c>
       <c r="P49" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O49-O48)</f>
+        <v>0.0</v>
       </c>
       <c r="Q49" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J49-P49</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R49" s="7">
-        <f t="shared" si="13"/>
-        <v>2.8848155270704399</v>
+        <f>Q49*B49</f>
+        <v>2.88481552707044</v>
       </c>
       <c r="S49" s="7">
         <f>SUM($Q$41:Q49)</f>
         <v>-162.6228545289855</v>
       </c>
       <c r="U49" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J49&lt;0,-J49,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V49" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J49&gt;0,J49,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.3">
@@ -10448,84 +10651,84 @@
         <v>9</v>
       </c>
       <c r="B50" s="6">
-        <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <f>1/(1+$B$6)^A50</f>
+        <v>0.5002489671314589</v>
       </c>
       <c r="C50">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A50&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D50">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A50&gt;=$B$8,A50&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E50" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C50*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F50" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D50*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G50" s="7">
         <f>F50*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H50" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G50</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I50" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D50*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J50" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G50-H50-E50-I50</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K50" s="7">
-        <f t="shared" si="8"/>
-        <v>2.6711254880281854</v>
+        <f>J50*B50</f>
+        <v>2.6711254880281845</v>
       </c>
       <c r="L50" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A50&gt;=$B$8,A50&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M50" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G50-H50-L50</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N50" s="7">
         <f>SUM($M$41:M50)</f>
-        <v>-37.283262318840571</v>
+        <v>-37.28326231884057</v>
       </c>
       <c r="O50" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N50)</f>
+        <v>0.0</v>
       </c>
       <c r="P50" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O50-O49)</f>
+        <v>0.0</v>
       </c>
       <c r="Q50" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J50-P50</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R50" s="7">
-        <f t="shared" si="13"/>
-        <v>2.6711254880281854</v>
+        <f>Q50*B50</f>
+        <v>2.6711254880281845</v>
       </c>
       <c r="S50" s="7">
         <f>SUM($Q$41:Q50)</f>
         <v>-157.28326231884057</v>
       </c>
       <c r="U50" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J50&lt;0,-J50,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V50" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J50&gt;0,J50,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.3">
@@ -10533,84 +10736,84 @@
         <v>10</v>
       </c>
       <c r="B51" s="6">
-        <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <f>1/(1+$B$6)^A51</f>
+        <v>0.46319348808468414</v>
       </c>
       <c r="C51">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A51&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D51">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A51&gt;=$B$8,A51&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E51" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C51*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F51" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D51*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G51" s="7">
         <f>F51*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H51" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G51</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I51" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D51*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J51" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G51-H51-E51-I51</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K51" s="7">
-        <f t="shared" si="8"/>
-        <v>2.4732643407668378</v>
+        <f>J51*B51</f>
+        <v>2.4732643407668373</v>
       </c>
       <c r="L51" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A51&gt;=$B$8,A51&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M51" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G51-H51-L51</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N51" s="7">
         <f>SUM($M$41:M51)</f>
-        <v>-41.943670108695642</v>
+        <v>-41.94367010869564</v>
       </c>
       <c r="O51" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N51)</f>
+        <v>0.0</v>
       </c>
       <c r="P51" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O51-O50)</f>
+        <v>0.0</v>
       </c>
       <c r="Q51" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J51-P51</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R51" s="7">
-        <f t="shared" si="13"/>
-        <v>2.4732643407668378</v>
+        <f>Q51*B51</f>
+        <v>2.4732643407668373</v>
       </c>
       <c r="S51" s="7">
         <f>SUM($Q$41:Q51)</f>
         <v>-151.94367010869564</v>
       </c>
       <c r="U51" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J51&lt;0,-J51,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V51" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J51&gt;0,J51,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.3">
@@ -10618,84 +10821,84 @@
         <v>11</v>
       </c>
       <c r="B52" s="6">
-        <f t="shared" si="0"/>
-        <v>0.42888285933767062</v>
+        <f>1/(1+$B$6)^A52</f>
+        <v>0.4288828593376705</v>
       </c>
       <c r="C52">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A52&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D52">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A52&gt;=$B$8,A52&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E52" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C52*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F52" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D52*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G52" s="7">
         <f>F52*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H52" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G52</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I52" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D52*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J52" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G52-H52-E52-I52</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K52" s="7">
-        <f t="shared" si="8"/>
-        <v>2.290059574784109</v>
+        <f>J52*B52</f>
+        <v>2.2900595747841086</v>
       </c>
       <c r="L52" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A52&gt;=$B$8,A52&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M52" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G52-H52-L52</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N52" s="7">
         <f>SUM($M$41:M52)</f>
-        <v>-46.604077898550713</v>
+        <v>-46.60407789855071</v>
       </c>
       <c r="O52" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N52)</f>
+        <v>0.0</v>
       </c>
       <c r="P52" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O52-O51)</f>
+        <v>0.0</v>
       </c>
       <c r="Q52" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J52-P52</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R52" s="7">
-        <f t="shared" si="13"/>
-        <v>2.290059574784109</v>
+        <f>Q52*B52</f>
+        <v>2.2900595747841086</v>
       </c>
       <c r="S52" s="7">
         <f>SUM($Q$41:Q52)</f>
-        <v>-146.60407789855071</v>
+        <v>-146.6040778985507</v>
       </c>
       <c r="U52" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J52&lt;0,-J52,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V52" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J52&gt;0,J52,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.3">
@@ -10703,84 +10906,84 @@
         <v>12</v>
       </c>
       <c r="B53" s="6">
-        <f t="shared" si="0"/>
-        <v>0.39711375864599124</v>
+        <f>1/(1+$B$6)^A53</f>
+        <v>0.3971137586459912</v>
       </c>
       <c r="C53">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A53&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D53">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A53&gt;=$B$8,A53&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E53" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C53*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F53" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D53*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G53" s="7">
         <f>F53*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H53" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G53</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I53" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D53*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J53" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G53-H53-E53-I53</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K53" s="7">
-        <f t="shared" si="8"/>
-        <v>2.1204255322075083</v>
+        <f>J53*B53</f>
+        <v>2.120425532207508</v>
       </c>
       <c r="L53" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A53&gt;=$B$8,A53&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M53" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G53-H53-L53</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N53" s="7">
         <f>SUM($M$41:M53)</f>
         <v>-51.264485688405784</v>
       </c>
       <c r="O53" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N53)</f>
+        <v>0.0</v>
       </c>
       <c r="P53" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O53-O52)</f>
+        <v>0.0</v>
       </c>
       <c r="Q53" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J53-P53</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R53" s="7">
-        <f t="shared" si="13"/>
-        <v>2.1204255322075083</v>
+        <f>Q53*B53</f>
+        <v>2.120425532207508</v>
       </c>
       <c r="S53" s="7">
         <f>SUM($Q$41:Q53)</f>
         <v>-141.26448568840578</v>
       </c>
       <c r="U53" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J53&lt;0,-J53,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V53" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J53&gt;0,J53,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.3">
@@ -10788,84 +10991,84 @@
         <v>13</v>
       </c>
       <c r="B54" s="6">
-        <f t="shared" si="0"/>
-        <v>0.36769792467221413</v>
+        <f>1/(1+$B$6)^A54</f>
+        <v>0.367697924672214</v>
       </c>
       <c r="C54">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A54&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D54">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A54&gt;=$B$8,A54&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E54" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C54*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F54" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D54*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G54" s="7">
         <f>F54*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H54" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G54</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I54" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D54*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J54" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G54-H54-E54-I54</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K54" s="7">
-        <f t="shared" si="8"/>
-        <v>1.9633569742662114</v>
+        <f>J54*B54</f>
+        <v>1.9633569742662107</v>
       </c>
       <c r="L54" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A54&gt;=$B$8,A54&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M54" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G54-H54-L54</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N54" s="7">
         <f>SUM($M$41:M54)</f>
         <v>-55.924893478260856</v>
       </c>
       <c r="O54" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N54)</f>
+        <v>0.0</v>
       </c>
       <c r="P54" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O54-O53)</f>
+        <v>0.0</v>
       </c>
       <c r="Q54" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J54-P54</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R54" s="7">
-        <f t="shared" si="13"/>
-        <v>1.9633569742662114</v>
+        <f>Q54*B54</f>
+        <v>1.9633569742662107</v>
       </c>
       <c r="S54" s="7">
         <f>SUM($Q$41:Q54)</f>
         <v>-135.92489347826086</v>
       </c>
       <c r="U54" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J54&lt;0,-J54,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V54" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J54&gt;0,J54,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.3">
@@ -10873,84 +11076,84 @@
         <v>14</v>
       </c>
       <c r="B55" s="6">
-        <f t="shared" si="0"/>
-        <v>0.34046104136316119</v>
+        <f>1/(1+$B$6)^A55</f>
+        <v>0.34046104136316113</v>
       </c>
       <c r="C55">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A55&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D55">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A55&gt;=$B$8,A55&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E55" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C55*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F55" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D55*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G55" s="7">
         <f>F55*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H55" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G55</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I55" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D55*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J55" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G55-H55-E55-I55</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K55" s="7">
-        <f t="shared" si="8"/>
-        <v>1.8179231243205658</v>
+        <f>J55*B55</f>
+        <v>1.8179231243205656</v>
       </c>
       <c r="L55" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A55&gt;=$B$8,A55&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M55" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G55-H55-L55</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N55" s="7">
         <f>SUM($M$41:M55)</f>
-        <v>-60.585301268115927</v>
+        <v>-60.58530126811593</v>
       </c>
       <c r="O55" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N55)</f>
+        <v>0.0</v>
       </c>
       <c r="P55" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O55-O54)</f>
+        <v>0.0</v>
       </c>
       <c r="Q55" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J55-P55</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R55" s="7">
-        <f t="shared" si="13"/>
-        <v>1.8179231243205658</v>
+        <f>Q55*B55</f>
+        <v>1.8179231243205656</v>
       </c>
       <c r="S55" s="7">
         <f>SUM($Q$41:Q55)</f>
         <v>-130.58530126811593</v>
       </c>
       <c r="U55" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J55&lt;0,-J55,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V55" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J55&gt;0,J55,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.3">
@@ -10958,71 +11161,71 @@
         <v>15</v>
       </c>
       <c r="B56" s="6">
-        <f t="shared" si="0"/>
+        <f>1/(1+$B$6)^A56</f>
         <v>0.31524170496588994</v>
       </c>
       <c r="C56">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A56&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D56">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A56&gt;=$B$8,A56&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E56" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C56*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F56" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D56*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G56" s="7">
         <f>F56*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H56" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G56</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I56" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D56*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J56" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G56-H56-E56-I56</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K56" s="7">
-        <f t="shared" si="8"/>
+        <f>J56*B56</f>
         <v>1.6832621521486717</v>
       </c>
       <c r="L56" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A56&gt;=$B$8,A56&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M56" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G56-H56-L56</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N56" s="7">
         <f>SUM($M$41:M56)</f>
-        <v>-65.245709057970998</v>
+        <v>-65.245709057971</v>
       </c>
       <c r="O56" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N56)</f>
+        <v>0.0</v>
       </c>
       <c r="P56" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O56-O55)</f>
+        <v>0.0</v>
       </c>
       <c r="Q56" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J56-P56</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R56" s="7">
-        <f t="shared" si="13"/>
+        <f>Q56*B56</f>
         <v>1.6832621521486717</v>
       </c>
       <c r="S56" s="7">
@@ -11030,12 +11233,12 @@
         <v>-125.245709057971</v>
       </c>
       <c r="U56" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J56&lt;0,-J56,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V56" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J56&gt;0,J56,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.3">
@@ -11043,84 +11246,84 @@
         <v>16</v>
       </c>
       <c r="B57" s="6">
-        <f t="shared" si="0"/>
-        <v>0.29189046756100923</v>
+        <f>1/(1+$B$6)^A57</f>
+        <v>0.29189046756100917</v>
       </c>
       <c r="C57">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A57&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D57">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A57&gt;=$B$8,A57&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E57" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C57*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F57" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D57*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G57" s="7">
         <f>F57*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H57" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G57</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I57" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D57*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J57" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G57-H57-E57-I57</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K57" s="7">
-        <f t="shared" si="8"/>
-        <v>1.5585760668043258</v>
+        <f>J57*B57</f>
+        <v>1.5585760668043256</v>
       </c>
       <c r="L57" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A57&gt;=$B$8,A57&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M57" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G57-H57-L57</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N57" s="7">
         <f>SUM($M$41:M57)</f>
         <v>-69.90611684782607</v>
       </c>
       <c r="O57" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N57)</f>
+        <v>0.0</v>
       </c>
       <c r="P57" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O57-O56)</f>
+        <v>0.0</v>
       </c>
       <c r="Q57" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J57-P57</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R57" s="7">
-        <f t="shared" si="13"/>
-        <v>1.5585760668043258</v>
+        <f>Q57*B57</f>
+        <v>1.5585760668043256</v>
       </c>
       <c r="S57" s="7">
         <f>SUM($Q$41:Q57)</f>
         <v>-119.90611684782607</v>
       </c>
       <c r="U57" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J57&lt;0,-J57,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V57" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J57&gt;0,J57,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.3">
@@ -11128,84 +11331,84 @@
         <v>17</v>
       </c>
       <c r="B58" s="6">
-        <f t="shared" si="0"/>
-        <v>0.27026895144537894</v>
+        <f>1/(1+$B$6)^A58</f>
+        <v>0.2702689514453788</v>
       </c>
       <c r="C58">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A58&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D58">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A58&gt;=$B$8,A58&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E58" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C58*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F58" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D58*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G58" s="7">
         <f>F58*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H58" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G58</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I58" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D58*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J58" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G58-H58-E58-I58</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K58" s="7">
-        <f t="shared" si="8"/>
-        <v>1.4431259877817832</v>
+        <f>J58*B58</f>
+        <v>1.4431259877817828</v>
       </c>
       <c r="L58" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A58&gt;=$B$8,A58&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M58" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G58-H58-L58</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N58" s="7">
         <f>SUM($M$41:M58)</f>
-        <v>-74.566524637681141</v>
+        <v>-74.56652463768114</v>
       </c>
       <c r="O58" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N58)</f>
+        <v>0.0</v>
       </c>
       <c r="P58" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O58-O57)</f>
+        <v>0.0</v>
       </c>
       <c r="Q58" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J58-P58</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R58" s="7">
-        <f t="shared" si="13"/>
-        <v>1.4431259877817832</v>
+        <f>Q58*B58</f>
+        <v>1.4431259877817828</v>
       </c>
       <c r="S58" s="7">
         <f>SUM($Q$41:Q58)</f>
         <v>-114.56652463768114</v>
       </c>
       <c r="U58" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J58&lt;0,-J58,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V58" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J58&gt;0,J58,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.3">
@@ -11213,84 +11416,84 @@
         <v>18</v>
       </c>
       <c r="B59" s="6">
-        <f t="shared" si="0"/>
-        <v>0.25024902911609154</v>
+        <f>1/(1+$B$6)^A59</f>
+        <v>0.2502490291160915</v>
       </c>
       <c r="C59">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A59&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D59">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A59&gt;=$B$8,A59&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E59" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C59*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F59" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D59*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G59" s="7">
         <f>F59*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H59" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G59</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I59" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D59*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J59" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G59-H59-E59-I59</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K59" s="7">
-        <f t="shared" si="8"/>
-        <v>1.3362277664646138</v>
+        <f>J59*B59</f>
+        <v>1.3362277664646136</v>
       </c>
       <c r="L59" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A59&gt;=$B$8,A59&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M59" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G59-H59-L59</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N59" s="7">
         <f>SUM($M$41:M59)</f>
-        <v>-79.226932427536212</v>
+        <v>-79.22693242753621</v>
       </c>
       <c r="O59" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N59)</f>
+        <v>0.0</v>
       </c>
       <c r="P59" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O59-O58)</f>
+        <v>0.0</v>
       </c>
       <c r="Q59" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J59-P59</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R59" s="7">
-        <f t="shared" si="13"/>
-        <v>1.3362277664646138</v>
+        <f>Q59*B59</f>
+        <v>1.3362277664646136</v>
       </c>
       <c r="S59" s="7">
         <f>SUM($Q$41:Q59)</f>
         <v>-109.22693242753621</v>
       </c>
       <c r="U59" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J59&lt;0,-J59,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V59" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J59&gt;0,J59,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.3">
@@ -11298,84 +11501,84 @@
         <v>19</v>
       </c>
       <c r="B60" s="6">
-        <f t="shared" si="0"/>
-        <v>0.23171206399638106</v>
+        <f>1/(1+$B$6)^A60</f>
+        <v>0.231712063996381</v>
       </c>
       <c r="C60">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A60&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D60">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A60&gt;=$B$8,A60&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E60" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C60*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F60" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D60*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G60" s="7">
         <f>F60*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H60" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G60</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I60" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D60*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J60" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G60-H60-E60-I60</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K60" s="7">
-        <f t="shared" si="8"/>
-        <v>1.2372479319116796</v>
+        <f>J60*B60</f>
+        <v>1.2372479319116791</v>
       </c>
       <c r="L60" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A60&gt;=$B$8,A60&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M60" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G60-H60-L60</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N60" s="7">
         <f>SUM($M$41:M60)</f>
-        <v>-83.887340217391284</v>
+        <v>-83.88734021739128</v>
       </c>
       <c r="O60" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N60)</f>
+        <v>0.0</v>
       </c>
       <c r="P60" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O60-O59)</f>
+        <v>0.0</v>
       </c>
       <c r="Q60" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J60-P60</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R60" s="7">
-        <f t="shared" si="13"/>
-        <v>1.2372479319116796</v>
+        <f>Q60*B60</f>
+        <v>1.2372479319116791</v>
       </c>
       <c r="S60" s="7">
         <f>SUM($Q$41:Q60)</f>
         <v>-103.88734021739128</v>
       </c>
       <c r="U60" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J60&lt;0,-J60,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V60" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J60&gt;0,J60,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.3">
@@ -11383,84 +11586,84 @@
         <v>20</v>
       </c>
       <c r="B61" s="6">
-        <f t="shared" si="0"/>
-        <v>0.21454820740405653</v>
+        <f>1/(1+$B$6)^A61</f>
+        <v>0.21454820740405645</v>
       </c>
       <c r="C61">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A61&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D61">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A61&gt;=$B$8,A61&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E61" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C61*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F61" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D61*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G61" s="7">
         <f>F61*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H61" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G61</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I61" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D61*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J61" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G61-H61-E61-I61</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K61" s="7">
-        <f t="shared" si="8"/>
-        <v>1.1455999369552587</v>
+        <f>J61*B61</f>
+        <v>1.1455999369552583</v>
       </c>
       <c r="L61" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A61&gt;=$B$8,A61&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M61" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G61-H61-L61</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N61" s="7">
         <f>SUM($M$41:M61)</f>
-        <v>-88.547748007246355</v>
+        <v>-88.54774800724635</v>
       </c>
       <c r="O61" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N61)</f>
+        <v>0.0</v>
       </c>
       <c r="P61" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O61-O60)</f>
+        <v>0.0</v>
       </c>
       <c r="Q61" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J61-P61</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R61" s="7">
-        <f t="shared" si="13"/>
-        <v>1.1455999369552587</v>
+        <f>Q61*B61</f>
+        <v>1.1455999369552583</v>
       </c>
       <c r="S61" s="7">
         <f>SUM($Q$41:Q61)</f>
-        <v>-98.547748007246355</v>
+        <v>-98.54774800724635</v>
       </c>
       <c r="U61" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J61&lt;0,-J61,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V61" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J61&gt;0,J61,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.3">
@@ -11468,84 +11671,84 @@
         <v>21</v>
       </c>
       <c r="B62" s="6">
-        <f t="shared" si="0"/>
-        <v>0.19865574759634863</v>
+        <f>1/(1+$B$6)^A62</f>
+        <v>0.19865574759634858</v>
       </c>
       <c r="C62">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A62&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D62">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>IF(AND(A62&gt;=$B$8,A62&lt;$B$8+$B$7),1,0)</f>
+        <v>1.0</v>
       </c>
       <c r="E62" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C62*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F62" s="12">
-        <f t="shared" si="4"/>
-        <v>4.9250000000000007</v>
+        <f>D62*$B$14</f>
+        <v>4.925000000000001</v>
       </c>
       <c r="G62" s="7">
         <f>F62*($B$13+$B$19*Inputs!$D$148)/1000</f>
         <v>23.339575000000004</v>
       </c>
       <c r="H62" s="7">
-        <f t="shared" si="5"/>
+        <f>$B$5*G62</f>
         <v>17.999982789855075</v>
       </c>
       <c r="I62" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D62*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J62" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3395922101449287</v>
+        <f>G62-H62-E62-I62</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="K62" s="7">
-        <f t="shared" si="8"/>
-        <v>1.0607406823659802</v>
+        <f>J62*B62</f>
+        <v>1.06074068236598</v>
       </c>
       <c r="L62" s="7">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <f>IF(AND(A62&gt;=$B$8,A62&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>10.0</v>
       </c>
       <c r="M62" s="7">
-        <f t="shared" si="10"/>
-        <v>-4.6604077898550713</v>
+        <f>G62-H62-L62</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="N62" s="7">
         <f>SUM($M$41:M62)</f>
-        <v>-93.208155797101426</v>
+        <v>-93.20815579710143</v>
       </c>
       <c r="O62" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N62)</f>
+        <v>0.0</v>
       </c>
       <c r="P62" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O62-O61)</f>
+        <v>0.0</v>
       </c>
       <c r="Q62" s="7">
-        <f t="shared" si="12"/>
-        <v>5.3395922101449287</v>
+        <f>J62-P62</f>
+        <v>5.339592210144929</v>
       </c>
       <c r="R62" s="7">
-        <f t="shared" si="13"/>
-        <v>1.0607406823659802</v>
+        <f>Q62*B62</f>
+        <v>1.06074068236598</v>
       </c>
       <c r="S62" s="7">
         <f>SUM($Q$41:Q62)</f>
-        <v>-93.208155797101426</v>
+        <v>-93.20815579710143</v>
       </c>
       <c r="U62" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J62&lt;0,-J62,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V62" s="7">
-        <f t="shared" si="15"/>
-        <v>5.3395922101449287</v>
+        <f>IF(J62&gt;0,J62,NA())</f>
+        <v>5.339592210144929</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.3">
@@ -11553,1441 +11756,2167 @@
         <v>22</v>
       </c>
       <c r="B63" s="6">
-        <f t="shared" si="0"/>
-        <v>0.18394050703365611</v>
+        <f>1/(1+$B$6)^A63</f>
+        <v>0.18394050703365605</v>
       </c>
       <c r="C63">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IF(A63&lt;$B$8,1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="D63">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF(AND(A63&gt;=$B$8,A63&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
       </c>
       <c r="E63" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>C63*$B$9/$B$8</f>
+        <v>0.0</v>
       </c>
       <c r="F63" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>D63*$B$14</f>
+        <v>0.0</v>
       </c>
       <c r="G63" s="7">
         <f>F63*($B$13+$B$19*Inputs!$D$148)/1000</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H63" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>$B$5*G63</f>
+        <v>0.0</v>
       </c>
       <c r="I63" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>D63*$B$16*$B$9</f>
+        <v>0.0</v>
       </c>
       <c r="J63" s="7">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>G63-H63-E63-I63</f>
+        <v>0.0</v>
       </c>
       <c r="K63" s="7">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>J63*B63</f>
+        <v>0.0</v>
       </c>
       <c r="L63" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>IF(AND(A63&gt;=$B$8,A63&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
       </c>
       <c r="M63" s="7">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>G63-H63-L63</f>
+        <v>0.0</v>
       </c>
       <c r="N63" s="7">
         <f>SUM($M$41:M63)</f>
-        <v>-93.208155797101426</v>
+        <v>-93.20815579710143</v>
       </c>
       <c r="O63" s="7">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>$B$17*MAX(0,N63)</f>
+        <v>0.0</v>
       </c>
       <c r="P63" s="7">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>MAX(0,O63-O62)</f>
+        <v>0.0</v>
       </c>
       <c r="Q63" s="7">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>J63-P63</f>
+        <v>0.0</v>
       </c>
       <c r="R63" s="7">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>Q63*B63</f>
+        <v>0.0</v>
       </c>
       <c r="S63" s="7">
         <f>SUM($Q$41:Q63)</f>
-        <v>-93.208155797101426</v>
+        <v>-93.20815579710143</v>
       </c>
       <c r="U63" s="7" t="e">
-        <f t="shared" si="14"/>
+        <f>IF(J63&lt;0,-J63,NA())</f>
         <v>#N/A</v>
       </c>
       <c r="V63" s="7" t="e">
-        <f t="shared" si="15"/>
+        <f>IF(J63&gt;0,J63,NA())</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row spans="1:22" x14ac:dyDescent="0.3" r="64">
+      <c r="A64">
+        <v>23</v>
+      </c>
+      <c r="B64" s="6">
+        <f>1/(1+$B$6)^A64</f>
+        <v>0.17031528429042228</v>
+      </c>
+      <c r="C64">
+        <f>IF(A64&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D64">
+        <f>IF(AND(A64&gt;=$B$8,A64&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E64" s="7">
+        <f>C64*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F64" s="12">
+        <f>D64*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G64" s="7">
+        <f>F64*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H64" s="7">
+        <f>$B$5*G64</f>
+        <v>0.0</v>
+      </c>
+      <c r="I64" s="7">
+        <f>D64*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J64" s="7">
+        <f>G64-H64-E64-I64</f>
+        <v>0.0</v>
+      </c>
+      <c r="K64" s="7">
+        <f>J64*B64</f>
+        <v>0.0</v>
+      </c>
+      <c r="L64" s="7">
+        <f>IF(AND(A64&gt;=$B$8,A64&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M64" s="7">
+        <f>G64-H64-L64</f>
+        <v>0.0</v>
+      </c>
+      <c r="N64" s="7">
+        <f>SUM($M$41:M64)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O64" s="7">
+        <f>$B$17*MAX(0,N64)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P64" s="7">
+        <f>MAX(0,O64-O63)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q64" s="7">
+        <f>J64-P64</f>
+        <v>0.0</v>
+      </c>
+      <c r="R64" s="7">
+        <f>Q64*B64</f>
+        <v>0.0</v>
+      </c>
+      <c r="S64" s="7">
+        <f>SUM($Q$41:Q64)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U64" s="7" t="e">
+        <f>IF(J64&lt;0,-J64,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V64" s="7" t="e">
+        <f>IF(J64&gt;0,J64,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="65">
+      <c r="A65">
+        <v>24</v>
+      </c>
+      <c r="B65" s="6">
+        <f>1/(1+$B$6)^A65</f>
+        <v>0.15769933730594654</v>
+      </c>
+      <c r="C65">
+        <f>IF(A65&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D65">
+        <f>IF(AND(A65&gt;=$B$8,A65&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E65" s="7">
+        <f>C65*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F65" s="12">
+        <f>D65*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G65" s="7">
+        <f>F65*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H65" s="7">
+        <f>$B$5*G65</f>
+        <v>0.0</v>
+      </c>
+      <c r="I65" s="7">
+        <f>D65*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J65" s="7">
+        <f>G65-H65-E65-I65</f>
+        <v>0.0</v>
+      </c>
+      <c r="K65" s="7">
+        <f>J65*B65</f>
+        <v>0.0</v>
+      </c>
+      <c r="L65" s="7">
+        <f>IF(AND(A65&gt;=$B$8,A65&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M65" s="7">
+        <f>G65-H65-L65</f>
+        <v>0.0</v>
+      </c>
+      <c r="N65" s="7">
+        <f>SUM($M$41:M65)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O65" s="7">
+        <f>$B$17*MAX(0,N65)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P65" s="7">
+        <f>MAX(0,O65-O64)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q65" s="7">
+        <f>J65-P65</f>
+        <v>0.0</v>
+      </c>
+      <c r="R65" s="7">
+        <f>Q65*B65</f>
+        <v>0.0</v>
+      </c>
+      <c r="S65" s="7">
+        <f>SUM($Q$41:Q65)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U65" s="7" t="e">
+        <f>IF(J65&lt;0,-J65,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V65" s="7" t="e">
+        <f>IF(J65&gt;0,J65,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="66">
+      <c r="A66">
+        <v>25</v>
+      </c>
+      <c r="B66" s="6">
+        <f>1/(1+$B$6)^A66</f>
+        <v>0.14601790491291344</v>
+      </c>
+      <c r="C66">
+        <f>IF(A66&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D66">
+        <f>IF(AND(A66&gt;=$B$8,A66&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E66" s="7">
+        <f>C66*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F66" s="12">
+        <f>D66*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G66" s="7">
+        <f>F66*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H66" s="7">
+        <f>$B$5*G66</f>
+        <v>0.0</v>
+      </c>
+      <c r="I66" s="7">
+        <f>D66*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J66" s="7">
+        <f>G66-H66-E66-I66</f>
+        <v>0.0</v>
+      </c>
+      <c r="K66" s="7">
+        <f>J66*B66</f>
+        <v>0.0</v>
+      </c>
+      <c r="L66" s="7">
+        <f>IF(AND(A66&gt;=$B$8,A66&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M66" s="7">
+        <f>G66-H66-L66</f>
+        <v>0.0</v>
+      </c>
+      <c r="N66" s="7">
+        <f>SUM($M$41:M66)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O66" s="7">
+        <f>$B$17*MAX(0,N66)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P66" s="7">
+        <f>MAX(0,O66-O65)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q66" s="7">
+        <f>J66-P66</f>
+        <v>0.0</v>
+      </c>
+      <c r="R66" s="7">
+        <f>Q66*B66</f>
+        <v>0.0</v>
+      </c>
+      <c r="S66" s="7">
+        <f>SUM($Q$41:Q66)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U66" s="7" t="e">
+        <f>IF(J66&lt;0,-J66,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V66" s="7" t="e">
+        <f>IF(J66&gt;0,J66,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="67">
+      <c r="A67">
+        <v>26</v>
+      </c>
+      <c r="B67" s="6">
+        <f>1/(1+$B$6)^A67</f>
+        <v>0.1352017638082532</v>
+      </c>
+      <c r="C67">
+        <f>IF(A67&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D67">
+        <f>IF(AND(A67&gt;=$B$8,A67&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E67" s="7">
+        <f>C67*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F67" s="12">
+        <f>D67*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G67" s="7">
+        <f>F67*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H67" s="7">
+        <f>$B$5*G67</f>
+        <v>0.0</v>
+      </c>
+      <c r="I67" s="7">
+        <f>D67*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J67" s="7">
+        <f>G67-H67-E67-I67</f>
+        <v>0.0</v>
+      </c>
+      <c r="K67" s="7">
+        <f>J67*B67</f>
+        <v>0.0</v>
+      </c>
+      <c r="L67" s="7">
+        <f>IF(AND(A67&gt;=$B$8,A67&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M67" s="7">
+        <f>G67-H67-L67</f>
+        <v>0.0</v>
+      </c>
+      <c r="N67" s="7">
+        <f>SUM($M$41:M67)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O67" s="7">
+        <f>$B$17*MAX(0,N67)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P67" s="7">
+        <f>MAX(0,O67-O66)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q67" s="7">
+        <f>J67-P67</f>
+        <v>0.0</v>
+      </c>
+      <c r="R67" s="7">
+        <f>Q67*B67</f>
+        <v>0.0</v>
+      </c>
+      <c r="S67" s="7">
+        <f>SUM($Q$41:Q67)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U67" s="7" t="e">
+        <f>IF(J67&lt;0,-J67,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V67" s="7" t="e">
+        <f>IF(J67&gt;0,J67,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="68">
+      <c r="A68">
+        <v>27</v>
+      </c>
+      <c r="B68" s="6">
+        <f>1/(1+$B$6)^A68</f>
+        <v>0.12518681834097517</v>
+      </c>
+      <c r="C68">
+        <f>IF(A68&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D68">
+        <f>IF(AND(A68&gt;=$B$8,A68&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E68" s="7">
+        <f>C68*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F68" s="12">
+        <f>D68*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G68" s="7">
+        <f>F68*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H68" s="7">
+        <f>$B$5*G68</f>
+        <v>0.0</v>
+      </c>
+      <c r="I68" s="7">
+        <f>D68*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J68" s="7">
+        <f>G68-H68-E68-I68</f>
+        <v>0.0</v>
+      </c>
+      <c r="K68" s="7">
+        <f>J68*B68</f>
+        <v>0.0</v>
+      </c>
+      <c r="L68" s="7">
+        <f>IF(AND(A68&gt;=$B$8,A68&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M68" s="7">
+        <f>G68-H68-L68</f>
+        <v>0.0</v>
+      </c>
+      <c r="N68" s="7">
+        <f>SUM($M$41:M68)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O68" s="7">
+        <f>$B$17*MAX(0,N68)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P68" s="7">
+        <f>MAX(0,O68-O67)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q68" s="7">
+        <f>J68-P68</f>
+        <v>0.0</v>
+      </c>
+      <c r="R68" s="7">
+        <f>Q68*B68</f>
+        <v>0.0</v>
+      </c>
+      <c r="S68" s="7">
+        <f>SUM($Q$41:Q68)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U68" s="7" t="e">
+        <f>IF(J68&lt;0,-J68,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V68" s="7" t="e">
+        <f>IF(J68&gt;0,J68,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="69">
+      <c r="A69">
+        <v>28</v>
+      </c>
+      <c r="B69" s="6">
+        <f>1/(1+$B$6)^A69</f>
+        <v>0.1159137206860881</v>
+      </c>
+      <c r="C69">
+        <f>IF(A69&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D69">
+        <f>IF(AND(A69&gt;=$B$8,A69&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E69" s="7">
+        <f>C69*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F69" s="12">
+        <f>D69*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G69" s="7">
+        <f>F69*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H69" s="7">
+        <f>$B$5*G69</f>
+        <v>0.0</v>
+      </c>
+      <c r="I69" s="7">
+        <f>D69*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J69" s="7">
+        <f>G69-H69-E69-I69</f>
+        <v>0.0</v>
+      </c>
+      <c r="K69" s="7">
+        <f>J69*B69</f>
+        <v>0.0</v>
+      </c>
+      <c r="L69" s="7">
+        <f>IF(AND(A69&gt;=$B$8,A69&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M69" s="7">
+        <f>G69-H69-L69</f>
+        <v>0.0</v>
+      </c>
+      <c r="N69" s="7">
+        <f>SUM($M$41:M69)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O69" s="7">
+        <f>$B$17*MAX(0,N69)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P69" s="7">
+        <f>MAX(0,O69-O68)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q69" s="7">
+        <f>J69-P69</f>
+        <v>0.0</v>
+      </c>
+      <c r="R69" s="7">
+        <f>Q69*B69</f>
+        <v>0.0</v>
+      </c>
+      <c r="S69" s="7">
+        <f>SUM($Q$41:Q69)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U69" s="7" t="e">
+        <f>IF(J69&lt;0,-J69,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V69" s="7" t="e">
+        <f>IF(J69&gt;0,J69,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="70">
+      <c r="A70">
+        <v>29</v>
+      </c>
+      <c r="B70" s="6">
+        <f>1/(1+$B$6)^A70</f>
+        <v>0.10732751915378527</v>
+      </c>
+      <c r="C70">
+        <f>IF(A70&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D70">
+        <f>IF(AND(A70&gt;=$B$8,A70&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E70" s="7">
+        <f>C70*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F70" s="12">
+        <f>D70*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G70" s="7">
+        <f>F70*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H70" s="7">
+        <f>$B$5*G70</f>
+        <v>0.0</v>
+      </c>
+      <c r="I70" s="7">
+        <f>D70*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J70" s="7">
+        <f>G70-H70-E70-I70</f>
+        <v>0.0</v>
+      </c>
+      <c r="K70" s="7">
+        <f>J70*B70</f>
+        <v>0.0</v>
+      </c>
+      <c r="L70" s="7">
+        <f>IF(AND(A70&gt;=$B$8,A70&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M70" s="7">
+        <f>G70-H70-L70</f>
+        <v>0.0</v>
+      </c>
+      <c r="N70" s="7">
+        <f>SUM($M$41:M70)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O70" s="7">
+        <f>$B$17*MAX(0,N70)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P70" s="7">
+        <f>MAX(0,O70-O69)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q70" s="7">
+        <f>J70-P70</f>
+        <v>0.0</v>
+      </c>
+      <c r="R70" s="7">
+        <f>Q70*B70</f>
+        <v>0.0</v>
+      </c>
+      <c r="S70" s="7">
+        <f>SUM($Q$41:Q70)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U70" s="7" t="e">
+        <f>IF(J70&lt;0,-J70,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V70" s="7" t="e">
+        <f>IF(J70&gt;0,J70,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="71">
+      <c r="A71">
+        <v>30</v>
+      </c>
+      <c r="B71" s="6">
+        <f>1/(1+$B$6)^A71</f>
+        <v>0.09937733254980118</v>
+      </c>
+      <c r="C71">
+        <f>IF(A71&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D71">
+        <f>IF(AND(A71&gt;=$B$8,A71&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E71" s="7">
+        <f>C71*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F71" s="12">
+        <f>D71*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G71" s="7">
+        <f>F71*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H71" s="7">
+        <f>$B$5*G71</f>
+        <v>0.0</v>
+      </c>
+      <c r="I71" s="7">
+        <f>D71*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J71" s="7">
+        <f>G71-H71-E71-I71</f>
+        <v>0.0</v>
+      </c>
+      <c r="K71" s="7">
+        <f>J71*B71</f>
+        <v>0.0</v>
+      </c>
+      <c r="L71" s="7">
+        <f>IF(AND(A71&gt;=$B$8,A71&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M71" s="7">
+        <f>G71-H71-L71</f>
+        <v>0.0</v>
+      </c>
+      <c r="N71" s="7">
+        <f>SUM($M$41:M71)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O71" s="7">
+        <f>$B$17*MAX(0,N71)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P71" s="7">
+        <f>MAX(0,O71-O70)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q71" s="7">
+        <f>J71-P71</f>
+        <v>0.0</v>
+      </c>
+      <c r="R71" s="7">
+        <f>Q71*B71</f>
+        <v>0.0</v>
+      </c>
+      <c r="S71" s="7">
+        <f>SUM($Q$41:Q71)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U71" s="7" t="e">
+        <f>IF(J71&lt;0,-J71,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V71" s="7" t="e">
+        <f>IF(J71&gt;0,J71,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="72">
+      <c r="A72">
+        <v>31</v>
+      </c>
+      <c r="B72" s="6">
+        <f>1/(1+$B$6)^A72</f>
+        <v>0.0920160486572233</v>
+      </c>
+      <c r="C72">
+        <f>IF(A72&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D72">
+        <f>IF(AND(A72&gt;=$B$8,A72&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E72" s="7">
+        <f>C72*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F72" s="12">
+        <f>D72*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G72" s="7">
+        <f>F72*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H72" s="7">
+        <f>$B$5*G72</f>
+        <v>0.0</v>
+      </c>
+      <c r="I72" s="7">
+        <f>D72*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J72" s="7">
+        <f>G72-H72-E72-I72</f>
+        <v>0.0</v>
+      </c>
+      <c r="K72" s="7">
+        <f>J72*B72</f>
+        <v>0.0</v>
+      </c>
+      <c r="L72" s="7">
+        <f>IF(AND(A72&gt;=$B$8,A72&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M72" s="7">
+        <f>G72-H72-L72</f>
+        <v>0.0</v>
+      </c>
+      <c r="N72" s="7">
+        <f>SUM($M$41:M72)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O72" s="7">
+        <f>$B$17*MAX(0,N72)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P72" s="7">
+        <f>MAX(0,O72-O71)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q72" s="7">
+        <f>J72-P72</f>
+        <v>0.0</v>
+      </c>
+      <c r="R72" s="7">
+        <f>Q72*B72</f>
+        <v>0.0</v>
+      </c>
+      <c r="S72" s="7">
+        <f>SUM($Q$41:Q72)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U72" s="7" t="e">
+        <f>IF(J72&lt;0,-J72,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V72" s="7" t="e">
+        <f>IF(J72&gt;0,J72,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="73">
+      <c r="A73">
+        <v>32</v>
+      </c>
+      <c r="B73" s="6">
+        <f>1/(1+$B$6)^A73</f>
+        <v>0.08520004505298454</v>
+      </c>
+      <c r="C73">
+        <f>IF(A73&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D73">
+        <f>IF(AND(A73&gt;=$B$8,A73&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="7">
+        <f>C73*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F73" s="12">
+        <f>D73*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G73" s="7">
+        <f>F73*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H73" s="7">
+        <f>$B$5*G73</f>
+        <v>0.0</v>
+      </c>
+      <c r="I73" s="7">
+        <f>D73*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J73" s="7">
+        <f>G73-H73-E73-I73</f>
+        <v>0.0</v>
+      </c>
+      <c r="K73" s="7">
+        <f>J73*B73</f>
+        <v>0.0</v>
+      </c>
+      <c r="L73" s="7">
+        <f>IF(AND(A73&gt;=$B$8,A73&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M73" s="7">
+        <f>G73-H73-L73</f>
+        <v>0.0</v>
+      </c>
+      <c r="N73" s="7">
+        <f>SUM($M$41:M73)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O73" s="7">
+        <f>$B$17*MAX(0,N73)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P73" s="7">
+        <f>MAX(0,O73-O72)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q73" s="7">
+        <f>J73-P73</f>
+        <v>0.0</v>
+      </c>
+      <c r="R73" s="7">
+        <f>Q73*B73</f>
+        <v>0.0</v>
+      </c>
+      <c r="S73" s="7">
+        <f>SUM($Q$41:Q73)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U73" s="7" t="e">
+        <f>IF(J73&lt;0,-J73,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V73" s="7" t="e">
+        <f>IF(J73&gt;0,J73,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="74">
+      <c r="A74">
+        <v>33</v>
+      </c>
+      <c r="B74" s="6">
+        <f>1/(1+$B$6)^A74</f>
+        <v>0.07888893060461531</v>
+      </c>
+      <c r="C74">
+        <f>IF(A74&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D74">
+        <f>IF(AND(A74&gt;=$B$8,A74&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="7">
+        <f>C74*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F74" s="12">
+        <f>D74*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G74" s="7">
+        <f>F74*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H74" s="7">
+        <f>$B$5*G74</f>
+        <v>0.0</v>
+      </c>
+      <c r="I74" s="7">
+        <f>D74*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J74" s="7">
+        <f>G74-H74-E74-I74</f>
+        <v>0.0</v>
+      </c>
+      <c r="K74" s="7">
+        <f>J74*B74</f>
+        <v>0.0</v>
+      </c>
+      <c r="L74" s="7">
+        <f>IF(AND(A74&gt;=$B$8,A74&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M74" s="7">
+        <f>G74-H74-L74</f>
+        <v>0.0</v>
+      </c>
+      <c r="N74" s="7">
+        <f>SUM($M$41:M74)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O74" s="7">
+        <f>$B$17*MAX(0,N74)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P74" s="7">
+        <f>MAX(0,O74-O73)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q74" s="7">
+        <f>J74-P74</f>
+        <v>0.0</v>
+      </c>
+      <c r="R74" s="7">
+        <f>Q74*B74</f>
+        <v>0.0</v>
+      </c>
+      <c r="S74" s="7">
+        <f>SUM($Q$41:Q74)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U74" s="7" t="e">
+        <f>IF(J74&lt;0,-J74,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V74" s="7" t="e">
+        <f>IF(J74&gt;0,J74,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="75">
+      <c r="A75">
+        <v>34</v>
+      </c>
+      <c r="B75" s="6">
+        <f>1/(1+$B$6)^A75</f>
+        <v>0.07304530611538454</v>
+      </c>
+      <c r="C75">
+        <f>IF(A75&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D75">
+        <f>IF(AND(A75&gt;=$B$8,A75&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E75" s="7">
+        <f>C75*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F75" s="12">
+        <f>D75*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G75" s="7">
+        <f>F75*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H75" s="7">
+        <f>$B$5*G75</f>
+        <v>0.0</v>
+      </c>
+      <c r="I75" s="7">
+        <f>D75*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J75" s="7">
+        <f>G75-H75-E75-I75</f>
+        <v>0.0</v>
+      </c>
+      <c r="K75" s="7">
+        <f>J75*B75</f>
+        <v>0.0</v>
+      </c>
+      <c r="L75" s="7">
+        <f>IF(AND(A75&gt;=$B$8,A75&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M75" s="7">
+        <f>G75-H75-L75</f>
+        <v>0.0</v>
+      </c>
+      <c r="N75" s="7">
+        <f>SUM($M$41:M75)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O75" s="7">
+        <f>$B$17*MAX(0,N75)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P75" s="7">
+        <f>MAX(0,O75-O74)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q75" s="7">
+        <f>J75-P75</f>
+        <v>0.0</v>
+      </c>
+      <c r="R75" s="7">
+        <f>Q75*B75</f>
+        <v>0.0</v>
+      </c>
+      <c r="S75" s="7">
+        <f>SUM($Q$41:Q75)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U75" s="7" t="e">
+        <f>IF(J75&lt;0,-J75,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V75" s="7" t="e">
+        <f>IF(J75&gt;0,J75,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="76">
+      <c r="A76">
+        <v>35</v>
+      </c>
+      <c r="B76" s="6">
+        <f>1/(1+$B$6)^A76</f>
+        <v>0.06763454269943012</v>
+      </c>
+      <c r="C76">
+        <f>IF(A76&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D76">
+        <f>IF(AND(A76&gt;=$B$8,A76&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E76" s="7">
+        <f>C76*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F76" s="12">
+        <f>D76*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G76" s="7">
+        <f>F76*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H76" s="7">
+        <f>$B$5*G76</f>
+        <v>0.0</v>
+      </c>
+      <c r="I76" s="7">
+        <f>D76*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J76" s="7">
+        <f>G76-H76-E76-I76</f>
+        <v>0.0</v>
+      </c>
+      <c r="K76" s="7">
+        <f>J76*B76</f>
+        <v>0.0</v>
+      </c>
+      <c r="L76" s="7">
+        <f>IF(AND(A76&gt;=$B$8,A76&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M76" s="7">
+        <f>G76-H76-L76</f>
+        <v>0.0</v>
+      </c>
+      <c r="N76" s="7">
+        <f>SUM($M$41:M76)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O76" s="7">
+        <f>$B$17*MAX(0,N76)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P76" s="7">
+        <f>MAX(0,O76-O75)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q76" s="7">
+        <f>J76-P76</f>
+        <v>0.0</v>
+      </c>
+      <c r="R76" s="7">
+        <f>Q76*B76</f>
+        <v>0.0</v>
+      </c>
+      <c r="S76" s="7">
+        <f>SUM($Q$41:Q76)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U76" s="7" t="e">
+        <f>IF(J76&lt;0,-J76,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V76" s="7" t="e">
+        <f>IF(J76&gt;0,J76,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="77">
+      <c r="A77">
+        <v>36</v>
+      </c>
+      <c r="B77" s="6">
+        <f>1/(1+$B$6)^A77</f>
+        <v>0.0626245765735464</v>
+      </c>
+      <c r="C77">
+        <f>IF(A77&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D77">
+        <f>IF(AND(A77&gt;=$B$8,A77&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E77" s="7">
+        <f>C77*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F77" s="12">
+        <f>D77*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G77" s="7">
+        <f>F77*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H77" s="7">
+        <f>$B$5*G77</f>
+        <v>0.0</v>
+      </c>
+      <c r="I77" s="7">
+        <f>D77*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J77" s="7">
+        <f>G77-H77-E77-I77</f>
+        <v>0.0</v>
+      </c>
+      <c r="K77" s="7">
+        <f>J77*B77</f>
+        <v>0.0</v>
+      </c>
+      <c r="L77" s="7">
+        <f>IF(AND(A77&gt;=$B$8,A77&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M77" s="7">
+        <f>G77-H77-L77</f>
+        <v>0.0</v>
+      </c>
+      <c r="N77" s="7">
+        <f>SUM($M$41:M77)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O77" s="7">
+        <f>$B$17*MAX(0,N77)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P77" s="7">
+        <f>MAX(0,O77-O76)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q77" s="7">
+        <f>J77-P77</f>
+        <v>0.0</v>
+      </c>
+      <c r="R77" s="7">
+        <f>Q77*B77</f>
+        <v>0.0</v>
+      </c>
+      <c r="S77" s="7">
+        <f>SUM($Q$41:Q77)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U77" s="7" t="e">
+        <f>IF(J77&lt;0,-J77,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V77" s="7" t="e">
+        <f>IF(J77&gt;0,J77,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="78">
+      <c r="A78">
+        <v>37</v>
+      </c>
+      <c r="B78" s="6">
+        <f>1/(1+$B$6)^A78</f>
+        <v>0.05798571904958</v>
+      </c>
+      <c r="C78">
+        <f>IF(A78&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D78">
+        <f>IF(AND(A78&gt;=$B$8,A78&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E78" s="7">
+        <f>C78*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F78" s="12">
+        <f>D78*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G78" s="7">
+        <f>F78*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H78" s="7">
+        <f>$B$5*G78</f>
+        <v>0.0</v>
+      </c>
+      <c r="I78" s="7">
+        <f>D78*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J78" s="7">
+        <f>G78-H78-E78-I78</f>
+        <v>0.0</v>
+      </c>
+      <c r="K78" s="7">
+        <f>J78*B78</f>
+        <v>0.0</v>
+      </c>
+      <c r="L78" s="7">
+        <f>IF(AND(A78&gt;=$B$8,A78&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M78" s="7">
+        <f>G78-H78-L78</f>
+        <v>0.0</v>
+      </c>
+      <c r="N78" s="7">
+        <f>SUM($M$41:M78)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O78" s="7">
+        <f>$B$17*MAX(0,N78)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P78" s="7">
+        <f>MAX(0,O78-O77)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q78" s="7">
+        <f>J78-P78</f>
+        <v>0.0</v>
+      </c>
+      <c r="R78" s="7">
+        <f>Q78*B78</f>
+        <v>0.0</v>
+      </c>
+      <c r="S78" s="7">
+        <f>SUM($Q$41:Q78)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U78" s="7" t="e">
+        <f>IF(J78&lt;0,-J78,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V78" s="7" t="e">
+        <f>IF(J78&gt;0,J78,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="79">
+      <c r="A79">
+        <v>38</v>
+      </c>
+      <c r="B79" s="6">
+        <f>1/(1+$B$6)^A79</f>
+        <v>0.053690480601462955</v>
+      </c>
+      <c r="C79">
+        <f>IF(A79&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D79">
+        <f>IF(AND(A79&gt;=$B$8,A79&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E79" s="7">
+        <f>C79*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F79" s="12">
+        <f>D79*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G79" s="7">
+        <f>F79*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H79" s="7">
+        <f>$B$5*G79</f>
+        <v>0.0</v>
+      </c>
+      <c r="I79" s="7">
+        <f>D79*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J79" s="7">
+        <f>G79-H79-E79-I79</f>
+        <v>0.0</v>
+      </c>
+      <c r="K79" s="7">
+        <f>J79*B79</f>
+        <v>0.0</v>
+      </c>
+      <c r="L79" s="7">
+        <f>IF(AND(A79&gt;=$B$8,A79&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M79" s="7">
+        <f>G79-H79-L79</f>
+        <v>0.0</v>
+      </c>
+      <c r="N79" s="7">
+        <f>SUM($M$41:M79)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O79" s="7">
+        <f>$B$17*MAX(0,N79)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P79" s="7">
+        <f>MAX(0,O79-O78)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q79" s="7">
+        <f>J79-P79</f>
+        <v>0.0</v>
+      </c>
+      <c r="R79" s="7">
+        <f>Q79*B79</f>
+        <v>0.0</v>
+      </c>
+      <c r="S79" s="7">
+        <f>SUM($Q$41:Q79)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U79" s="7" t="e">
+        <f>IF(J79&lt;0,-J79,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V79" s="7" t="e">
+        <f>IF(J79&gt;0,J79,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="80">
+      <c r="A80">
+        <v>39</v>
+      </c>
+      <c r="B80" s="6">
+        <f>1/(1+$B$6)^A80</f>
+        <v>0.04971340796431756</v>
+      </c>
+      <c r="C80">
+        <f>IF(A80&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D80">
+        <f>IF(AND(A80&gt;=$B$8,A80&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E80" s="7">
+        <f>C80*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F80" s="12">
+        <f>D80*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G80" s="7">
+        <f>F80*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H80" s="7">
+        <f>$B$5*G80</f>
+        <v>0.0</v>
+      </c>
+      <c r="I80" s="7">
+        <f>D80*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J80" s="7">
+        <f>G80-H80-E80-I80</f>
+        <v>0.0</v>
+      </c>
+      <c r="K80" s="7">
+        <f>J80*B80</f>
+        <v>0.0</v>
+      </c>
+      <c r="L80" s="7">
+        <f>IF(AND(A80&gt;=$B$8,A80&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M80" s="7">
+        <f>G80-H80-L80</f>
+        <v>0.0</v>
+      </c>
+      <c r="N80" s="7">
+        <f>SUM($M$41:M80)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O80" s="7">
+        <f>$B$17*MAX(0,N80)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P80" s="7">
+        <f>MAX(0,O80-O79)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q80" s="7">
+        <f>J80-P80</f>
+        <v>0.0</v>
+      </c>
+      <c r="R80" s="7">
+        <f>Q80*B80</f>
+        <v>0.0</v>
+      </c>
+      <c r="S80" s="7">
+        <f>SUM($Q$41:Q80)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U80" s="7" t="e">
+        <f>IF(J80&lt;0,-J80,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V80" s="7" t="e">
+        <f>IF(J80&gt;0,J80,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="81">
+      <c r="A81">
+        <v>40</v>
+      </c>
+      <c r="B81" s="6">
+        <f>1/(1+$B$6)^A81</f>
+        <v>0.04603093330029402</v>
+      </c>
+      <c r="C81">
+        <f>IF(A81&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D81">
+        <f>IF(AND(A81&gt;=$B$8,A81&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E81" s="7">
+        <f>C81*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F81" s="12">
+        <f>D81*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G81" s="7">
+        <f>F81*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H81" s="7">
+        <f>$B$5*G81</f>
+        <v>0.0</v>
+      </c>
+      <c r="I81" s="7">
+        <f>D81*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J81" s="7">
+        <f>G81-H81-E81-I81</f>
+        <v>0.0</v>
+      </c>
+      <c r="K81" s="7">
+        <f>J81*B81</f>
+        <v>0.0</v>
+      </c>
+      <c r="L81" s="7">
+        <f>IF(AND(A81&gt;=$B$8,A81&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M81" s="7">
+        <f>G81-H81-L81</f>
+        <v>0.0</v>
+      </c>
+      <c r="N81" s="7">
+        <f>SUM($M$41:M81)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O81" s="7">
+        <f>$B$17*MAX(0,N81)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P81" s="7">
+        <f>MAX(0,O81-O80)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q81" s="7">
+        <f>J81-P81</f>
+        <v>0.0</v>
+      </c>
+      <c r="R81" s="7">
+        <f>Q81*B81</f>
+        <v>0.0</v>
+      </c>
+      <c r="S81" s="7">
+        <f>SUM($Q$41:Q81)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U81" s="7" t="e">
+        <f>IF(J81&lt;0,-J81,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V81" s="7" t="e">
+        <f>IF(J81&gt;0,J81,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="82">
+      <c r="A82">
+        <v>41</v>
+      </c>
+      <c r="B82" s="6">
+        <f>1/(1+$B$6)^A82</f>
+        <v>0.04262123453730928</v>
+      </c>
+      <c r="C82">
+        <f>IF(A82&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D82">
+        <f>IF(AND(A82&gt;=$B$8,A82&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E82" s="7">
+        <f>C82*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F82" s="12">
+        <f>D82*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G82" s="7">
+        <f>F82*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H82" s="7">
+        <f>$B$5*G82</f>
+        <v>0.0</v>
+      </c>
+      <c r="I82" s="7">
+        <f>D82*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J82" s="7">
+        <f>G82-H82-E82-I82</f>
+        <v>0.0</v>
+      </c>
+      <c r="K82" s="7">
+        <f>J82*B82</f>
+        <v>0.0</v>
+      </c>
+      <c r="L82" s="7">
+        <f>IF(AND(A82&gt;=$B$8,A82&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M82" s="7">
+        <f>G82-H82-L82</f>
+        <v>0.0</v>
+      </c>
+      <c r="N82" s="7">
+        <f>SUM($M$41:M82)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O82" s="7">
+        <f>$B$17*MAX(0,N82)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P82" s="7">
+        <f>MAX(0,O82-O81)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q82" s="7">
+        <f>J82-P82</f>
+        <v>0.0</v>
+      </c>
+      <c r="R82" s="7">
+        <f>Q82*B82</f>
+        <v>0.0</v>
+      </c>
+      <c r="S82" s="7">
+        <f>SUM($Q$41:Q82)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U82" s="7" t="e">
+        <f>IF(J82&lt;0,-J82,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V82" s="7" t="e">
+        <f>IF(J82&gt;0,J82,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="83">
+      <c r="A83">
+        <v>42</v>
+      </c>
+      <c r="B83" s="6">
+        <f>1/(1+$B$6)^A83</f>
+        <v>0.03946410605306415</v>
+      </c>
+      <c r="C83">
+        <f>IF(A83&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D83">
+        <f>IF(AND(A83&gt;=$B$8,A83&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E83" s="7">
+        <f>C83*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F83" s="12">
+        <f>D83*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G83" s="7">
+        <f>F83*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H83" s="7">
+        <f>$B$5*G83</f>
+        <v>0.0</v>
+      </c>
+      <c r="I83" s="7">
+        <f>D83*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J83" s="7">
+        <f>G83-H83-E83-I83</f>
+        <v>0.0</v>
+      </c>
+      <c r="K83" s="7">
+        <f>J83*B83</f>
+        <v>0.0</v>
+      </c>
+      <c r="L83" s="7">
+        <f>IF(AND(A83&gt;=$B$8,A83&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M83" s="7">
+        <f>G83-H83-L83</f>
+        <v>0.0</v>
+      </c>
+      <c r="N83" s="7">
+        <f>SUM($M$41:M83)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O83" s="7">
+        <f>$B$17*MAX(0,N83)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P83" s="7">
+        <f>MAX(0,O83-O82)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q83" s="7">
+        <f>J83-P83</f>
+        <v>0.0</v>
+      </c>
+      <c r="R83" s="7">
+        <f>Q83*B83</f>
+        <v>0.0</v>
+      </c>
+      <c r="S83" s="7">
+        <f>SUM($Q$41:Q83)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U83" s="7" t="e">
+        <f>IF(J83&lt;0,-J83,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V83" s="7" t="e">
+        <f>IF(J83&gt;0,J83,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="84">
+      <c r="A84">
+        <v>43</v>
+      </c>
+      <c r="B84" s="6">
+        <f>1/(1+$B$6)^A84</f>
+        <v>0.03654083893802236</v>
+      </c>
+      <c r="C84">
+        <f>IF(A84&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D84">
+        <f>IF(AND(A84&gt;=$B$8,A84&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E84" s="7">
+        <f>C84*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F84" s="12">
+        <f>D84*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G84" s="7">
+        <f>F84*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H84" s="7">
+        <f>$B$5*G84</f>
+        <v>0.0</v>
+      </c>
+      <c r="I84" s="7">
+        <f>D84*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J84" s="7">
+        <f>G84-H84-E84-I84</f>
+        <v>0.0</v>
+      </c>
+      <c r="K84" s="7">
+        <f>J84*B84</f>
+        <v>0.0</v>
+      </c>
+      <c r="L84" s="7">
+        <f>IF(AND(A84&gt;=$B$8,A84&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M84" s="7">
+        <f>G84-H84-L84</f>
+        <v>0.0</v>
+      </c>
+      <c r="N84" s="7">
+        <f>SUM($M$41:M84)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O84" s="7">
+        <f>$B$17*MAX(0,N84)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P84" s="7">
+        <f>MAX(0,O84-O83)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q84" s="7">
+        <f>J84-P84</f>
+        <v>0.0</v>
+      </c>
+      <c r="R84" s="7">
+        <f>Q84*B84</f>
+        <v>0.0</v>
+      </c>
+      <c r="S84" s="7">
+        <f>SUM($Q$41:Q84)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U84" s="7" t="e">
+        <f>IF(J84&lt;0,-J84,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V84" s="7" t="e">
+        <f>IF(J84&gt;0,J84,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row spans="1:22" x14ac:dyDescent="0.3" r="85">
+      <c r="A85">
+        <v>44</v>
+      </c>
+      <c r="B85" s="6">
+        <f>1/(1+$B$6)^A85</f>
+        <v>0.033834110127798474</v>
+      </c>
+      <c r="C85">
+        <f>IF(A85&lt;$B$8,1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D85">
+        <f>IF(AND(A85&gt;=$B$8,A85&lt;$B$8+$B$7),1,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E85" s="7">
+        <f>C85*$B$9/$B$8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F85" s="12">
+        <f>D85*$B$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="G85" s="7">
+        <f>F85*($B$13+$B$19*Inputs!$D$148)/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="H85" s="7">
+        <f>$B$5*G85</f>
+        <v>0.0</v>
+      </c>
+      <c r="I85" s="7">
+        <f>D85*$B$16*$B$9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J85" s="7">
+        <f>G85-H85-E85-I85</f>
+        <v>0.0</v>
+      </c>
+      <c r="K85" s="7">
+        <f>J85*B85</f>
+        <v>0.0</v>
+      </c>
+      <c r="L85" s="7">
+        <f>IF(AND(A85&gt;=$B$8,A85&lt;$B$8+$B$18),$B$9/$B$18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M85" s="7">
+        <f>G85-H85-L85</f>
+        <v>0.0</v>
+      </c>
+      <c r="N85" s="7">
+        <f>SUM($M$41:M85)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="O85" s="7">
+        <f>$B$17*MAX(0,N85)</f>
+        <v>0.0</v>
+      </c>
+      <c r="P85" s="7">
+        <f>MAX(0,O85-O84)</f>
+        <v>0.0</v>
+      </c>
+      <c r="Q85" s="7">
+        <f>J85-P85</f>
+        <v>0.0</v>
+      </c>
+      <c r="R85" s="7">
+        <f>Q85*B85</f>
+        <v>0.0</v>
+      </c>
+      <c r="S85" s="7">
+        <f>SUM($Q$41:Q85)</f>
+        <v>-93.20815579710143</v>
+      </c>
+      <c r="U85" s="7" t="e">
+        <f>IF(J85&lt;0,-J85,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V85" s="7" t="e">
+        <f>IF(J85&gt;0,J85,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="28" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+    <row r="89" spans="1:14" ht="28" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B89" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G89" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="L67" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="M67" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="N89" s="1" t="s">
         <v>372</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>373</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68" s="6">
-        <f t="shared" ref="F68:F94" si="17">SUMPRODUCT($B$41:$B$63*($A$41:$A$63&gt;=$B$8+E68)*($A$41:$A$63&lt;$B$8+E68+$B$7))</f>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G68" s="7">
-        <f t="shared" ref="G68:G94" si="18">(D68-C68*$B$5)*$B$15*F68-B68*$B$28-I68*B68*$B$9*F68</f>
-        <v>-144.05101535660108</v>
-      </c>
-      <c r="H68" s="7">
-        <f t="shared" ref="H68:H94" si="19">(D68-C68*$B$5)*$C$15*F68-B68*($C$9/$B$9)*$B$28-I68*B68*$C$9*F68</f>
-        <v>-259.41977774562076</v>
-      </c>
-      <c r="I68" s="6">
-        <f t="shared" ref="I68:I93" si="20">$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="J68" s="7">
-        <f t="shared" ref="J68:J94" si="21">D68*$B$15-C68*$B$5*$B$15-B68*$B$9/$B$18</f>
-        <v>-4.6604077898550713</v>
-      </c>
-      <c r="K68" s="7">
-        <f t="shared" ref="K68:K94" si="22">IF($B$18&lt;$B$7,"n/a",G68-$B$17*MAX(0,J68)*F68)</f>
-        <v>-144.05101535660108</v>
-      </c>
-      <c r="L68" s="7">
-        <f t="shared" ref="L68:L94" si="23">D68*$C$15-C68*$B$5*$C$15-B68*$C$9/$C$18</f>
-        <v>-11.758386413043478</v>
-      </c>
-      <c r="M68" s="7">
-        <f t="shared" ref="M68:M94" si="24">IF($C$18&lt;$C$7,"n/a",H68-$B$17*MAX(0,L68)*F68)</f>
-        <v>-259.41977774562076</v>
-      </c>
-      <c r="N68" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>374</v>
-      </c>
-      <c r="B69">
-        <v>1.05</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G69" s="7">
-        <f t="shared" si="18"/>
-        <v>-153.68064498623073</v>
-      </c>
-      <c r="H69" s="7">
-        <f t="shared" si="19"/>
-        <v>-273.86422219006528</v>
-      </c>
-      <c r="I69" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="7">
-        <f t="shared" si="21"/>
-        <v>-5.1604077898550713</v>
-      </c>
-      <c r="K69" s="7">
-        <f t="shared" si="22"/>
-        <v>-153.68064498623073</v>
-      </c>
-      <c r="L69" s="7">
-        <f t="shared" si="23"/>
-        <v>-12.508386413043478</v>
-      </c>
-      <c r="M69" s="7">
-        <f t="shared" si="24"/>
-        <v>-273.86422219006528</v>
-      </c>
-      <c r="N69" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>375</v>
-      </c>
-      <c r="B70">
-        <v>0.95</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G70" s="7">
-        <f t="shared" si="18"/>
-        <v>-134.42138572697144</v>
-      </c>
-      <c r="H70" s="7">
-        <f t="shared" si="19"/>
-        <v>-244.97533330117631</v>
-      </c>
-      <c r="I70" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="7">
-        <f t="shared" si="21"/>
-        <v>-4.1604077898550713</v>
-      </c>
-      <c r="K70" s="7">
-        <f t="shared" si="22"/>
-        <v>-134.42138572697144</v>
-      </c>
-      <c r="L70" s="7">
-        <f t="shared" si="23"/>
-        <v>-11.008386413043478</v>
-      </c>
-      <c r="M70" s="7">
-        <f t="shared" si="24"/>
-        <v>-244.97533330117631</v>
-      </c>
-      <c r="N70" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>376</v>
-      </c>
-      <c r="B71">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G71" s="7">
-        <f t="shared" si="18"/>
-        <v>-163.31027461586035</v>
-      </c>
-      <c r="H71" s="7">
-        <f t="shared" si="19"/>
-        <v>-288.30866663450968</v>
-      </c>
-      <c r="I71" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="7">
-        <f t="shared" si="21"/>
-        <v>-5.6604077898550731</v>
-      </c>
-      <c r="K71" s="7">
-        <f t="shared" si="22"/>
-        <v>-163.31027461586035</v>
-      </c>
-      <c r="L71" s="7">
-        <f t="shared" si="23"/>
-        <v>-13.258386413043478</v>
-      </c>
-      <c r="M71" s="7">
-        <f t="shared" si="24"/>
-        <v>-288.30866663450968</v>
-      </c>
-      <c r="N71" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>377</v>
-      </c>
-      <c r="B72">
-        <v>0.9</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G72" s="7">
-        <f t="shared" si="18"/>
-        <v>-124.79175609734182</v>
-      </c>
-      <c r="H72" s="7">
-        <f t="shared" si="19"/>
-        <v>-230.53088885673191</v>
-      </c>
-      <c r="I72" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="7">
-        <f t="shared" si="21"/>
-        <v>-3.6604077898550713</v>
-      </c>
-      <c r="K72" s="7">
-        <f t="shared" si="22"/>
-        <v>-124.79175609734182</v>
-      </c>
-      <c r="L72" s="7">
-        <f t="shared" si="23"/>
-        <v>-10.258386413043478</v>
-      </c>
-      <c r="M72" s="7">
-        <f t="shared" si="24"/>
-        <v>-230.53088885673191</v>
-      </c>
-      <c r="N72" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>378</v>
-      </c>
-      <c r="B73">
-        <v>1.2</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G73" s="7">
-        <f t="shared" si="18"/>
-        <v>-182.56953387511959</v>
-      </c>
-      <c r="H73" s="7">
-        <f t="shared" si="19"/>
-        <v>-317.19755552339853</v>
-      </c>
-      <c r="I73" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="7">
-        <f t="shared" si="21"/>
-        <v>-6.6604077898550713</v>
-      </c>
-      <c r="K73" s="7">
-        <f t="shared" si="22"/>
-        <v>-182.56953387511959</v>
-      </c>
-      <c r="L73" s="7">
-        <f t="shared" si="23"/>
-        <v>-14.758386413043478</v>
-      </c>
-      <c r="M73" s="7">
-        <f t="shared" si="24"/>
-        <v>-317.19755552339853</v>
-      </c>
-      <c r="N73" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>379</v>
-      </c>
-      <c r="B74">
-        <v>0.8</v>
-      </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G74" s="7">
-        <f t="shared" si="18"/>
-        <v>-105.53249683808258</v>
-      </c>
-      <c r="H74" s="7">
-        <f t="shared" si="19"/>
-        <v>-201.64199996784305</v>
-      </c>
-      <c r="I74" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="7">
-        <f t="shared" si="21"/>
-        <v>-2.6604077898550713</v>
-      </c>
-      <c r="K74" s="7">
-        <f t="shared" si="22"/>
-        <v>-105.53249683808258</v>
-      </c>
-      <c r="L74" s="7">
-        <f t="shared" si="23"/>
-        <v>-8.7583864130434783</v>
-      </c>
-      <c r="M74" s="7">
-        <f t="shared" si="24"/>
-        <v>-201.64199996784305</v>
-      </c>
-      <c r="N74" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>380</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75">
-        <v>1.05</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G75" s="7">
-        <f t="shared" si="18"/>
-        <v>-152.2327970400431</v>
-      </c>
-      <c r="H75" s="7">
-        <f t="shared" si="19"/>
-        <v>-264.38685643379603</v>
-      </c>
-      <c r="I75" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="7">
-        <f t="shared" si="21"/>
-        <v>-5.5604069293478275</v>
-      </c>
-      <c r="K75" s="7">
-        <f t="shared" si="22"/>
-        <v>-152.2327970400431</v>
-      </c>
-      <c r="L75" s="7">
-        <f t="shared" si="23"/>
-        <v>-12.304766983695652</v>
-      </c>
-      <c r="M75" s="7">
-        <f t="shared" si="24"/>
-        <v>-264.38685643379603</v>
-      </c>
-      <c r="N75" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>381</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76">
-        <v>0.95</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G76" s="7">
-        <f t="shared" si="18"/>
-        <v>-135.86923367315907</v>
-      </c>
-      <c r="H76" s="7">
-        <f t="shared" si="19"/>
-        <v>-254.45269905744547</v>
-      </c>
-      <c r="I76" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J76" s="7">
-        <f t="shared" si="21"/>
-        <v>-3.7604086503623186</v>
-      </c>
-      <c r="K76" s="7">
-        <f t="shared" si="22"/>
-        <v>-135.86923367315907</v>
-      </c>
-      <c r="L76" s="7">
-        <f t="shared" si="23"/>
-        <v>-11.212005842391305</v>
-      </c>
-      <c r="M76" s="7">
-        <f t="shared" si="24"/>
-        <v>-254.45269905744547</v>
-      </c>
-      <c r="N76" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>382</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G77" s="7">
-        <f t="shared" si="18"/>
-        <v>-160.41457872348511</v>
-      </c>
-      <c r="H77" s="7">
-        <f t="shared" si="19"/>
-        <v>-269.35393512197129</v>
-      </c>
-      <c r="I77" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="7">
-        <f t="shared" si="21"/>
-        <v>-6.4604060688405802</v>
-      </c>
-      <c r="K77" s="7">
-        <f t="shared" si="22"/>
-        <v>-160.41457872348511</v>
-      </c>
-      <c r="L77" s="7">
-        <f t="shared" si="23"/>
-        <v>-12.851147554347827</v>
-      </c>
-      <c r="M77" s="7">
-        <f t="shared" si="24"/>
-        <v>-269.35393512197129</v>
-      </c>
-      <c r="N77" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>383</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78">
-        <v>0.9</v>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G78" s="7">
-        <f t="shared" si="18"/>
-        <v>-127.68745198971706</v>
-      </c>
-      <c r="H78" s="7">
-        <f t="shared" si="19"/>
-        <v>-249.48562036927018</v>
-      </c>
-      <c r="I78" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J78" s="7">
-        <f t="shared" si="21"/>
-        <v>-2.860409510869566</v>
-      </c>
-      <c r="K78" s="7">
-        <f t="shared" si="22"/>
-        <v>-127.68745198971706</v>
-      </c>
-      <c r="L78" s="7">
-        <f t="shared" si="23"/>
-        <v>-10.665625271739129</v>
-      </c>
-      <c r="M78" s="7">
-        <f t="shared" si="24"/>
-        <v>-249.48562036927018</v>
-      </c>
-      <c r="N78" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>384</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79">
-        <v>1.2</v>
-      </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G79" s="7">
-        <f t="shared" si="18"/>
-        <v>-176.7781420903691</v>
-      </c>
-      <c r="H79" s="7">
-        <f t="shared" si="19"/>
-        <v>-279.28809249832187</v>
-      </c>
-      <c r="I79" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="7">
-        <f t="shared" si="21"/>
-        <v>-8.2604043478260856</v>
-      </c>
-      <c r="K79" s="7">
-        <f t="shared" si="22"/>
-        <v>-176.7781420903691</v>
-      </c>
-      <c r="L79" s="7">
-        <f t="shared" si="23"/>
-        <v>-13.943908695652173</v>
-      </c>
-      <c r="M79" s="7">
-        <f t="shared" si="24"/>
-        <v>-279.28809249832187</v>
-      </c>
-      <c r="N79" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>385</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80">
-        <v>0.8</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G80" s="7">
-        <f t="shared" si="18"/>
-        <v>-111.32388862283307</v>
-      </c>
-      <c r="H80" s="7">
-        <f t="shared" si="19"/>
-        <v>-239.55146299291965</v>
-      </c>
-      <c r="I80" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="7">
-        <f t="shared" si="21"/>
-        <v>-1.0604112318840588</v>
-      </c>
-      <c r="K80" s="7">
-        <f t="shared" si="22"/>
-        <v>-111.32388862283307</v>
-      </c>
-      <c r="L80" s="7">
-        <f t="shared" si="23"/>
-        <v>-9.5728641304347821</v>
-      </c>
-      <c r="M80" s="7">
-        <f t="shared" si="24"/>
-        <v>-239.55146299291965</v>
-      </c>
-      <c r="N80" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>386</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>1.05</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G81" s="7">
-        <f t="shared" si="18"/>
-        <v>-133.4421548113595</v>
-      </c>
-      <c r="H81" s="7">
-        <f t="shared" si="19"/>
-        <v>-252.97924350028205</v>
-      </c>
-      <c r="I81" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="7">
-        <f t="shared" si="21"/>
-        <v>-3.4934290398550694</v>
-      </c>
-      <c r="K81" s="7">
-        <f t="shared" si="22"/>
-        <v>-133.4421548113595</v>
-      </c>
-      <c r="L81" s="7">
-        <f t="shared" si="23"/>
-        <v>-11.049925163043477</v>
-      </c>
-      <c r="M81" s="7">
-        <f t="shared" si="24"/>
-        <v>-252.97924350028205</v>
-      </c>
-      <c r="N81" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>387</v>
-      </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82">
-        <v>0.95</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G82" s="7">
-        <f t="shared" si="18"/>
-        <v>-154.65987590184267</v>
-      </c>
-      <c r="H82" s="7">
-        <f t="shared" si="19"/>
-        <v>-265.86031199095942</v>
-      </c>
-      <c r="I82" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J82" s="7">
-        <f t="shared" si="21"/>
-        <v>-5.8273865398550733</v>
-      </c>
-      <c r="K82" s="7">
-        <f t="shared" si="22"/>
-        <v>-154.65987590184267</v>
-      </c>
-      <c r="L82" s="7">
-        <f t="shared" si="23"/>
-        <v>-12.466847663043479</v>
-      </c>
-      <c r="M82" s="7">
-        <f t="shared" si="24"/>
-        <v>-265.86031199095942</v>
-      </c>
-      <c r="N82" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>388</v>
-      </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
-      <c r="D83">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G83" s="7">
-        <f t="shared" si="18"/>
-        <v>-122.83329426611789</v>
-      </c>
-      <c r="H83" s="7">
-        <f t="shared" si="19"/>
-        <v>-246.53870925494337</v>
-      </c>
-      <c r="I83" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="7">
-        <f t="shared" si="21"/>
-        <v>-2.3264502898550674</v>
-      </c>
-      <c r="K83" s="7">
-        <f t="shared" si="22"/>
-        <v>-122.83329426611789</v>
-      </c>
-      <c r="L83" s="7">
-        <f t="shared" si="23"/>
-        <v>-10.341463913043476</v>
-      </c>
-      <c r="M83" s="7">
-        <f t="shared" si="24"/>
-        <v>-246.53870925494337</v>
-      </c>
-      <c r="N83" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>389</v>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84">
-        <v>0.9</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G84" s="7">
-        <f t="shared" si="18"/>
-        <v>-165.26873644708425</v>
-      </c>
-      <c r="H84" s="7">
-        <f t="shared" si="19"/>
-        <v>-272.30084623629813</v>
-      </c>
-      <c r="I84" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J84" s="7">
-        <f t="shared" si="21"/>
-        <v>-6.9943652898550717</v>
-      </c>
-      <c r="K84" s="7">
-        <f t="shared" si="22"/>
-        <v>-165.26873644708425</v>
-      </c>
-      <c r="L84" s="7">
-        <f t="shared" si="23"/>
-        <v>-13.175308913043478</v>
-      </c>
-      <c r="M84" s="7">
-        <f t="shared" si="24"/>
-        <v>-272.30084623629813</v>
-      </c>
-      <c r="N84" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>390</v>
-      </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85">
-        <v>1.2</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G85" s="7">
-        <f t="shared" si="18"/>
-        <v>-101.61557317563475</v>
-      </c>
-      <c r="H85" s="7">
-        <f t="shared" si="19"/>
-        <v>-233.65764076426601</v>
-      </c>
-      <c r="I85" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="7">
-        <f t="shared" si="21"/>
-        <v>7.5072101449293882E-3</v>
-      </c>
-      <c r="K85" s="7">
-        <f t="shared" si="22"/>
-        <v>-101.6292226007869</v>
-      </c>
-      <c r="L85" s="7">
-        <f t="shared" si="23"/>
-        <v>-8.9245414130434799</v>
-      </c>
-      <c r="M85" s="7">
-        <f t="shared" si="24"/>
-        <v>-233.65764076426601</v>
-      </c>
-      <c r="N85" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>391</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86">
-        <v>0.8</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G86" s="7">
-        <f t="shared" si="18"/>
-        <v>-186.48645753756739</v>
-      </c>
-      <c r="H86" s="7">
-        <f t="shared" si="19"/>
-        <v>-285.18191472697549</v>
-      </c>
-      <c r="I86" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J86" s="7">
-        <f t="shared" si="21"/>
-        <v>-9.328322789855072</v>
-      </c>
-      <c r="K86" s="7">
-        <f t="shared" si="22"/>
-        <v>-186.48645753756739</v>
-      </c>
-      <c r="L86" s="7">
-        <f t="shared" si="23"/>
-        <v>-14.592231413043478</v>
-      </c>
-      <c r="M86" s="7">
-        <f t="shared" si="24"/>
-        <v>-285.18191472697549</v>
-      </c>
-      <c r="N86" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>392</v>
-      </c>
-      <c r="B87">
-        <v>1.05</v>
-      </c>
-      <c r="C87">
-        <v>1</v>
-      </c>
-      <c r="D87">
-        <v>0.95</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G87" s="7">
-        <f t="shared" si="18"/>
-        <v>-164.28950553147232</v>
-      </c>
-      <c r="H87" s="7">
-        <f t="shared" si="19"/>
-        <v>-280.30475643540393</v>
-      </c>
-      <c r="I87" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="7">
-        <f t="shared" si="21"/>
-        <v>-6.3273865398550733</v>
-      </c>
-      <c r="K87" s="7">
-        <f t="shared" si="22"/>
-        <v>-164.28950553147232</v>
-      </c>
-      <c r="L87" s="7">
-        <f t="shared" si="23"/>
-        <v>-13.216847663043479</v>
-      </c>
-      <c r="M87" s="7">
-        <f t="shared" si="24"/>
-        <v>-280.30475643540393</v>
-      </c>
-      <c r="N87" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>393</v>
-      </c>
-      <c r="B88">
-        <v>0.95</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>1.05</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-      <c r="F88" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G88" s="7">
-        <f t="shared" si="18"/>
-        <v>-123.81252518172984</v>
-      </c>
-      <c r="H88" s="7">
-        <f t="shared" si="19"/>
-        <v>-238.5347990558376</v>
-      </c>
-      <c r="I88" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J88" s="7">
-        <f t="shared" si="21"/>
-        <v>-2.9934290398550694</v>
-      </c>
-      <c r="K88" s="7">
-        <f t="shared" si="22"/>
-        <v>-123.81252518172984</v>
-      </c>
-      <c r="L88" s="7">
-        <f t="shared" si="23"/>
-        <v>-10.299925163043477</v>
-      </c>
-      <c r="M88" s="7">
-        <f t="shared" si="24"/>
-        <v>-238.5347990558376</v>
-      </c>
-      <c r="N88" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>394</v>
-      </c>
-      <c r="B89">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>0.9</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
-      </c>
-      <c r="G89" s="7">
-        <f t="shared" si="18"/>
-        <v>-184.52799570634352</v>
-      </c>
-      <c r="H89" s="7">
-        <f t="shared" si="19"/>
-        <v>-301.18973512518704</v>
-      </c>
-      <c r="I89" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="7">
-        <f t="shared" si="21"/>
-        <v>-7.9943652898550734</v>
-      </c>
-      <c r="K89" s="7">
-        <f t="shared" si="22"/>
-        <v>-184.52799570634352</v>
-      </c>
-      <c r="L89" s="7">
-        <f t="shared" si="23"/>
-        <v>-14.675308913043478</v>
-      </c>
-      <c r="M89" s="7">
-        <f t="shared" si="24"/>
-        <v>-301.18973512518704</v>
-      </c>
-      <c r="N89" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="B90">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E90)*($A$41:$A$85&lt;$B$8+E90+$B$7))</f>
+        <v>9.090877229119709</v>
       </c>
       <c r="G90" s="7">
-        <f t="shared" si="18"/>
-        <v>-103.57403500685862</v>
+        <f>(D90-C90*$B$5)*$B$15*F90-B90*$B$28-I90*B90*$B$9*F90</f>
+        <v>-144.05101535660108</v>
       </c>
       <c r="H90" s="7">
-        <f t="shared" si="19"/>
-        <v>-217.64982036605451</v>
+        <f>(D90-C90*$B$5)*$C$15*F90-B90*($C$9/$B$9)*$B$28-I90*B90*$C$9*F90</f>
+        <v>-259.41977774562076</v>
       </c>
       <c r="I90" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>$B$16</f>
+        <v>0.0</v>
       </c>
       <c r="J90" s="7">
-        <f t="shared" si="21"/>
-        <v>-1.3264502898550674</v>
+        <f>D90*$B$15-C90*$B$5*$B$15-B90*$B$9/$B$18</f>
+        <v>-4.660407789855071</v>
       </c>
       <c r="K90" s="7">
-        <f t="shared" si="22"/>
-        <v>-103.57403500685862</v>
+        <f>IF($B$18&lt;$B$7,"n/a",G90-$B$17*MAX(0,J90)*F90)</f>
+        <v>-144.05101535660108</v>
       </c>
       <c r="L90" s="7">
-        <f t="shared" si="23"/>
-        <v>-8.8414639130434765</v>
+        <f>D90*$C$15-C90*$B$5*$C$15-B90*$C$9/$C$18</f>
+        <v>-11.758386413043478</v>
       </c>
       <c r="M90" s="7">
-        <f t="shared" si="24"/>
-        <v>-217.64982036605451</v>
+        <f>IF($C$18&lt;$C$7,"n/a",H90-$B$17*MAX(0,L90)*F90)</f>
+        <v>-259.41977774562076</v>
       </c>
       <c r="N90" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="B91">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E91)*($A$41:$A$85&lt;$B$8+E91+$B$7))</f>
+        <v>9.090877229119709</v>
       </c>
       <c r="G91" s="7">
-        <f t="shared" si="18"/>
-        <v>-225.00497605608589</v>
+        <f>(D91-C91*$B$5)*$B$15*F91-B91*$B$28-I91*B91*$B$9*F91</f>
+        <v>-153.68064498623073</v>
       </c>
       <c r="H91" s="7">
-        <f t="shared" si="19"/>
-        <v>-342.95969250475326</v>
+        <f>(D91-C91*$B$5)*$C$15*F91-B91*($C$9/$B$9)*$B$28-I91*B91*$C$9*F91</f>
+        <v>-273.8642221900653</v>
       </c>
       <c r="I91" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>$B$16</f>
+        <v>0.0</v>
       </c>
       <c r="J91" s="7">
-        <f t="shared" si="21"/>
-        <v>-11.328322789855072</v>
+        <f>D91*$B$15-C91*$B$5*$B$15-B91*$B$9/$B$18</f>
+        <v>-5.160407789855071</v>
       </c>
       <c r="K91" s="7">
-        <f t="shared" si="22"/>
-        <v>-225.00497605608589</v>
+        <f>IF($B$18&lt;$B$7,"n/a",G91-$B$17*MAX(0,J91)*F91)</f>
+        <v>-153.68064498623073</v>
       </c>
       <c r="L91" s="7">
-        <f t="shared" si="23"/>
-        <v>-17.592231413043478</v>
+        <f>D91*$C$15-C91*$B$5*$C$15-B91*$C$9/$C$18</f>
+        <v>-12.508386413043478</v>
       </c>
       <c r="M91" s="7">
-        <f t="shared" si="24"/>
-        <v>-342.95969250475326</v>
+        <f>IF($C$18&lt;$C$7,"n/a",H91-$B$17*MAX(0,L91)*F91)</f>
+        <v>-273.8642221900653</v>
       </c>
       <c r="N91" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="B92">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E92)*($A$41:$A$85&lt;$B$8+E92+$B$7))</f>
+        <v>9.090877229119709</v>
       </c>
       <c r="G92" s="7">
-        <f t="shared" si="18"/>
-        <v>-63.097054657116246</v>
+        <f>(D92-C92*$B$5)*$B$15*F92-B92*$B$28-I92*B92*$B$9*F92</f>
+        <v>-134.42138572697144</v>
       </c>
       <c r="H92" s="7">
-        <f t="shared" si="19"/>
-        <v>-175.87986298648829</v>
+        <f>(D92-C92*$B$5)*$C$15*F92-B92*($C$9/$B$9)*$B$28-I92*B92*$C$9*F92</f>
+        <v>-244.9753333011763</v>
       </c>
       <c r="I92" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>$B$16</f>
+        <v>0.0</v>
       </c>
       <c r="J92" s="7">
-        <f t="shared" si="21"/>
-        <v>2.0075072101449294</v>
+        <f>D92*$B$15-C92*$B$5*$B$15-B92*$B$9/$B$18</f>
+        <v>-4.160407789855071</v>
       </c>
       <c r="K92" s="7">
-        <f t="shared" si="22"/>
-        <v>-66.747054973916278</v>
+        <f>IF($B$18&lt;$B$7,"n/a",G92-$B$17*MAX(0,J92)*F92)</f>
+        <v>-134.42138572697144</v>
       </c>
       <c r="L92" s="7">
-        <f t="shared" si="23"/>
-        <v>-5.9245414130434799</v>
+        <f>D92*$C$15-C92*$B$5*$C$15-B92*$C$9/$C$18</f>
+        <v>-11.008386413043478</v>
       </c>
       <c r="M92" s="7">
-        <f t="shared" si="24"/>
-        <v>-175.87986298648829</v>
+        <f>IF($C$18&lt;$C$7,"n/a",H92-$B$17*MAX(0,L92)*F92)</f>
+        <v>-244.9753333011763</v>
       </c>
       <c r="N92" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -12996,50 +13925,50 @@
         <v>1</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" s="6">
-        <f t="shared" si="17"/>
-        <v>8.4174789158515821</v>
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E93)*($A$41:$A$85&lt;$B$8+E93+$B$7))</f>
+        <v>9.090877229119709</v>
       </c>
       <c r="G93" s="7">
-        <f t="shared" si="18"/>
-        <v>-147.64668774445229</v>
+        <f>(D93-C93*$B$5)*$B$15*F93-B93*$B$28-I93*B93*$B$9*F93</f>
+        <v>-163.31027461586035</v>
       </c>
       <c r="H93" s="7">
-        <f t="shared" si="19"/>
-        <v>-261.60267486734432</v>
+        <f>(D93-C93*$B$5)*$C$15*F93-B93*($C$9/$B$9)*$B$28-I93*B93*$C$9*F93</f>
+        <v>-288.3086666345097</v>
       </c>
       <c r="I93" s="6">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>$B$16</f>
+        <v>0.0</v>
       </c>
       <c r="J93" s="7">
-        <f t="shared" si="21"/>
-        <v>-4.6604077898550713</v>
+        <f>D93*$B$15-C93*$B$5*$B$15-B93*$B$9/$B$18</f>
+        <v>-5.660407789855073</v>
       </c>
       <c r="K93" s="7">
-        <f t="shared" si="22"/>
-        <v>-147.64668774445229</v>
+        <f>IF($B$18&lt;$B$7,"n/a",G93-$B$17*MAX(0,J93)*F93)</f>
+        <v>-163.31027461586035</v>
       </c>
       <c r="L93" s="7">
-        <f t="shared" si="23"/>
-        <v>-11.758386413043478</v>
+        <f>D93*$C$15-C93*$B$5*$C$15-B93*$C$9/$C$18</f>
+        <v>-13.258386413043478</v>
       </c>
       <c r="M93" s="7">
-        <f t="shared" si="24"/>
-        <v>-261.60267486734432</v>
+        <f>IF($C$18&lt;$C$7,"n/a",H93-$B$17*MAX(0,L93)*F93)</f>
+        <v>-288.3086666345097</v>
       </c>
       <c r="N93" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -13051,663 +13980,1807 @@
         <v>0</v>
       </c>
       <c r="F94" s="6">
-        <f t="shared" si="17"/>
-        <v>9.0908772291197089</v>
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E94)*($A$41:$A$85&lt;$B$8+E94+$B$7))</f>
+        <v>9.090877229119709</v>
       </c>
       <c r="G94" s="7">
-        <f t="shared" si="18"/>
-        <v>-287.85647706968189</v>
+        <f>(D94-C94*$B$5)*$B$15*F94-B94*$B$28-I94*B94*$B$9*F94</f>
+        <v>-124.79175609734182</v>
       </c>
       <c r="H94" s="7">
-        <f t="shared" si="19"/>
-        <v>-475.12797031524201</v>
+        <f>(D94-C94*$B$5)*$C$15*F94-B94*($C$9/$B$9)*$B$28-I94*B94*$C$9*F94</f>
+        <v>-230.5308888567319</v>
       </c>
       <c r="I94" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J94" s="7">
+        <f>D94*$B$15-C94*$B$5*$B$15-B94*$B$9/$B$18</f>
+        <v>-3.6604077898550713</v>
+      </c>
+      <c r="K94" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G94-$B$17*MAX(0,J94)*F94)</f>
+        <v>-124.79175609734182</v>
+      </c>
+      <c r="L94" s="7">
+        <f>D94*$C$15-C94*$B$5*$C$15-B94*$C$9/$C$18</f>
+        <v>-10.258386413043478</v>
+      </c>
+      <c r="M94" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H94-$B$17*MAX(0,L94)*F94)</f>
+        <v>-230.5308888567319</v>
+      </c>
+      <c r="N94" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>378</v>
+      </c>
+      <c r="B95">
+        <v>1.2</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E95)*($A$41:$A$85&lt;$B$8+E95+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G95" s="7">
+        <f>(D95-C95*$B$5)*$B$15*F95-B95*$B$28-I95*B95*$B$9*F95</f>
+        <v>-182.5695338751196</v>
+      </c>
+      <c r="H95" s="7">
+        <f>(D95-C95*$B$5)*$C$15*F95-B95*($C$9/$B$9)*$B$28-I95*B95*$C$9*F95</f>
+        <v>-317.19755552339853</v>
+      </c>
+      <c r="I95" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J95" s="7">
+        <f>D95*$B$15-C95*$B$5*$B$15-B95*$B$9/$B$18</f>
+        <v>-6.660407789855071</v>
+      </c>
+      <c r="K95" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G95-$B$17*MAX(0,J95)*F95)</f>
+        <v>-182.5695338751196</v>
+      </c>
+      <c r="L95" s="7">
+        <f>D95*$C$15-C95*$B$5*$C$15-B95*$C$9/$C$18</f>
+        <v>-14.758386413043478</v>
+      </c>
+      <c r="M95" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H95-$B$17*MAX(0,L95)*F95)</f>
+        <v>-317.19755552339853</v>
+      </c>
+      <c r="N95" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>379</v>
+      </c>
+      <c r="B96">
+        <v>0.8</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E96)*($A$41:$A$85&lt;$B$8+E96+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G96" s="7">
+        <f>(D96-C96*$B$5)*$B$15*F96-B96*$B$28-I96*B96*$B$9*F96</f>
+        <v>-105.53249683808258</v>
+      </c>
+      <c r="H96" s="7">
+        <f>(D96-C96*$B$5)*$C$15*F96-B96*($C$9/$B$9)*$B$28-I96*B96*$C$9*F96</f>
+        <v>-201.64199996784305</v>
+      </c>
+      <c r="I96" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J96" s="7">
+        <f>D96*$B$15-C96*$B$5*$B$15-B96*$B$9/$B$18</f>
+        <v>-2.6604077898550713</v>
+      </c>
+      <c r="K96" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G96-$B$17*MAX(0,J96)*F96)</f>
+        <v>-105.53249683808258</v>
+      </c>
+      <c r="L96" s="7">
+        <f>D96*$C$15-C96*$B$5*$C$15-B96*$C$9/$C$18</f>
+        <v>-8.758386413043478</v>
+      </c>
+      <c r="M96" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H96-$B$17*MAX(0,L96)*F96)</f>
+        <v>-201.64199996784305</v>
+      </c>
+      <c r="N96" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>1.05</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E97)*($A$41:$A$85&lt;$B$8+E97+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G97" s="7">
+        <f>(D97-C97*$B$5)*$B$15*F97-B97*$B$28-I97*B97*$B$9*F97</f>
+        <v>-152.2327970400431</v>
+      </c>
+      <c r="H97" s="7">
+        <f>(D97-C97*$B$5)*$C$15*F97-B97*($C$9/$B$9)*$B$28-I97*B97*$C$9*F97</f>
+        <v>-264.386856433796</v>
+      </c>
+      <c r="I97" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J97" s="7">
+        <f>D97*$B$15-C97*$B$5*$B$15-B97*$B$9/$B$18</f>
+        <v>-5.5604069293478275</v>
+      </c>
+      <c r="K97" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G97-$B$17*MAX(0,J97)*F97)</f>
+        <v>-152.2327970400431</v>
+      </c>
+      <c r="L97" s="7">
+        <f>D97*$C$15-C97*$B$5*$C$15-B97*$C$9/$C$18</f>
+        <v>-12.304766983695652</v>
+      </c>
+      <c r="M97" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H97-$B$17*MAX(0,L97)*F97)</f>
+        <v>-264.386856433796</v>
+      </c>
+      <c r="N97" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>381</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>0.95</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E98)*($A$41:$A$85&lt;$B$8+E98+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G98" s="7">
+        <f>(D98-C98*$B$5)*$B$15*F98-B98*$B$28-I98*B98*$B$9*F98</f>
+        <v>-135.86923367315907</v>
+      </c>
+      <c r="H98" s="7">
+        <f>(D98-C98*$B$5)*$C$15*F98-B98*($C$9/$B$9)*$B$28-I98*B98*$C$9*F98</f>
+        <v>-254.45269905744547</v>
+      </c>
+      <c r="I98" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J98" s="7">
+        <f>D98*$B$15-C98*$B$5*$B$15-B98*$B$9/$B$18</f>
+        <v>-3.7604086503623186</v>
+      </c>
+      <c r="K98" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G98-$B$17*MAX(0,J98)*F98)</f>
+        <v>-135.86923367315907</v>
+      </c>
+      <c r="L98" s="7">
+        <f>D98*$C$15-C98*$B$5*$C$15-B98*$C$9/$C$18</f>
+        <v>-11.212005842391305</v>
+      </c>
+      <c r="M98" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H98-$B$17*MAX(0,L98)*F98)</f>
+        <v>-254.45269905744547</v>
+      </c>
+      <c r="N98" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>382</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E99)*($A$41:$A$85&lt;$B$8+E99+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G99" s="7">
+        <f>(D99-C99*$B$5)*$B$15*F99-B99*$B$28-I99*B99*$B$9*F99</f>
+        <v>-160.4145787234851</v>
+      </c>
+      <c r="H99" s="7">
+        <f>(D99-C99*$B$5)*$C$15*F99-B99*($C$9/$B$9)*$B$28-I99*B99*$C$9*F99</f>
+        <v>-269.3539351219713</v>
+      </c>
+      <c r="I99" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J99" s="7">
+        <f>D99*$B$15-C99*$B$5*$B$15-B99*$B$9/$B$18</f>
+        <v>-6.46040606884058</v>
+      </c>
+      <c r="K99" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G99-$B$17*MAX(0,J99)*F99)</f>
+        <v>-160.4145787234851</v>
+      </c>
+      <c r="L99" s="7">
+        <f>D99*$C$15-C99*$B$5*$C$15-B99*$C$9/$C$18</f>
+        <v>-12.851147554347827</v>
+      </c>
+      <c r="M99" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H99-$B$17*MAX(0,L99)*F99)</f>
+        <v>-269.3539351219713</v>
+      </c>
+      <c r="N99" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>383</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>0.9</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E100)*($A$41:$A$85&lt;$B$8+E100+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G100" s="7">
+        <f>(D100-C100*$B$5)*$B$15*F100-B100*$B$28-I100*B100*$B$9*F100</f>
+        <v>-127.68745198971706</v>
+      </c>
+      <c r="H100" s="7">
+        <f>(D100-C100*$B$5)*$C$15*F100-B100*($C$9/$B$9)*$B$28-I100*B100*$C$9*F100</f>
+        <v>-249.48562036927018</v>
+      </c>
+      <c r="I100" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J100" s="7">
+        <f>D100*$B$15-C100*$B$5*$B$15-B100*$B$9/$B$18</f>
+        <v>-2.860409510869566</v>
+      </c>
+      <c r="K100" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G100-$B$17*MAX(0,J100)*F100)</f>
+        <v>-127.68745198971706</v>
+      </c>
+      <c r="L100" s="7">
+        <f>D100*$C$15-C100*$B$5*$C$15-B100*$C$9/$C$18</f>
+        <v>-10.66562527173913</v>
+      </c>
+      <c r="M100" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H100-$B$17*MAX(0,L100)*F100)</f>
+        <v>-249.48562036927018</v>
+      </c>
+      <c r="N100" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>384</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>1.2</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E101)*($A$41:$A$85&lt;$B$8+E101+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G101" s="7">
+        <f>(D101-C101*$B$5)*$B$15*F101-B101*$B$28-I101*B101*$B$9*F101</f>
+        <v>-176.7781420903691</v>
+      </c>
+      <c r="H101" s="7">
+        <f>(D101-C101*$B$5)*$C$15*F101-B101*($C$9/$B$9)*$B$28-I101*B101*$C$9*F101</f>
+        <v>-279.2880924983219</v>
+      </c>
+      <c r="I101" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J101" s="7">
+        <f>D101*$B$15-C101*$B$5*$B$15-B101*$B$9/$B$18</f>
+        <v>-8.260404347826086</v>
+      </c>
+      <c r="K101" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G101-$B$17*MAX(0,J101)*F101)</f>
+        <v>-176.7781420903691</v>
+      </c>
+      <c r="L101" s="7">
+        <f>D101*$C$15-C101*$B$5*$C$15-B101*$C$9/$C$18</f>
+        <v>-13.943908695652173</v>
+      </c>
+      <c r="M101" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H101-$B$17*MAX(0,L101)*F101)</f>
+        <v>-279.2880924983219</v>
+      </c>
+      <c r="N101" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>385</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>0.8</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E102)*($A$41:$A$85&lt;$B$8+E102+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G102" s="7">
+        <f>(D102-C102*$B$5)*$B$15*F102-B102*$B$28-I102*B102*$B$9*F102</f>
+        <v>-111.32388862283307</v>
+      </c>
+      <c r="H102" s="7">
+        <f>(D102-C102*$B$5)*$C$15*F102-B102*($C$9/$B$9)*$B$28-I102*B102*$C$9*F102</f>
+        <v>-239.55146299291965</v>
+      </c>
+      <c r="I102" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J102" s="7">
+        <f>D102*$B$15-C102*$B$5*$B$15-B102*$B$9/$B$18</f>
+        <v>-1.0604112318840588</v>
+      </c>
+      <c r="K102" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G102-$B$17*MAX(0,J102)*F102)</f>
+        <v>-111.32388862283307</v>
+      </c>
+      <c r="L102" s="7">
+        <f>D102*$C$15-C102*$B$5*$C$15-B102*$C$9/$C$18</f>
+        <v>-9.572864130434782</v>
+      </c>
+      <c r="M102" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H102-$B$17*MAX(0,L102)*F102)</f>
+        <v>-239.55146299291965</v>
+      </c>
+      <c r="N102" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>386</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>1.05</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E103)*($A$41:$A$85&lt;$B$8+E103+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G103" s="7">
+        <f>(D103-C103*$B$5)*$B$15*F103-B103*$B$28-I103*B103*$B$9*F103</f>
+        <v>-133.4421548113595</v>
+      </c>
+      <c r="H103" s="7">
+        <f>(D103-C103*$B$5)*$C$15*F103-B103*($C$9/$B$9)*$B$28-I103*B103*$C$9*F103</f>
+        <v>-252.97924350028205</v>
+      </c>
+      <c r="I103" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J103" s="7">
+        <f>D103*$B$15-C103*$B$5*$B$15-B103*$B$9/$B$18</f>
+        <v>-3.4934290398550694</v>
+      </c>
+      <c r="K103" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G103-$B$17*MAX(0,J103)*F103)</f>
+        <v>-133.4421548113595</v>
+      </c>
+      <c r="L103" s="7">
+        <f>D103*$C$15-C103*$B$5*$C$15-B103*$C$9/$C$18</f>
+        <v>-11.049925163043477</v>
+      </c>
+      <c r="M103" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H103-$B$17*MAX(0,L103)*F103)</f>
+        <v>-252.97924350028205</v>
+      </c>
+      <c r="N103" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>387</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104">
+        <v>0.95</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E104)*($A$41:$A$85&lt;$B$8+E104+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G104" s="7">
+        <f>(D104-C104*$B$5)*$B$15*F104-B104*$B$28-I104*B104*$B$9*F104</f>
+        <v>-154.65987590184267</v>
+      </c>
+      <c r="H104" s="7">
+        <f>(D104-C104*$B$5)*$C$15*F104-B104*($C$9/$B$9)*$B$28-I104*B104*$C$9*F104</f>
+        <v>-265.8603119909594</v>
+      </c>
+      <c r="I104" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J104" s="7">
+        <f>D104*$B$15-C104*$B$5*$B$15-B104*$B$9/$B$18</f>
+        <v>-5.827386539855073</v>
+      </c>
+      <c r="K104" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G104-$B$17*MAX(0,J104)*F104)</f>
+        <v>-154.65987590184267</v>
+      </c>
+      <c r="L104" s="7">
+        <f>D104*$C$15-C104*$B$5*$C$15-B104*$C$9/$C$18</f>
+        <v>-12.46684766304348</v>
+      </c>
+      <c r="M104" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H104-$B$17*MAX(0,L104)*F104)</f>
+        <v>-265.8603119909594</v>
+      </c>
+      <c r="N104" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>388</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E105)*($A$41:$A$85&lt;$B$8+E105+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G105" s="7">
+        <f>(D105-C105*$B$5)*$B$15*F105-B105*$B$28-I105*B105*$B$9*F105</f>
+        <v>-122.83329426611789</v>
+      </c>
+      <c r="H105" s="7">
+        <f>(D105-C105*$B$5)*$C$15*F105-B105*($C$9/$B$9)*$B$28-I105*B105*$C$9*F105</f>
+        <v>-246.53870925494337</v>
+      </c>
+      <c r="I105" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J105" s="7">
+        <f>D105*$B$15-C105*$B$5*$B$15-B105*$B$9/$B$18</f>
+        <v>-2.3264502898550674</v>
+      </c>
+      <c r="K105" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G105-$B$17*MAX(0,J105)*F105)</f>
+        <v>-122.83329426611789</v>
+      </c>
+      <c r="L105" s="7">
+        <f>D105*$C$15-C105*$B$5*$C$15-B105*$C$9/$C$18</f>
+        <v>-10.341463913043476</v>
+      </c>
+      <c r="M105" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H105-$B$17*MAX(0,L105)*F105)</f>
+        <v>-246.53870925494337</v>
+      </c>
+      <c r="N105" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>389</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106">
+        <v>0.9</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E106)*($A$41:$A$85&lt;$B$8+E106+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G106" s="7">
+        <f>(D106-C106*$B$5)*$B$15*F106-B106*$B$28-I106*B106*$B$9*F106</f>
+        <v>-165.26873644708425</v>
+      </c>
+      <c r="H106" s="7">
+        <f>(D106-C106*$B$5)*$C$15*F106-B106*($C$9/$B$9)*$B$28-I106*B106*$C$9*F106</f>
+        <v>-272.3008462362981</v>
+      </c>
+      <c r="I106" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J106" s="7">
+        <f>D106*$B$15-C106*$B$5*$B$15-B106*$B$9/$B$18</f>
+        <v>-6.994365289855072</v>
+      </c>
+      <c r="K106" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G106-$B$17*MAX(0,J106)*F106)</f>
+        <v>-165.26873644708425</v>
+      </c>
+      <c r="L106" s="7">
+        <f>D106*$C$15-C106*$B$5*$C$15-B106*$C$9/$C$18</f>
+        <v>-13.175308913043478</v>
+      </c>
+      <c r="M106" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H106-$B$17*MAX(0,L106)*F106)</f>
+        <v>-272.3008462362981</v>
+      </c>
+      <c r="N106" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>390</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>1.2</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E107)*($A$41:$A$85&lt;$B$8+E107+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G107" s="7">
+        <f>(D107-C107*$B$5)*$B$15*F107-B107*$B$28-I107*B107*$B$9*F107</f>
+        <v>-101.61557317563475</v>
+      </c>
+      <c r="H107" s="7">
+        <f>(D107-C107*$B$5)*$C$15*F107-B107*($C$9/$B$9)*$B$28-I107*B107*$C$9*F107</f>
+        <v>-233.657640764266</v>
+      </c>
+      <c r="I107" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J107" s="7">
+        <f>D107*$B$15-C107*$B$5*$B$15-B107*$B$9/$B$18</f>
+        <v>0.007507210144929388</v>
+      </c>
+      <c r="K107" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G107-$B$17*MAX(0,J107)*F107)</f>
+        <v>-101.6292226007869</v>
+      </c>
+      <c r="L107" s="7">
+        <f>D107*$C$15-C107*$B$5*$C$15-B107*$C$9/$C$18</f>
+        <v>-8.92454141304348</v>
+      </c>
+      <c r="M107" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H107-$B$17*MAX(0,L107)*F107)</f>
+        <v>-233.657640764266</v>
+      </c>
+      <c r="N107" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>391</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108">
+        <v>0.8</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E108)*($A$41:$A$85&lt;$B$8+E108+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G108" s="7">
+        <f>(D108-C108*$B$5)*$B$15*F108-B108*$B$28-I108*B108*$B$9*F108</f>
+        <v>-186.4864575375674</v>
+      </c>
+      <c r="H108" s="7">
+        <f>(D108-C108*$B$5)*$C$15*F108-B108*($C$9/$B$9)*$B$28-I108*B108*$C$9*F108</f>
+        <v>-285.1819147269755</v>
+      </c>
+      <c r="I108" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J108" s="7">
+        <f>D108*$B$15-C108*$B$5*$B$15-B108*$B$9/$B$18</f>
+        <v>-9.328322789855072</v>
+      </c>
+      <c r="K108" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G108-$B$17*MAX(0,J108)*F108)</f>
+        <v>-186.4864575375674</v>
+      </c>
+      <c r="L108" s="7">
+        <f>D108*$C$15-C108*$B$5*$C$15-B108*$C$9/$C$18</f>
+        <v>-14.592231413043478</v>
+      </c>
+      <c r="M108" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H108-$B$17*MAX(0,L108)*F108)</f>
+        <v>-285.1819147269755</v>
+      </c>
+      <c r="N108" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>392</v>
+      </c>
+      <c r="B109">
+        <v>1.05</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <v>0.95</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E109)*($A$41:$A$85&lt;$B$8+E109+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G109" s="7">
+        <f>(D109-C109*$B$5)*$B$15*F109-B109*$B$28-I109*B109*$B$9*F109</f>
+        <v>-164.28950553147232</v>
+      </c>
+      <c r="H109" s="7">
+        <f>(D109-C109*$B$5)*$C$15*F109-B109*($C$9/$B$9)*$B$28-I109*B109*$C$9*F109</f>
+        <v>-280.30475643540393</v>
+      </c>
+      <c r="I109" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J109" s="7">
+        <f>D109*$B$15-C109*$B$5*$B$15-B109*$B$9/$B$18</f>
+        <v>-6.327386539855073</v>
+      </c>
+      <c r="K109" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G109-$B$17*MAX(0,J109)*F109)</f>
+        <v>-164.28950553147232</v>
+      </c>
+      <c r="L109" s="7">
+        <f>D109*$C$15-C109*$B$5*$C$15-B109*$C$9/$C$18</f>
+        <v>-13.21684766304348</v>
+      </c>
+      <c r="M109" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H109-$B$17*MAX(0,L109)*F109)</f>
+        <v>-280.30475643540393</v>
+      </c>
+      <c r="N109" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>393</v>
+      </c>
+      <c r="B110">
+        <v>0.95</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>1.05</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E110)*($A$41:$A$85&lt;$B$8+E110+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G110" s="7">
+        <f>(D110-C110*$B$5)*$B$15*F110-B110*$B$28-I110*B110*$B$9*F110</f>
+        <v>-123.81252518172984</v>
+      </c>
+      <c r="H110" s="7">
+        <f>(D110-C110*$B$5)*$C$15*F110-B110*($C$9/$B$9)*$B$28-I110*B110*$C$9*F110</f>
+        <v>-238.5347990558376</v>
+      </c>
+      <c r="I110" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J110" s="7">
+        <f>D110*$B$15-C110*$B$5*$B$15-B110*$B$9/$B$18</f>
+        <v>-2.9934290398550694</v>
+      </c>
+      <c r="K110" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G110-$B$17*MAX(0,J110)*F110)</f>
+        <v>-123.81252518172984</v>
+      </c>
+      <c r="L110" s="7">
+        <f>D110*$C$15-C110*$B$5*$C$15-B110*$C$9/$C$18</f>
+        <v>-10.299925163043477</v>
+      </c>
+      <c r="M110" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H110-$B$17*MAX(0,L110)*F110)</f>
+        <v>-238.5347990558376</v>
+      </c>
+      <c r="N110" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>394</v>
+      </c>
+      <c r="B111">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>0.9</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E111)*($A$41:$A$85&lt;$B$8+E111+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G111" s="7">
+        <f>(D111-C111*$B$5)*$B$15*F111-B111*$B$28-I111*B111*$B$9*F111</f>
+        <v>-184.52799570634352</v>
+      </c>
+      <c r="H111" s="7">
+        <f>(D111-C111*$B$5)*$C$15*F111-B111*($C$9/$B$9)*$B$28-I111*B111*$C$9*F111</f>
+        <v>-301.18973512518704</v>
+      </c>
+      <c r="I111" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J111" s="7">
+        <f>D111*$B$15-C111*$B$5*$B$15-B111*$B$9/$B$18</f>
+        <v>-7.994365289855073</v>
+      </c>
+      <c r="K111" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G111-$B$17*MAX(0,J111)*F111)</f>
+        <v>-184.52799570634352</v>
+      </c>
+      <c r="L111" s="7">
+        <f>D111*$C$15-C111*$B$5*$C$15-B111*$C$9/$C$18</f>
+        <v>-14.675308913043478</v>
+      </c>
+      <c r="M111" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H111-$B$17*MAX(0,L111)*F111)</f>
+        <v>-301.18973512518704</v>
+      </c>
+      <c r="N111" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>395</v>
+      </c>
+      <c r="B112">
+        <v>0.9</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E112)*($A$41:$A$85&lt;$B$8+E112+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G112" s="7">
+        <f>(D112-C112*$B$5)*$B$15*F112-B112*$B$28-I112*B112*$B$9*F112</f>
+        <v>-103.57403500685862</v>
+      </c>
+      <c r="H112" s="7">
+        <f>(D112-C112*$B$5)*$C$15*F112-B112*($C$9/$B$9)*$B$28-I112*B112*$C$9*F112</f>
+        <v>-217.6498203660545</v>
+      </c>
+      <c r="I112" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J112" s="7">
+        <f>D112*$B$15-C112*$B$5*$B$15-B112*$B$9/$B$18</f>
+        <v>-1.3264502898550674</v>
+      </c>
+      <c r="K112" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G112-$B$17*MAX(0,J112)*F112)</f>
+        <v>-103.57403500685862</v>
+      </c>
+      <c r="L112" s="7">
+        <f>D112*$C$15-C112*$B$5*$C$15-B112*$C$9/$C$18</f>
+        <v>-8.841463913043476</v>
+      </c>
+      <c r="M112" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H112-$B$17*MAX(0,L112)*F112)</f>
+        <v>-217.6498203660545</v>
+      </c>
+      <c r="N112" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>396</v>
+      </c>
+      <c r="B113">
+        <v>1.2</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113">
+        <v>0.8</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E113)*($A$41:$A$85&lt;$B$8+E113+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G113" s="7">
+        <f>(D113-C113*$B$5)*$B$15*F113-B113*$B$28-I113*B113*$B$9*F113</f>
+        <v>-225.0049760560859</v>
+      </c>
+      <c r="H113" s="7">
+        <f>(D113-C113*$B$5)*$C$15*F113-B113*($C$9/$B$9)*$B$28-I113*B113*$C$9*F113</f>
+        <v>-342.95969250475326</v>
+      </c>
+      <c r="I113" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J113" s="7">
+        <f>D113*$B$15-C113*$B$5*$B$15-B113*$B$9/$B$18</f>
+        <v>-11.328322789855072</v>
+      </c>
+      <c r="K113" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G113-$B$17*MAX(0,J113)*F113)</f>
+        <v>-225.0049760560859</v>
+      </c>
+      <c r="L113" s="7">
+        <f>D113*$C$15-C113*$B$5*$C$15-B113*$C$9/$C$18</f>
+        <v>-17.59223141304348</v>
+      </c>
+      <c r="M113" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H113-$B$17*MAX(0,L113)*F113)</f>
+        <v>-342.95969250475326</v>
+      </c>
+      <c r="N113" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>397</v>
+      </c>
+      <c r="B114">
+        <v>0.8</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114">
+        <v>1.2</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E114)*($A$41:$A$85&lt;$B$8+E114+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G114" s="7">
+        <f>(D114-C114*$B$5)*$B$15*F114-B114*$B$28-I114*B114*$B$9*F114</f>
+        <v>-63.097054657116246</v>
+      </c>
+      <c r="H114" s="7">
+        <f>(D114-C114*$B$5)*$C$15*F114-B114*($C$9/$B$9)*$B$28-I114*B114*$C$9*F114</f>
+        <v>-175.8798629864883</v>
+      </c>
+      <c r="I114" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J114" s="7">
+        <f>D114*$B$15-C114*$B$5*$B$15-B114*$B$9/$B$18</f>
+        <v>2.0075072101449294</v>
+      </c>
+      <c r="K114" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G114-$B$17*MAX(0,J114)*F114)</f>
+        <v>-66.74705497391628</v>
+      </c>
+      <c r="L114" s="7">
+        <f>D114*$C$15-C114*$B$5*$C$15-B114*$C$9/$C$18</f>
+        <v>-5.92454141304348</v>
+      </c>
+      <c r="M114" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H114-$B$17*MAX(0,L114)*F114)</f>
+        <v>-175.8798629864883</v>
+      </c>
+      <c r="N114" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>398</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E115)*($A$41:$A$85&lt;$B$8+E115+$B$7))</f>
+        <v>8.417478915851582</v>
+      </c>
+      <c r="G115" s="7">
+        <f>(D115-C115*$B$5)*$B$15*F115-B115*$B$28-I115*B115*$B$9*F115</f>
+        <v>-147.6466877444523</v>
+      </c>
+      <c r="H115" s="7">
+        <f>(D115-C115*$B$5)*$C$15*F115-B115*($C$9/$B$9)*$B$28-I115*B115*$C$9*F115</f>
+        <v>-261.6026748673443</v>
+      </c>
+      <c r="I115" s="6">
+        <f>$B$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J115" s="7">
+        <f>D115*$B$15-C115*$B$5*$B$15-B115*$B$9/$B$18</f>
+        <v>-4.660407789855071</v>
+      </c>
+      <c r="K115" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G115-$B$17*MAX(0,J115)*F115)</f>
+        <v>-147.6466877444523</v>
+      </c>
+      <c r="L115" s="7">
+        <f>D115*$C$15-C115*$B$5*$C$15-B115*$C$9/$C$18</f>
+        <v>-11.758386413043478</v>
+      </c>
+      <c r="M115" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H115-$B$17*MAX(0,L115)*F115)</f>
+        <v>-261.6026748673443</v>
+      </c>
+      <c r="N115" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>399</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116" s="6">
+        <f>SUMPRODUCT($B$41:$B$85*($A$41:$A$85&gt;=$B$8+E116)*($A$41:$A$85&lt;$B$8+E116+$B$7))</f>
+        <v>9.090877229119709</v>
+      </c>
+      <c r="G116" s="7">
+        <f>(D116-C116*$B$5)*$B$15*F116-B116*$B$28-I116*B116*$B$9*F116</f>
+        <v>-287.8564770696819</v>
+      </c>
+      <c r="H116" s="7">
+        <f>(D116-C116*$B$5)*$C$15*F116-B116*($C$9/$B$9)*$B$28-I116*B116*$C$9*F116</f>
+        <v>-475.127970315242</v>
+      </c>
+      <c r="I116" s="6">
         <f>Inputs!$C$166</f>
-        <v>7.9093281148075664E-2</v>
-      </c>
-      <c r="J94" s="7">
-        <f t="shared" si="21"/>
-        <v>-4.6604077898550713</v>
-      </c>
-      <c r="K94" s="7">
-        <f t="shared" si="22"/>
-        <v>-287.85647706968189</v>
-      </c>
-      <c r="L94" s="7">
-        <f t="shared" si="23"/>
+        <v>0.07909328114807566</v>
+      </c>
+      <c r="J116" s="7">
+        <f>D116*$B$15-C116*$B$5*$B$15-B116*$B$9/$B$18</f>
+        <v>-4.660407789855071</v>
+      </c>
+      <c r="K116" s="7">
+        <f>IF($B$18&lt;$B$7,"n/a",G116-$B$17*MAX(0,J116)*F116)</f>
+        <v>-287.8564770696819</v>
+      </c>
+      <c r="L116" s="7">
+        <f>D116*$C$15-C116*$B$5*$C$15-B116*$C$9/$C$18</f>
         <v>-11.758386413043478</v>
       </c>
-      <c r="M94" s="7">
-        <f t="shared" si="24"/>
-        <v>-475.12797031524201</v>
-      </c>
-      <c r="N94" t="s">
+      <c r="M116" s="7">
+        <f>IF($C$18&lt;$C$7,"n/a",H116-$B$17*MAX(0,L116)*F116)</f>
+        <v>-475.127970315242</v>
+      </c>
+      <c r="N116" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="42" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
+    <row r="124" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B124" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F124" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="G124" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="H124" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="I102" s="3" t="s">
+      <c r="I124" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>406</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B125" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C103">
+      <c r="C125">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D103">
+        <v>20.0</v>
+      </c>
+      <c r="D125">
         <f>$B$19</f>
-        <v>1</v>
-      </c>
-      <c r="E103" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E125" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F103" s="7">
-        <f>$B$14*$B$13/1000+D103*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F125" s="7">
+        <f>$B$14*$B$13/1000+D125*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G103" s="6">
-        <f t="shared" ref="G103:G113" si="25">(1+B103)^(-$B$8)*(1-(1+B103)^(-C103))/(1-1/(1+B103))</f>
-        <v>9.0908772291197018</v>
-      </c>
-      <c r="H103" s="7">
-        <f t="shared" ref="H103:H113" si="26">($B$9/$B$8)*(1-(1+B103)^(-$B$8))/(1-1/(1+B103))</f>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I103" s="7">
-        <f t="shared" ref="I103:I113" si="27">(F103*(1-$B$5)-E103*$B$9)*G103-H103</f>
-        <v>-144.05101535660091</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="G125" s="6">
+        <f>(1+B125)^(-$B$8)*(1-(1+B125)^(-C125))/(1-1/(1+B125))</f>
+        <v>9.090877229119702</v>
+      </c>
+      <c r="H125" s="7">
+        <f>($B$9/$B$8)*(1-(1+B125)^(-$B$8))/(1-1/(1+B125))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I125" s="7">
+        <f>(F125*(1-$B$5)-E125*$B$9)*G125-H125</f>
+        <v>-144.05101535660106</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>407</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B126" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C104">
+      <c r="C126">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D104">
+        <v>20.0</v>
+      </c>
+      <c r="D126">
         <v>0</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E126" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F104" s="7">
-        <f>$B$14*$B$13/1000+D104*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F126" s="7">
+        <f>$B$14*$B$13/1000+D126*$B$14*Inputs!$D$148/1000</f>
         <v>14.169225000000003</v>
       </c>
-      <c r="G104" s="6">
-        <f t="shared" si="25"/>
-        <v>9.0908772291197018</v>
-      </c>
-      <c r="H104" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I104" s="7">
-        <f t="shared" si="27"/>
-        <v>-163.12348144932429</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="G126" s="6">
+        <f>(1+B126)^(-$B$8)*(1-(1+B126)^(-C126))/(1-1/(1+B126))</f>
+        <v>9.090877229119702</v>
+      </c>
+      <c r="H126" s="7">
+        <f>($B$9/$B$8)*(1-(1+B126)^(-$B$8))/(1-1/(1+B126))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I126" s="7">
+        <f>(F126*(1-$B$5)-E126*$B$9)*G126-H126</f>
+        <v>-163.12348144932446</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>408</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B127" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C105">
+      <c r="C127">
         <v>30</v>
       </c>
-      <c r="D105">
-        <f t="shared" ref="D105:D111" si="28">$B$19</f>
-        <v>1</v>
-      </c>
-      <c r="E105" s="6">
+      <c r="D127">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E127" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="7">
-        <f>$B$14*$B$13/1000+D105*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F127" s="7">
+        <f>$B$14*$B$13/1000+D127*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G105" s="6">
-        <f t="shared" si="25"/>
-        <v>10.423873465858767</v>
-      </c>
-      <c r="H105" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I105" s="7">
-        <f t="shared" si="27"/>
-        <v>-136.93335903475651</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="G127" s="6">
+        <f>(1+B127)^(-$B$8)*(1-(1+B127)^(-C127))/(1-1/(1+B127))</f>
+        <v>10.423873465858765</v>
+      </c>
+      <c r="H127" s="7">
+        <f>($B$9/$B$8)*(1-(1+B127)^(-$B$8))/(1-1/(1+B127))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I127" s="7">
+        <f>(F127*(1-$B$5)-E127*$B$9)*G127-H127</f>
+        <v>-136.93335903475665</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>409</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B128" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C106">
+      <c r="C128">
         <v>40</v>
       </c>
-      <c r="D106">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="E106" s="6">
+      <c r="D128">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E128" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F106" s="7">
-        <f>$B$14*$B$13/1000+D106*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F128" s="7">
+        <f>$B$14*$B$13/1000+D128*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G106" s="6">
-        <f t="shared" si="25"/>
-        <v>11.041308642357691</v>
-      </c>
-      <c r="H106" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I106" s="7">
-        <f t="shared" si="27"/>
-        <v>-133.6365069760534</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="G128" s="6">
+        <f>(1+B128)^(-$B$8)*(1-(1+B128)^(-C128))/(1-1/(1+B128))</f>
+        <v>11.04130864235769</v>
+      </c>
+      <c r="H128" s="7">
+        <f>($B$9/$B$8)*(1-(1+B128)^(-$B$8))/(1-1/(1+B128))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I128" s="7">
+        <f>(F128*(1-$B$5)-E128*$B$9)*G128-H128</f>
+        <v>-133.63650697605354</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>410</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B129" s="8">
         <v>0.06</v>
       </c>
-      <c r="C107">
+      <c r="C129">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D107">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="E107" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D129">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E129" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F107" s="7">
-        <f>$B$14*$B$13/1000+D107*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F129" s="7">
+        <f>$B$14*$B$13/1000+D129*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G107" s="6">
-        <f t="shared" si="25"/>
+      <c r="G129" s="6">
+        <f>(1+B129)^(-$B$8)*(1-(1+B129)^(-C129))/(1-1/(1+B129))</f>
         <v>10.820680394872868</v>
       </c>
-      <c r="H107" s="7">
-        <f t="shared" si="26"/>
-        <v>194.33962264150929</v>
-      </c>
-      <c r="I107" s="7">
-        <f t="shared" si="27"/>
+      <c r="H129" s="7">
+        <f>($B$9/$B$8)*(1-(1+B129)^(-$B$8))/(1-1/(1+B129))</f>
+        <v>194.3396226415093</v>
+      </c>
+      <c r="I129" s="7">
+        <f>(F129*(1-$B$5)-E129*$B$9)*G129-H129</f>
         <v>-136.5616018965782</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>411</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B130" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C108">
+      <c r="C130">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D108">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="E108" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D130">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E130" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F108" s="7">
-        <f>$B$14*$B$13/1000+D108*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F130" s="7">
+        <f>$B$14*$B$13/1000+D130*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G108" s="6">
-        <f t="shared" si="25"/>
-        <v>9.9009478930057568</v>
-      </c>
-      <c r="H108" s="7">
-        <f t="shared" si="26"/>
+      <c r="G130" s="6">
+        <f>(1+B130)^(-$B$8)*(1-(1+B130)^(-C130))/(1-1/(1+B130))</f>
+        <v>9.90094789300576</v>
+      </c>
+      <c r="H130" s="7">
+        <f>($B$9/$B$8)*(1-(1+B130)^(-$B$8))/(1-1/(1+B130))</f>
         <v>193.45794392523374</v>
       </c>
-      <c r="I108" s="7">
-        <f t="shared" si="27"/>
-        <v>-140.59091968268936</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="I130" s="7">
+        <f>(F130*(1-$B$5)-E130*$B$9)*G130-H130</f>
+        <v>-140.59091968268933</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>412</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B131" s="8">
         <v>0.1</v>
       </c>
-      <c r="C109">
+      <c r="C131">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D109">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="E109" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D131">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E131" s="6">
         <f>B16</f>
-        <v>0</v>
-      </c>
-      <c r="F109" s="7">
-        <f>$B$14*$B$13/1000+D109*$B$14*Inputs!$D$148/1000</f>
+        <v>0.0</v>
+      </c>
+      <c r="F131" s="7">
+        <f>$B$14*$B$13/1000+D131*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G109" s="6">
-        <f t="shared" si="25"/>
-        <v>7.7396033815986929</v>
-      </c>
-      <c r="H109" s="7">
-        <f t="shared" si="26"/>
+      <c r="G131" s="6">
+        <f>(1+B131)^(-$B$8)*(1-(1+B131)^(-C131))/(1-1/(1+B131))</f>
+        <v>7.739603381598693</v>
+      </c>
+      <c r="H131" s="7">
+        <f>($B$9/$B$8)*(1-(1+B131)^(-$B$8))/(1-1/(1+B131))</f>
         <v>190.90909090909093</v>
       </c>
-      <c r="I109" s="7">
-        <f t="shared" si="27"/>
+      <c r="I131" s="7">
+        <f>(F131*(1-$B$5)-E131*$B$9)*G131-H131</f>
         <v>-149.58276498309522</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>413</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B132" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C110">
+      <c r="C132">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D110">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="E110" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D132">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E132" s="6">
         <f>Inputs!$C$166</f>
-        <v>7.9093281148075664E-2</v>
-      </c>
-      <c r="F110" s="7">
-        <f>$B$14*$B$13/1000+D110*$B$14*Inputs!$D$148/1000</f>
+        <v>0.07909328114807566</v>
+      </c>
+      <c r="F132" s="7">
+        <f>$B$14*$B$13/1000+D132*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G110" s="6">
-        <f t="shared" si="25"/>
-        <v>9.0908772291197018</v>
-      </c>
-      <c r="H110" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I110" s="7">
-        <f t="shared" si="27"/>
-        <v>-287.85647706968166</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="G132" s="6">
+        <f>(1+B132)^(-$B$8)*(1-(1+B132)^(-C132))/(1-1/(1+B132))</f>
+        <v>9.090877229119702</v>
+      </c>
+      <c r="H132" s="7">
+        <f>($B$9/$B$8)*(1-(1+B132)^(-$B$8))/(1-1/(1+B132))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I132" s="7">
+        <f>(F132*(1-$B$5)-E132*$B$9)*G132-H132</f>
+        <v>-287.8564770696818</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>414</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B133" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C111">
+      <c r="C133">
         <v>30</v>
       </c>
-      <c r="D111">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="E111" s="6">
+      <c r="D133">
+        <f>$B$19</f>
+        <v>1.0</v>
+      </c>
+      <c r="E133" s="6">
         <f>Inputs!$C$166</f>
-        <v>7.9093281148075664E-2</v>
-      </c>
-      <c r="F111" s="7">
-        <f>$B$14*$B$13/1000+D111*$B$14*Inputs!$D$148/1000</f>
+        <v>0.07909328114807566</v>
+      </c>
+      <c r="F133" s="7">
+        <f>$B$14*$B$13/1000+D133*$B$14*Inputs!$D$148/1000</f>
         <v>23.339575000000004</v>
       </c>
-      <c r="G111" s="6">
-        <f t="shared" si="25"/>
-        <v>10.423873465858767</v>
-      </c>
-      <c r="H111" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I111" s="7">
-        <f t="shared" si="27"/>
-        <v>-301.82502997218319</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="G133" s="6">
+        <f>(1+B133)^(-$B$8)*(1-(1+B133)^(-C133))/(1-1/(1+B133))</f>
+        <v>10.423873465858765</v>
+      </c>
+      <c r="H133" s="7">
+        <f>($B$9/$B$8)*(1-(1+B133)^(-$B$8))/(1-1/(1+B133))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I133" s="7">
+        <f>(F133*(1-$B$5)-E133*$B$9)*G133-H133</f>
+        <v>-301.8250299721833</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>415</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B134" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C112">
+      <c r="C134">
         <f>B7</f>
-        <v>20</v>
-      </c>
-      <c r="D112">
+        <v>20.0</v>
+      </c>
+      <c r="D134">
         <v>0</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E134" s="6">
         <f>Inputs!$C$166</f>
-        <v>7.9093281148075664E-2</v>
-      </c>
-      <c r="F112" s="7">
-        <f>$B$14*$B$13/1000+D112*$B$14*Inputs!$D$148/1000</f>
+        <v>0.07909328114807566</v>
+      </c>
+      <c r="F134" s="7">
+        <f>$B$14*$B$13/1000+D134*$B$14*Inputs!$D$148/1000</f>
         <v>14.169225000000003</v>
       </c>
-      <c r="G112" s="6">
-        <f t="shared" si="25"/>
-        <v>9.0908772291197018</v>
-      </c>
-      <c r="H112" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I112" s="7">
-        <f t="shared" si="27"/>
-        <v>-306.92894316240506</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="G134" s="6">
+        <f>(1+B134)^(-$B$8)*(1-(1+B134)^(-C134))/(1-1/(1+B134))</f>
+        <v>9.090877229119702</v>
+      </c>
+      <c r="H134" s="7">
+        <f>($B$9/$B$8)*(1-(1+B134)^(-$B$8))/(1-1/(1+B134))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I134" s="7">
+        <f>(F134*(1-$B$5)-E134*$B$9)*G134-H134</f>
+        <v>-306.9289431624052</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>416</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B135" s="8">
         <f>B6</f>
         <v>0.08</v>
       </c>
-      <c r="C113">
+      <c r="C135">
         <v>30</v>
       </c>
-      <c r="D113">
+      <c r="D135">
         <v>0</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E135" s="6">
         <f>Inputs!$C$166</f>
-        <v>7.9093281148075664E-2</v>
-      </c>
-      <c r="F113" s="7">
-        <f>$B$14*$B$13/1000+D113*$B$14*Inputs!$D$148/1000</f>
+        <v>0.07909328114807566</v>
+      </c>
+      <c r="F135" s="7">
+        <f>$B$14*$B$13/1000+D135*$B$14*Inputs!$D$148/1000</f>
         <v>14.169225000000003</v>
       </c>
-      <c r="G113" s="6">
-        <f t="shared" si="25"/>
-        <v>10.423873465858767</v>
-      </c>
-      <c r="H113" s="7">
-        <f t="shared" si="26"/>
-        <v>192.59259259259238</v>
-      </c>
-      <c r="I113" s="7">
-        <f t="shared" si="27"/>
-        <v>-323.69409367437572</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+      <c r="G135" s="6">
+        <f>(1+B135)^(-$B$8)*(1-(1+B135)^(-C135))/(1-1/(1+B135))</f>
+        <v>10.423873465858765</v>
+      </c>
+      <c r="H135" s="7">
+        <f>($B$9/$B$8)*(1-(1+B135)^(-$B$8))/(1-1/(1+B135))</f>
+        <v>192.59259259259252</v>
+      </c>
+      <c r="I135" s="7">
+        <f>(F135*(1-$B$5)-E135*$B$9)*G135-H135</f>
+        <v>-323.69409367437584</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B119" s="6">
+      <c r="B141" s="6">
         <v>0.7</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C141" s="6">
         <f>B5</f>
-        <v>0.77122153209109734</v>
-      </c>
-      <c r="D119" s="6">
+        <v>0.7712215320910973</v>
+      </c>
+      <c r="D141" s="6">
         <f>Inputs!$C$151</f>
-        <v>0.93830000000000002</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120">
+        <v>0.9383</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A142">
         <v>150</v>
       </c>
-      <c r="B120" s="7">
-        <f t="shared" ref="B120:D123" si="29">$B$15*(1-B$119)*$B$27-$A120*($B$28/$B$9)-$B$16*$A120*$B$27</f>
-        <v>-80.791281172994928</v>
-      </c>
-      <c r="C120" s="7">
-        <f t="shared" si="29"/>
-        <v>-95.902867208452932</v>
-      </c>
-      <c r="D120" s="7">
-        <f t="shared" si="29"/>
+      <c r="B142" s="7">
+        <f>$B$15*(1-B$141)*$B$27-$A142*($B$28/$B$9)-$B$16*$A142*$B$27</f>
+        <v>-80.79128117299493</v>
+      </c>
+      <c r="C142" s="7">
+        <f>$B$15*(1-C$141)*$B$27-$A142*($B$28/$B$9)-$B$16*$A142*$B$27</f>
+        <v>-95.90286720845293</v>
+      </c>
+      <c r="D142" s="7">
+        <f>$B$15*(1-D$141)*$B$27-$A142*($B$28/$B$9)-$B$16*$A142*$B$27</f>
         <v>-131.35311053161632</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143">
         <v>200</v>
       </c>
-      <c r="B121" s="7">
-        <f t="shared" si="29"/>
+      <c r="B143" s="7">
+        <f>$B$15*(1-B$141)*$B$27-$A143*($B$28/$B$9)-$B$16*$A143*$B$27</f>
         <v>-128.93942932114308</v>
       </c>
-      <c r="C121" s="7">
-        <f t="shared" si="29"/>
+      <c r="C143" s="7">
+        <f>$B$15*(1-C$141)*$B$27-$A143*($B$28/$B$9)-$B$16*$A143*$B$27</f>
         <v>-144.05101535660108</v>
       </c>
-      <c r="D121" s="7">
-        <f t="shared" si="29"/>
+      <c r="D143" s="7">
+        <f>$B$15*(1-D$141)*$B$27-$A143*($B$28/$B$9)-$B$16*$A143*$B$27</f>
         <v>-179.50125867976448</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144">
         <v>250</v>
       </c>
-      <c r="B122" s="7">
-        <f t="shared" si="29"/>
+      <c r="B144" s="7">
+        <f>$B$15*(1-B$141)*$B$27-$A144*($B$28/$B$9)-$B$16*$A144*$B$27</f>
         <v>-177.08757746929123</v>
       </c>
-      <c r="C122" s="7">
-        <f t="shared" si="29"/>
+      <c r="C144" s="7">
+        <f>$B$15*(1-C$141)*$B$27-$A144*($B$28/$B$9)-$B$16*$A144*$B$27</f>
         <v>-192.19916350474924</v>
       </c>
-      <c r="D122" s="7">
-        <f t="shared" si="29"/>
+      <c r="D144" s="7">
+        <f>$B$15*(1-D$141)*$B$27-$A144*($B$28/$B$9)-$B$16*$A144*$B$27</f>
         <v>-227.64940682791263</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A145">
         <v>300</v>
       </c>
-      <c r="B123" s="7">
-        <f t="shared" si="29"/>
+      <c r="B145" s="7">
+        <f>$B$15*(1-B$141)*$B$27-$A145*($B$28/$B$9)-$B$16*$A145*$B$27</f>
         <v>-225.23572561743936</v>
       </c>
-      <c r="C123" s="7">
-        <f t="shared" si="29"/>
+      <c r="C145" s="7">
+        <f>$B$15*(1-C$141)*$B$27-$A145*($B$28/$B$9)-$B$16*$A145*$B$27</f>
         <v>-240.34731165289736</v>
       </c>
-      <c r="D123" s="7">
-        <f t="shared" si="29"/>
-        <v>-275.79755497606072</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
+      <c r="D145" s="7">
+        <f>$B$15*(1-D$141)*$B$27-$A145*($B$28/$B$9)-$B$16*$A145*$B$27</f>
+        <v>-275.7975549760607</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B149" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C149" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>422</v>
       </c>
-      <c r="B128">
+      <c r="B150">
         <v>17.8</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C150" t="s">
         <v>423</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D150" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>425</v>
       </c>
-      <c r="B129">
+      <c r="B151">
         <v>17.3</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C151" t="s">
         <v>423</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D151" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>427</v>
       </c>
-      <c r="B130">
+      <c r="B152">
         <f>Inputs!$C$83</f>
         <v>7.5</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C152" t="s">
         <v>428</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D152" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>430</v>
       </c>
-      <c r="B131">
+      <c r="B153">
         <v>14</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C153" t="s">
         <v>431</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D153" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>433</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B154" t="s">
         <v>434</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D154" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>435</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B156" s="7">
         <f>B25</f>
-        <v>43.147150391637652</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+        <v>43.14715039163766</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>436</v>
       </c>
-      <c r="B135" s="13">
-        <f>B25/B128</f>
+      <c r="B157" s="13">
+        <f>B25/B150</f>
         <v>2.4239972130133514</v>
       </c>
     </row>
